--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E09E3F0-EBDF-448B-8FFD-E64EE5FD5CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A009BC63-54EA-4ADC-8897-D4D85B990769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6652,7 +6652,7 @@
         <v>6500</v>
       </c>
       <c r="F17" t="s">
-        <v>959</v>
+        <v>1007</v>
       </c>
       <c r="G17" t="s">
         <v>991</v>

--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A009BC63-54EA-4ADC-8897-D4D85B990769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B3AEA4-18F2-4356-8DBD-D3870BA90B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2930,9 +2930,6 @@
     <t>?</t>
   </si>
   <si>
-    <t>mary.brown@yahoo.com</t>
-  </si>
-  <si>
     <t>daniel.johnson@yahoo.com</t>
   </si>
   <si>
@@ -2957,9 +2954,6 @@
     <t xml:space="preserve"> 2019-07-03 </t>
   </si>
   <si>
-    <t>john.davis@hotmail.com</t>
-  </si>
-  <si>
     <t>not available</t>
   </si>
   <si>
@@ -5733,6 +5727,12 @@
   </si>
   <si>
     <t xml:space="preserve">Robert     Brown </t>
+  </si>
+  <si>
+    <t>mary.brown@yahoo</t>
+  </si>
+  <si>
+    <t>john.davishotmail.com</t>
   </si>
 </sst>
 </file>
@@ -5742,10 +5742,18 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5768,10 +5776,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5780,8 +5789,10 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6220,8 +6231,8 @@
       <c r="G4" s="5">
         <v>43909</v>
       </c>
-      <c r="H4" t="s">
-        <v>964</v>
+      <c r="H4" s="6" t="s">
+        <v>1897</v>
       </c>
       <c r="I4">
         <v>37773911</v>
@@ -6256,7 +6267,7 @@
         <v>45628</v>
       </c>
       <c r="H5" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I5">
         <v>37855874</v>
@@ -6273,7 +6284,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -6288,19 +6299,19 @@
         <v>33</v>
       </c>
       <c r="G6" t="s">
+        <v>965</v>
+      </c>
+      <c r="H6" t="s">
         <v>966</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>967</v>
-      </c>
-      <c r="I6" t="s">
-        <v>968</v>
       </c>
       <c r="J6" t="s">
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -6326,10 +6337,10 @@
         <v>44127</v>
       </c>
       <c r="H7" t="s">
+        <v>969</v>
+      </c>
+      <c r="I7" t="s">
         <v>970</v>
-      </c>
-      <c r="I7" t="s">
-        <v>971</v>
       </c>
       <c r="J7" t="s">
         <v>54</v>
@@ -6358,19 +6369,19 @@
         <v>500</v>
       </c>
       <c r="G8" t="s">
+        <v>971</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1898</v>
+      </c>
+      <c r="I8" t="s">
         <v>972</v>
-      </c>
-      <c r="H8" t="s">
-        <v>973</v>
-      </c>
-      <c r="I8" t="s">
-        <v>974</v>
       </c>
       <c r="J8" t="s">
         <v>962</v>
       </c>
       <c r="K8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -6390,7 +6401,7 @@
         <v>45561</v>
       </c>
       <c r="H9" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="I9">
         <v>55859430</v>
@@ -6399,7 +6410,7 @@
         <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -6416,13 +6427,13 @@
         <v>9000</v>
       </c>
       <c r="G10" t="s">
+        <v>974</v>
+      </c>
+      <c r="H10" t="s">
+        <v>975</v>
+      </c>
+      <c r="I10" t="s">
         <v>976</v>
-      </c>
-      <c r="H10" t="s">
-        <v>977</v>
-      </c>
-      <c r="I10" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -6445,20 +6456,20 @@
         <v>500</v>
       </c>
       <c r="G11" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H11" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="I11">
         <f>974-7599-3420</f>
         <v>-10045</v>
       </c>
       <c r="J11" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -6481,19 +6492,19 @@
         <v>500</v>
       </c>
       <c r="G12" t="s">
+        <v>980</v>
+      </c>
+      <c r="H12" t="s">
+        <v>981</v>
+      </c>
+      <c r="I12" t="s">
         <v>982</v>
-      </c>
-      <c r="H12" t="s">
-        <v>983</v>
-      </c>
-      <c r="I12" t="s">
-        <v>984</v>
       </c>
       <c r="J12" t="s">
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -6516,7 +6527,7 @@
         <v>1000</v>
       </c>
       <c r="H13" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="I13">
         <f>974-4653-7608</f>
@@ -6549,10 +6560,10 @@
         <v>-50</v>
       </c>
       <c r="G14" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="H14" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="I14">
         <v>55031838</v>
@@ -6587,7 +6598,7 @@
         <v>44197</v>
       </c>
       <c r="H15" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="I15">
         <f>974-5656-2009</f>
@@ -6597,7 +6608,7 @@
         <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -6620,10 +6631,10 @@
         <v>-50</v>
       </c>
       <c r="G16" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H16" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="I16">
         <v>97445192493</v>
@@ -6632,7 +6643,7 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -6652,16 +6663,16 @@
         <v>6500</v>
       </c>
       <c r="F17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G17" t="s">
+        <v>989</v>
+      </c>
+      <c r="H17" t="s">
+        <v>990</v>
+      </c>
+      <c r="I17" t="s">
         <v>991</v>
-      </c>
-      <c r="H17" t="s">
-        <v>992</v>
-      </c>
-      <c r="I17" t="s">
-        <v>993</v>
       </c>
       <c r="J17" t="s">
         <v>48</v>
@@ -6687,19 +6698,19 @@
         <v>4500</v>
       </c>
       <c r="F18" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G18" t="s">
+        <v>992</v>
+      </c>
+      <c r="H18" t="s">
+        <v>993</v>
+      </c>
+      <c r="I18" t="s">
         <v>994</v>
       </c>
-      <c r="H18" t="s">
-        <v>995</v>
-      </c>
-      <c r="I18" t="s">
-        <v>996</v>
-      </c>
       <c r="J18" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K18" t="s">
         <v>65</v>
@@ -6728,16 +6739,16 @@
         <v>45639</v>
       </c>
       <c r="H19" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="I19" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="J19" t="s">
         <v>57</v>
       </c>
       <c r="K19" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -6763,7 +6774,7 @@
         <v>44493</v>
       </c>
       <c r="H20" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I20">
         <v>39879075</v>
@@ -6772,7 +6783,7 @@
         <v>56</v>
       </c>
       <c r="K20" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -6795,16 +6806,16 @@
         <v>300</v>
       </c>
       <c r="G21" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="H21" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="I21">
         <v>32905889</v>
       </c>
       <c r="J21" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K21" t="s">
         <v>63</v>
@@ -6830,19 +6841,19 @@
         <v>33</v>
       </c>
       <c r="G22" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I22" t="s">
         <v>1004</v>
       </c>
-      <c r="H22" t="s">
-        <v>1005</v>
-      </c>
-      <c r="I22" t="s">
-        <v>1006</v>
-      </c>
       <c r="J22" t="s">
         <v>48</v>
       </c>
       <c r="K22" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -6862,13 +6873,13 @@
         <v>4800</v>
       </c>
       <c r="F23" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G23" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H23" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="I23">
         <v>59017135</v>
@@ -6897,13 +6908,13 @@
         <v>9500</v>
       </c>
       <c r="G24" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I24" t="s">
         <v>1009</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I24" t="s">
-        <v>1011</v>
       </c>
       <c r="J24" t="s">
         <v>55</v>
@@ -6935,10 +6946,10 @@
         <v>51</v>
       </c>
       <c r="H25" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I25" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="J25" t="s">
         <v>50</v>
@@ -6964,19 +6975,19 @@
         <v>5750</v>
       </c>
       <c r="F26" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H26" t="s">
         <v>1014</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>1015</v>
       </c>
-      <c r="H26" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1017</v>
-      </c>
       <c r="J26" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K26" t="s">
         <v>50</v>
@@ -6999,22 +7010,22 @@
         <v>6000</v>
       </c>
       <c r="F27" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H27" t="s">
         <v>1018</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H27" t="s">
-        <v>1020</v>
       </c>
       <c r="I27">
         <v>97430013586</v>
       </c>
       <c r="J27" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K27" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -7040,7 +7051,7 @@
         <v>52</v>
       </c>
       <c r="I28" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J28" t="s">
         <v>56</v>
@@ -7072,13 +7083,13 @@
         <v>45352</v>
       </c>
       <c r="H29" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I29">
         <v>41162889</v>
       </c>
       <c r="J29" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K29" t="s">
         <v>48</v>
@@ -7110,7 +7121,7 @@
         <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="J30" t="s">
         <v>55</v>
@@ -7139,13 +7150,13 @@
         <v>250</v>
       </c>
       <c r="G31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I31" t="s">
         <v>1025</v>
-      </c>
-      <c r="H31" t="s">
-        <v>1026</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1027</v>
       </c>
       <c r="J31" t="s">
         <v>50</v>
@@ -7174,13 +7185,13 @@
         <v>1000</v>
       </c>
       <c r="G32" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I32" t="s">
         <v>1028</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I32" t="s">
-        <v>1030</v>
       </c>
       <c r="J32" t="s">
         <v>60</v>
@@ -7212,7 +7223,7 @@
         <v>45512</v>
       </c>
       <c r="H33" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="I33">
         <f>974-4124-5950</f>
@@ -7222,7 +7233,7 @@
         <v>58</v>
       </c>
       <c r="K33" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -7245,16 +7256,16 @@
         <v>750</v>
       </c>
       <c r="G34" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="H34" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="I34">
         <v>37354619</v>
       </c>
       <c r="J34" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -7286,7 +7297,7 @@
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="J35" t="s">
         <v>58</v>
@@ -7315,20 +7326,20 @@
         <v>250</v>
       </c>
       <c r="G36" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H36" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="I36">
         <f>974-5264-7387</f>
         <v>-11677</v>
       </c>
       <c r="J36" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K36" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -7351,19 +7362,19 @@
         <v>250</v>
       </c>
       <c r="G37" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I37" t="s">
         <v>1037</v>
-      </c>
-      <c r="H37" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1039</v>
       </c>
       <c r="J37" t="s">
         <v>55</v>
       </c>
       <c r="K37" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -7389,16 +7400,16 @@
         <v>45083</v>
       </c>
       <c r="H38" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="I38" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="J38" t="s">
         <v>59</v>
       </c>
       <c r="K38" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -7453,13 +7464,13 @@
         <v>963</v>
       </c>
       <c r="G40" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I40" t="s">
         <v>1042</v>
-      </c>
-      <c r="H40" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I40" t="s">
-        <v>1044</v>
       </c>
       <c r="J40" t="s">
         <v>48</v>
@@ -7491,10 +7502,10 @@
         <v>44173</v>
       </c>
       <c r="H41" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="I41" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="J41" t="s">
         <v>58</v>
@@ -7526,10 +7537,10 @@
         <v>43860</v>
       </c>
       <c r="H42" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="I42" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="K42" t="s">
         <v>50</v>
@@ -7555,10 +7566,10 @@
         <v>500</v>
       </c>
       <c r="G43" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H43" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="I43" t="s">
         <v>48</v>
@@ -7567,7 +7578,7 @@
         <v>58</v>
       </c>
       <c r="K43" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -7593,10 +7604,10 @@
         <v>44652</v>
       </c>
       <c r="H44" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="I44" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="J44" t="s">
         <v>56</v>
@@ -7622,19 +7633,19 @@
         <v>-250</v>
       </c>
       <c r="G45" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I45" t="s">
         <v>1053</v>
-      </c>
-      <c r="H45" t="s">
-        <v>1054</v>
-      </c>
-      <c r="I45" t="s">
-        <v>1055</v>
       </c>
       <c r="J45" t="s">
         <v>50</v>
       </c>
       <c r="K45" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -7657,7 +7668,7 @@
         <v>44394</v>
       </c>
       <c r="H46" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I46">
         <f>974-6091-2981</f>
@@ -7693,10 +7704,10 @@
         <v>45384</v>
       </c>
       <c r="H47" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="I47" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="J47" t="s">
         <v>57</v>
@@ -7722,13 +7733,13 @@
         <v>8500</v>
       </c>
       <c r="F48" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G48" s="5">
         <v>43577</v>
       </c>
       <c r="H48" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="I48">
         <f>974-4964-4959</f>
@@ -7764,13 +7775,13 @@
         <v>44248</v>
       </c>
       <c r="H49" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="I49" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="J49" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K49" t="s">
         <v>65</v>
@@ -7799,7 +7810,7 @@
         <v>44270</v>
       </c>
       <c r="H50" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I50">
         <f>974-4026-1290</f>
@@ -7832,10 +7843,10 @@
         <v>1000</v>
       </c>
       <c r="G51" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="H51" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="I51">
         <f>974-7656-1972</f>
@@ -7865,10 +7876,10 @@
         <v>6000</v>
       </c>
       <c r="G52" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="H52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="I52">
         <v>123</v>
@@ -7903,13 +7914,13 @@
         <v>44567</v>
       </c>
       <c r="H53" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="I53" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J53" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K53" t="s">
         <v>64</v>
@@ -7938,14 +7949,14 @@
         <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I54">
         <f>974-4176-4361</f>
         <v>-7563</v>
       </c>
       <c r="J54" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K54" t="s">
         <v>50</v>
@@ -7974,13 +7985,13 @@
         <v>45549</v>
       </c>
       <c r="H55" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I55">
         <v>45333206</v>
       </c>
       <c r="J55" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K55" t="s">
         <v>67</v>
@@ -8006,16 +8017,16 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="H56" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="I56" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="K56" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -8041,13 +8052,13 @@
         <v>50</v>
       </c>
       <c r="H57" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="I57" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="J57" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K57" t="s">
         <v>65</v>
@@ -8073,13 +8084,13 @@
         <v>33</v>
       </c>
       <c r="G58" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I58" t="s">
         <v>1076</v>
-      </c>
-      <c r="H58" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I58" t="s">
-        <v>1078</v>
       </c>
       <c r="J58" t="s">
         <v>50</v>
@@ -8108,19 +8119,19 @@
         <v>33</v>
       </c>
       <c r="G59" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I59" t="s">
         <v>1079</v>
       </c>
-      <c r="H59" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I59" t="s">
-        <v>1081</v>
-      </c>
       <c r="J59" t="s">
         <v>48</v>
       </c>
       <c r="K59" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -8143,13 +8154,13 @@
         <v>-200</v>
       </c>
       <c r="G60" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I60" t="s">
         <v>1082</v>
-      </c>
-      <c r="H60" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I60" t="s">
-        <v>1084</v>
       </c>
       <c r="J60" t="s">
         <v>54</v>
@@ -8175,10 +8186,10 @@
         <v>33</v>
       </c>
       <c r="H61" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I61" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="J61" t="s">
         <v>56</v>
@@ -8210,7 +8221,7 @@
         <v>45140</v>
       </c>
       <c r="H62" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I62" t="s">
         <v>48</v>
@@ -8242,16 +8253,16 @@
         <v>500</v>
       </c>
       <c r="G63" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I63" t="s">
         <v>1088</v>
       </c>
-      <c r="H63" t="s">
-        <v>1089</v>
-      </c>
-      <c r="I63" t="s">
-        <v>1090</v>
-      </c>
       <c r="J63" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K63" t="s">
         <v>67</v>
@@ -8274,16 +8285,16 @@
         <v>6500</v>
       </c>
       <c r="F64" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G64" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H64" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I64" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J64" t="s">
         <v>54</v>
@@ -8312,17 +8323,17 @@
         <v>33</v>
       </c>
       <c r="G65" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="H65" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I65">
         <f>974-6131-4658</f>
         <v>-9815</v>
       </c>
       <c r="J65" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -8345,7 +8356,7 @@
         <v>959</v>
       </c>
       <c r="G66" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="H66" t="s">
         <v>48</v>
@@ -8380,13 +8391,13 @@
         <v>750</v>
       </c>
       <c r="G67" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I67" t="s">
         <v>1096</v>
-      </c>
-      <c r="H67" t="s">
-        <v>1097</v>
-      </c>
-      <c r="I67" t="s">
-        <v>1098</v>
       </c>
       <c r="J67" t="s">
         <v>58</v>
@@ -8415,10 +8426,10 @@
         <v>500</v>
       </c>
       <c r="G68" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="H68" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I68" t="s">
         <v>50</v>
@@ -8450,10 +8461,10 @@
         <v>300</v>
       </c>
       <c r="G69" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="H69" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="I69">
         <v>49078072</v>
@@ -8488,10 +8499,10 @@
         <v>44270</v>
       </c>
       <c r="H70" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I70" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="J70" t="s">
         <v>56</v>
@@ -8523,13 +8534,13 @@
         <v>43599</v>
       </c>
       <c r="H71" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="I71" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="J71" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K71" t="s">
         <v>61</v>
@@ -8558,7 +8569,7 @@
         <v>48</v>
       </c>
       <c r="H72" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="I72">
         <f>974-4947-2658</f>
@@ -8585,22 +8596,22 @@
         <v>48</v>
       </c>
       <c r="F73" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G73" s="5">
         <v>44532</v>
       </c>
       <c r="H73" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I73" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="J73" t="s">
         <v>55</v>
       </c>
       <c r="K73" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -8620,16 +8631,16 @@
         <v>5250</v>
       </c>
       <c r="G74" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H74" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I74">
         <v>54004240</v>
       </c>
       <c r="J74" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K74" t="s">
         <v>68</v>
@@ -8658,7 +8669,7 @@
         <v>45376</v>
       </c>
       <c r="H75" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="I75" t="s">
         <v>48</v>
@@ -8687,22 +8698,22 @@
         <v>7200</v>
       </c>
       <c r="F76" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G76" s="5">
         <v>44237</v>
       </c>
       <c r="H76" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="I76" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="J76" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K76" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -8728,7 +8739,7 @@
         <v>45601</v>
       </c>
       <c r="H77" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="I77" t="s">
         <v>48</v>
@@ -8737,7 +8748,7 @@
         <v>48</v>
       </c>
       <c r="K77" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,7 +8771,7 @@
         <v>50</v>
       </c>
       <c r="H78" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="I78">
         <f>974-7015-9325</f>
@@ -8790,16 +8801,16 @@
         <v>6500</v>
       </c>
       <c r="F79" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G79" s="5">
         <v>45328</v>
       </c>
       <c r="H79" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I79" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="J79" t="s">
         <v>58</v>
@@ -8831,7 +8842,7 @@
         <v>45481</v>
       </c>
       <c r="H80" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="I80">
         <f>974-6366-4372</f>
@@ -8867,16 +8878,16 @@
         <v>44748</v>
       </c>
       <c r="H81" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="I81">
         <v>40965486</v>
       </c>
       <c r="J81" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K81" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -8902,7 +8913,7 @@
         <v>45575</v>
       </c>
       <c r="H82" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I82" t="s">
         <v>48</v>
@@ -8931,13 +8942,13 @@
         <v>5500</v>
       </c>
       <c r="F83" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G83" s="5">
         <v>44584</v>
       </c>
       <c r="H83" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="K83" t="s">
         <v>64</v>
@@ -8966,13 +8977,13 @@
         <v>44353</v>
       </c>
       <c r="H84" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="I84" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="J84" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K84" t="s">
         <v>61</v>
@@ -9001,16 +9012,16 @@
         <v>45208</v>
       </c>
       <c r="H85" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I85" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="J85" t="s">
         <v>54</v>
       </c>
       <c r="K85" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -9036,7 +9047,7 @@
         <v>44073</v>
       </c>
       <c r="H86" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="I86">
         <f>974-5655-8022</f>
@@ -9072,7 +9083,7 @@
         <v>45401</v>
       </c>
       <c r="H87" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="I87" t="s">
         <v>50</v>
@@ -9101,13 +9112,13 @@
         <v>7500</v>
       </c>
       <c r="F88" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G88" s="5">
         <v>44295</v>
       </c>
       <c r="H88" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="I88">
         <v>39045010</v>
@@ -9116,7 +9127,7 @@
         <v>60</v>
       </c>
       <c r="K88" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -9139,19 +9150,19 @@
         <v>300</v>
       </c>
       <c r="G89" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H89" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="I89" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J89" t="s">
         <v>59</v>
       </c>
       <c r="K89" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -9177,7 +9188,7 @@
         <v>43600</v>
       </c>
       <c r="H90" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="I90">
         <v>72753012</v>
@@ -9209,13 +9220,13 @@
         <v>48</v>
       </c>
       <c r="G91" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H91" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="I91" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="J91" t="s">
         <v>962</v>
@@ -9244,16 +9255,16 @@
         <v>48</v>
       </c>
       <c r="G92" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I92" t="s">
         <v>1134</v>
       </c>
-      <c r="H92" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I92" t="s">
-        <v>1136</v>
-      </c>
       <c r="J92" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K92" t="s">
         <v>48</v>
@@ -9279,16 +9290,16 @@
         <v>500</v>
       </c>
       <c r="G93" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I93" t="s">
         <v>1137</v>
       </c>
-      <c r="H93" t="s">
-        <v>1138</v>
-      </c>
-      <c r="I93" t="s">
-        <v>1139</v>
-      </c>
       <c r="J93" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K93" t="s">
         <v>62</v>
@@ -9317,7 +9328,7 @@
         <v>44414</v>
       </c>
       <c r="H94" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="I94">
         <v>76223632</v>
@@ -9326,7 +9337,7 @@
         <v>50</v>
       </c>
       <c r="K94" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -9349,16 +9360,16 @@
         <v>500</v>
       </c>
       <c r="G95" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H95" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="I95" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="J95" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K95" t="s">
         <v>64</v>
@@ -9387,10 +9398,10 @@
         <v>44113</v>
       </c>
       <c r="H96" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="I96" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="J96" t="s">
         <v>962</v>
@@ -9422,10 +9433,10 @@
         <v>43761</v>
       </c>
       <c r="H97" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="I97" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="K97" t="s">
         <v>63</v>
@@ -9454,7 +9465,7 @@
         <v>43466</v>
       </c>
       <c r="H98" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="I98">
         <v>71427428</v>
@@ -9486,16 +9497,16 @@
         <v>250</v>
       </c>
       <c r="G99" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I99" t="s">
         <v>1148</v>
       </c>
-      <c r="H99" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I99" t="s">
-        <v>1150</v>
-      </c>
       <c r="J99" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K99" t="s">
         <v>65</v>
@@ -9521,10 +9532,10 @@
         <v>750</v>
       </c>
       <c r="G100" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H100" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="I100">
         <v>63713553</v>
@@ -9556,13 +9567,13 @@
         <v>500</v>
       </c>
       <c r="G101" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I101" t="s">
         <v>1152</v>
-      </c>
-      <c r="H101" t="s">
-        <v>1153</v>
-      </c>
-      <c r="I101" t="s">
-        <v>1154</v>
       </c>
       <c r="J101" t="s">
         <v>50</v>
@@ -9594,7 +9605,7 @@
         <v>45471</v>
       </c>
       <c r="H102" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="I102">
         <f>974-7583-3609</f>
@@ -9627,10 +9638,10 @@
         <v>1000</v>
       </c>
       <c r="G103" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H103" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="I103" t="s">
         <v>50</v>
@@ -9659,13 +9670,13 @@
         <v>250</v>
       </c>
       <c r="G104" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I104" t="s">
         <v>1158</v>
-      </c>
-      <c r="H104" t="s">
-        <v>1159</v>
-      </c>
-      <c r="I104" t="s">
-        <v>1160</v>
       </c>
       <c r="J104" t="s">
         <v>60</v>
@@ -9691,19 +9702,19 @@
         <v>6000</v>
       </c>
       <c r="F105" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G105" s="5">
         <v>45043</v>
       </c>
       <c r="H105" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="I105" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="J105" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K105" t="s">
         <v>66</v>
@@ -9726,16 +9737,16 @@
         <v>48</v>
       </c>
       <c r="F106" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G106" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H106" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I106" t="s">
         <v>1164</v>
-      </c>
-      <c r="H106" t="s">
-        <v>1165</v>
-      </c>
-      <c r="I106" t="s">
-        <v>1166</v>
       </c>
       <c r="K106" t="s">
         <v>63</v>
@@ -9761,10 +9772,10 @@
         <v>500</v>
       </c>
       <c r="G107" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="H107" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="I107">
         <f>974-4077-6878</f>
@@ -9797,7 +9808,7 @@
         <v>500</v>
       </c>
       <c r="H108" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="I108">
         <f>974-7672-8067</f>
@@ -9827,16 +9838,16 @@
         <v>7000</v>
       </c>
       <c r="F109" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G109" s="5">
         <v>45509</v>
       </c>
       <c r="H109" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="I109" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="J109" t="s">
         <v>60</v>
@@ -9865,13 +9876,13 @@
         <v>1000</v>
       </c>
       <c r="G110" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H110" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I110" t="s">
         <v>1172</v>
-      </c>
-      <c r="H110" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I110" t="s">
-        <v>1174</v>
       </c>
       <c r="J110" t="s">
         <v>60</v>
@@ -9897,16 +9908,16 @@
         <v>6250</v>
       </c>
       <c r="F111" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G111" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H111" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I111" t="s">
         <v>1175</v>
-      </c>
-      <c r="H111" t="s">
-        <v>1176</v>
-      </c>
-      <c r="I111" t="s">
-        <v>1177</v>
       </c>
       <c r="J111" t="s">
         <v>57</v>
@@ -9938,7 +9949,7 @@
         <v>44633</v>
       </c>
       <c r="H112" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="I112">
         <f>974-3760-6321</f>
@@ -9974,13 +9985,13 @@
         <v>44060</v>
       </c>
       <c r="H113" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="I113" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="J113" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K113" t="s">
         <v>68</v>
@@ -10009,7 +10020,7 @@
         <v>50</v>
       </c>
       <c r="H114" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="I114">
         <v>55536448</v>
@@ -10044,10 +10055,10 @@
         <v>44646</v>
       </c>
       <c r="H115" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I115" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="J115" t="s">
         <v>48</v>
@@ -10073,16 +10084,16 @@
         <v>6500</v>
       </c>
       <c r="F116" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G116" s="5">
         <v>43971</v>
       </c>
       <c r="H116" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="I116" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J116" t="s">
         <v>60</v>
@@ -10111,13 +10122,13 @@
         <v>-200</v>
       </c>
       <c r="G117" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H117" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I117" t="s">
         <v>1186</v>
-      </c>
-      <c r="H117" t="s">
-        <v>1187</v>
-      </c>
-      <c r="I117" t="s">
-        <v>1188</v>
       </c>
       <c r="J117" t="s">
         <v>58</v>
@@ -10146,13 +10157,13 @@
         <v>500</v>
       </c>
       <c r="G118" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H118" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I118" t="s">
         <v>1189</v>
-      </c>
-      <c r="H118" t="s">
-        <v>1190</v>
-      </c>
-      <c r="I118" t="s">
-        <v>1191</v>
       </c>
       <c r="J118" t="s">
         <v>59</v>
@@ -10184,10 +10195,10 @@
         <v>44427</v>
       </c>
       <c r="H119" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="I119" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="J119" t="s">
         <v>59</v>
@@ -10219,10 +10230,10 @@
         <v>45601</v>
       </c>
       <c r="H120" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="I120" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="J120" t="s">
         <v>54</v>
@@ -10248,13 +10259,13 @@
         <v>6800</v>
       </c>
       <c r="F121" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G121" s="5">
         <v>45635</v>
       </c>
       <c r="H121" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="I121">
         <f>974-5371-2208</f>
@@ -10284,19 +10295,19 @@
         <v>5200</v>
       </c>
       <c r="F122" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G122" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H122" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I122" t="s">
         <v>1197</v>
       </c>
-      <c r="H122" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I122" t="s">
-        <v>1199</v>
-      </c>
       <c r="J122" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K122" t="s">
         <v>63</v>
@@ -10319,13 +10330,13 @@
         <v>48</v>
       </c>
       <c r="F123" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G123" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="H123" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="I123">
         <f>974-4609-2392</f>
@@ -10355,13 +10366,13 @@
         <v>9250</v>
       </c>
       <c r="F124" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G124" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="H124" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="I124">
         <v>33403055</v>
@@ -10396,7 +10407,7 @@
         <v>44502</v>
       </c>
       <c r="H125" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="I125">
         <v>52889387</v>
@@ -10405,7 +10416,7 @@
         <v>59</v>
       </c>
       <c r="K125" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -10431,14 +10442,14 @@
         <v>44508</v>
       </c>
       <c r="H126" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="I126">
         <f>974-6803-1824</f>
         <v>-7653</v>
       </c>
       <c r="K126" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -10461,10 +10472,10 @@
         <v>750</v>
       </c>
       <c r="G127" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="H127" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I127">
         <f>974-6419-2081</f>
@@ -10497,10 +10508,10 @@
         <v>1000</v>
       </c>
       <c r="G128" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H128" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="I128">
         <v>55162708</v>
@@ -10532,19 +10543,19 @@
         <v>963</v>
       </c>
       <c r="G129" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H129" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I129" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="J129" t="s">
         <v>50</v>
       </c>
       <c r="K129" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -10564,16 +10575,16 @@
         <v>6250</v>
       </c>
       <c r="F130" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G130" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H130" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I130" t="s">
         <v>1211</v>
-      </c>
-      <c r="H130" t="s">
-        <v>1212</v>
-      </c>
-      <c r="I130" t="s">
-        <v>1213</v>
       </c>
       <c r="J130" t="s">
         <v>58</v>
@@ -10602,7 +10613,7 @@
         <v>44708</v>
       </c>
       <c r="H131" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="I131">
         <v>50693119</v>
@@ -10611,7 +10622,7 @@
         <v>962</v>
       </c>
       <c r="K131" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -10637,7 +10648,7 @@
         <v>45611</v>
       </c>
       <c r="H132" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="I132">
         <v>97439437309</v>
@@ -10669,13 +10680,13 @@
         <v>500</v>
       </c>
       <c r="G133" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I133" t="s">
         <v>1216</v>
-      </c>
-      <c r="H133" t="s">
-        <v>1217</v>
-      </c>
-      <c r="I133" t="s">
-        <v>1218</v>
       </c>
       <c r="J133" t="s">
         <v>54</v>
@@ -10701,16 +10712,16 @@
         <v>7200</v>
       </c>
       <c r="F134" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G134" s="5">
         <v>44988</v>
       </c>
       <c r="H134" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="I134" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="J134" t="s">
         <v>56</v>
@@ -10736,22 +10747,22 @@
         <v>50</v>
       </c>
       <c r="F135" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G135" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="H135" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="I135">
         <v>51872293</v>
       </c>
       <c r="J135" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K135" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -10777,13 +10788,13 @@
         <v>44052</v>
       </c>
       <c r="H136" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="I136" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="J136" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K136" t="s">
         <v>61</v>
@@ -10809,10 +10820,10 @@
         <v>-200</v>
       </c>
       <c r="G137" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="H137" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="I137">
         <f>974-3175-6106</f>
@@ -10848,16 +10859,16 @@
         <v>43608</v>
       </c>
       <c r="H138" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="I138" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="J138" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K138" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -10880,13 +10891,13 @@
         <v>-200</v>
       </c>
       <c r="G139" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I139" t="s">
         <v>1229</v>
-      </c>
-      <c r="H139" t="s">
-        <v>1230</v>
-      </c>
-      <c r="I139" t="s">
-        <v>1231</v>
       </c>
       <c r="J139" t="s">
         <v>57</v>
@@ -10912,16 +10923,16 @@
         <v>4800</v>
       </c>
       <c r="F140" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G140" s="5">
         <v>44912</v>
       </c>
       <c r="H140" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="I140" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J140" t="s">
         <v>50</v>
@@ -10950,19 +10961,19 @@
         <v>500</v>
       </c>
       <c r="G141" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I141" t="s">
         <v>1233</v>
-      </c>
-      <c r="H141" t="s">
-        <v>1234</v>
-      </c>
-      <c r="I141" t="s">
-        <v>1235</v>
       </c>
       <c r="J141" t="s">
         <v>50</v>
       </c>
       <c r="K141" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -10982,16 +10993,16 @@
         <v>6500</v>
       </c>
       <c r="F142" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G142" s="5">
         <v>44042</v>
       </c>
       <c r="H142" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="I142" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="J142" t="s">
         <v>962</v>
@@ -11023,10 +11034,10 @@
         <v>45191</v>
       </c>
       <c r="H143" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="I143" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="J143" t="s">
         <v>57</v>
@@ -11058,10 +11069,10 @@
         <v>45119</v>
       </c>
       <c r="H144" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="I144" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="J144" t="s">
         <v>962</v>
@@ -11087,13 +11098,13 @@
         <v>5250</v>
       </c>
       <c r="F145" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G145" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="H145" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="I145">
         <f>974-7810-4322</f>
@@ -11126,16 +11137,16 @@
         <v>43656</v>
       </c>
       <c r="H146" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="I146" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="J146" t="s">
         <v>60</v>
       </c>
       <c r="K146" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -11155,10 +11166,10 @@
         <v>48</v>
       </c>
       <c r="G147" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="H147" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="I147">
         <v>123</v>
@@ -11187,22 +11198,22 @@
         <v>7750</v>
       </c>
       <c r="F148" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G148" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I148" t="s">
         <v>1247</v>
-      </c>
-      <c r="H148" t="s">
-        <v>1248</v>
-      </c>
-      <c r="I148" t="s">
-        <v>1249</v>
       </c>
       <c r="J148" t="s">
         <v>56</v>
       </c>
       <c r="K148" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -11228,10 +11239,10 @@
         <v>45564</v>
       </c>
       <c r="H149" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="I149" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="J149" t="s">
         <v>48</v>
@@ -11260,10 +11271,10 @@
         <v>750</v>
       </c>
       <c r="G150" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H150" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="I150">
         <v>123</v>
@@ -11295,14 +11306,14 @@
         <v>45354</v>
       </c>
       <c r="H151" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="I151">
         <f>974-4309-1345</f>
         <v>-4680</v>
       </c>
       <c r="J151" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K151" t="s">
         <v>66</v>
@@ -11328,13 +11339,13 @@
         <v>48</v>
       </c>
       <c r="G152" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I152" t="s">
         <v>1255</v>
-      </c>
-      <c r="H152" t="s">
-        <v>1256</v>
-      </c>
-      <c r="I152" t="s">
-        <v>1257</v>
       </c>
       <c r="J152" t="s">
         <v>58</v>
@@ -11360,16 +11371,16 @@
         <v>9000</v>
       </c>
       <c r="F153" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G153" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="H153" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="I153" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="J153" t="s">
         <v>57</v>
@@ -11401,10 +11412,10 @@
         <v>48</v>
       </c>
       <c r="H154" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="I154" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J154" t="s">
         <v>54</v>
@@ -11433,19 +11444,19 @@
         <v>250</v>
       </c>
       <c r="G155" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I155" t="s">
         <v>1261</v>
       </c>
-      <c r="H155" t="s">
-        <v>1262</v>
-      </c>
-      <c r="I155" t="s">
-        <v>1263</v>
-      </c>
       <c r="J155" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K155" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -11468,13 +11479,13 @@
         <v>500</v>
       </c>
       <c r="G156" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I156" t="s">
         <v>1264</v>
-      </c>
-      <c r="H156" t="s">
-        <v>1265</v>
-      </c>
-      <c r="I156" t="s">
-        <v>1266</v>
       </c>
       <c r="J156" t="s">
         <v>962</v>
@@ -11500,13 +11511,13 @@
         <v>8200</v>
       </c>
       <c r="F157" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G157" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H157" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="I157">
         <f>974-4119-5778</f>
@@ -11533,16 +11544,16 @@
         <v>5200</v>
       </c>
       <c r="F158" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G158" s="5">
         <v>43659</v>
       </c>
       <c r="H158" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="I158" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="J158" t="s">
         <v>58</v>
@@ -11568,16 +11579,16 @@
         <v>7000</v>
       </c>
       <c r="F159" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G159" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H159" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I159" t="s">
         <v>1271</v>
-      </c>
-      <c r="H159" t="s">
-        <v>1272</v>
-      </c>
-      <c r="I159" t="s">
-        <v>1273</v>
       </c>
       <c r="J159" t="s">
         <v>57</v>
@@ -11606,13 +11617,13 @@
         <v>750</v>
       </c>
       <c r="G160" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H160" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I160" t="s">
         <v>1274</v>
-      </c>
-      <c r="H160" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I160" t="s">
-        <v>1276</v>
       </c>
       <c r="J160" t="s">
         <v>56</v>
@@ -11644,16 +11655,16 @@
         <v>44451</v>
       </c>
       <c r="H161" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I161" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J161" t="s">
         <v>54</v>
       </c>
       <c r="K161" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -11679,10 +11690,10 @@
         <v>45632</v>
       </c>
       <c r="H162" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="I162" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="J162" t="s">
         <v>50</v>
@@ -11711,13 +11722,13 @@
         <v>48</v>
       </c>
       <c r="G163" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H163" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="I163" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J163" t="s">
         <v>57</v>
@@ -11743,13 +11754,13 @@
         <v>9500</v>
       </c>
       <c r="F164" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G164" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H164" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="I164">
         <v>47522591</v>
@@ -11781,7 +11792,7 @@
         <v>44053</v>
       </c>
       <c r="H165" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="I165">
         <f>974-3580-1261</f>
@@ -11811,16 +11822,16 @@
         <v>7200</v>
       </c>
       <c r="F166" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G166" t="s">
         <v>52</v>
       </c>
       <c r="H166" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="I166" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="J166" t="s">
         <v>50</v>
@@ -11843,13 +11854,13 @@
         <v>5000</v>
       </c>
       <c r="F167" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G167" s="5">
         <v>45624</v>
       </c>
       <c r="H167" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="I167" t="s">
         <v>48</v>
@@ -11884,13 +11895,13 @@
         <v>45100</v>
       </c>
       <c r="H168" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="I168" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J168" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K168" t="s">
         <v>63</v>
@@ -11913,22 +11924,22 @@
         <v>8200</v>
       </c>
       <c r="F169" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G169" s="5">
         <v>44014</v>
       </c>
       <c r="H169" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="I169" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="J169" t="s">
         <v>58</v>
       </c>
       <c r="K169" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -11951,10 +11962,10 @@
         <v>300</v>
       </c>
       <c r="G170" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="H170" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="I170">
         <f>974-6166-3886</f>
@@ -11987,17 +11998,17 @@
         <v>250</v>
       </c>
       <c r="G171" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="H171" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="I171">
         <f>974-4572-7261</f>
         <v>-10859</v>
       </c>
       <c r="J171" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K171" t="s">
         <v>48</v>
@@ -12023,19 +12034,19 @@
         <v>963</v>
       </c>
       <c r="G172" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H172" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I172" t="s">
         <v>1294</v>
-      </c>
-      <c r="H172" t="s">
-        <v>1295</v>
-      </c>
-      <c r="I172" t="s">
-        <v>1296</v>
       </c>
       <c r="J172" t="s">
         <v>57</v>
       </c>
       <c r="K172" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -12058,10 +12069,10 @@
         <v>48</v>
       </c>
       <c r="G173" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="H173" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="I173">
         <v>50139911</v>
@@ -12096,10 +12107,10 @@
         <v>51</v>
       </c>
       <c r="H174" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="I174" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J174" t="s">
         <v>54</v>
@@ -12131,7 +12142,7 @@
         <v>44912</v>
       </c>
       <c r="H175" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="I175">
         <f>974-3608-9364</f>
@@ -12164,13 +12175,13 @@
         <v>959</v>
       </c>
       <c r="G176" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I176" t="s">
         <v>1301</v>
-      </c>
-      <c r="H176" t="s">
-        <v>1302</v>
-      </c>
-      <c r="I176" t="s">
-        <v>1303</v>
       </c>
       <c r="J176" t="s">
         <v>58</v>
@@ -12202,10 +12213,10 @@
         <v>44842</v>
       </c>
       <c r="H177" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="I177" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="J177" t="s">
         <v>57</v>
@@ -12237,10 +12248,10 @@
         <v>44599</v>
       </c>
       <c r="H178" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="I178" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="J178" t="s">
         <v>57</v>
@@ -12269,10 +12280,10 @@
         <v>959</v>
       </c>
       <c r="G179" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="H179" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="I179">
         <f>974-5456-8226</f>
@@ -12282,7 +12293,7 @@
         <v>56</v>
       </c>
       <c r="K179" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -12308,13 +12319,13 @@
         <v>44141</v>
       </c>
       <c r="H180" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="I180">
         <v>75777958</v>
       </c>
       <c r="J180" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K180" t="s">
         <v>68</v>
@@ -12340,10 +12351,10 @@
         <v>500</v>
       </c>
       <c r="G181" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="H181" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="I181">
         <v>58625581</v>
@@ -12378,10 +12389,10 @@
         <v>45169</v>
       </c>
       <c r="H182" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="I182" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="J182" t="s">
         <v>60</v>
@@ -12413,10 +12424,10 @@
         <v>43648</v>
       </c>
       <c r="H183" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="I183" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="J183" t="s">
         <v>59</v>
@@ -12448,7 +12459,7 @@
         <v>45171</v>
       </c>
       <c r="H184" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="I184">
         <f>974-5084-8026</f>
@@ -12475,19 +12486,19 @@
         <v>5750</v>
       </c>
       <c r="F185" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G185" s="5">
         <v>43776</v>
       </c>
       <c r="H185" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="I185">
         <v>69196659</v>
       </c>
       <c r="J185" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K185" t="s">
         <v>66</v>
@@ -12510,13 +12521,13 @@
         <v>48</v>
       </c>
       <c r="F186" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G186" s="5">
         <v>45146</v>
       </c>
       <c r="H186" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I186">
         <v>77521639</v>
@@ -12545,7 +12556,7 @@
         <v>7500</v>
       </c>
       <c r="F187" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G187" s="5">
         <v>44113</v>
@@ -12586,10 +12597,10 @@
         <v>43575</v>
       </c>
       <c r="H188" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="I188" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="J188" t="s">
         <v>54</v>
@@ -12618,16 +12629,16 @@
         <v>1000</v>
       </c>
       <c r="G189" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="H189" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="I189" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J189" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K189" t="s">
         <v>66</v>
@@ -12653,13 +12664,13 @@
         <v>1000</v>
       </c>
       <c r="G190" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I190" t="s">
         <v>1324</v>
-      </c>
-      <c r="H190" t="s">
-        <v>1325</v>
-      </c>
-      <c r="I190" t="s">
-        <v>1326</v>
       </c>
       <c r="J190" t="s">
         <v>57</v>
@@ -12688,10 +12699,10 @@
         <v>250</v>
       </c>
       <c r="G191" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H191" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="I191">
         <v>39625089</v>
@@ -12723,10 +12734,10 @@
         <v>963</v>
       </c>
       <c r="G192" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H192" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="I192">
         <f>974-5065-5995</f>
@@ -12753,17 +12764,17 @@
         <v>4800</v>
       </c>
       <c r="G193" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="H193" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="I193">
         <f>974-6461-6902</f>
         <v>-12389</v>
       </c>
       <c r="J193" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K193" t="s">
         <v>62</v>
@@ -12792,10 +12803,10 @@
         <v>44758</v>
       </c>
       <c r="H194" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I194" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="J194" t="s">
         <v>54</v>
@@ -12821,19 +12832,19 @@
         <v>8000</v>
       </c>
       <c r="F195" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G195" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="H195" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="I195" t="s">
         <v>48</v>
       </c>
       <c r="J195" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K195" t="s">
         <v>62</v>
@@ -12859,10 +12870,10 @@
         <v>500</v>
       </c>
       <c r="G196" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="H196" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="I196">
         <f>974-3131-1256</f>
@@ -12895,19 +12906,19 @@
         <v>250</v>
       </c>
       <c r="G197" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="H197" t="s">
         <v>53</v>
       </c>
       <c r="I197" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="J197" t="s">
         <v>54</v>
       </c>
       <c r="K197" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -12933,7 +12944,7 @@
         <v>44657</v>
       </c>
       <c r="H198" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="I198">
         <f>974-3314-4764</f>
@@ -12966,13 +12977,13 @@
         <v>1000</v>
       </c>
       <c r="G199" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="H199" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="I199" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J199" t="s">
         <v>962</v>
@@ -13004,10 +13015,10 @@
         <v>44442</v>
       </c>
       <c r="H200" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="I200" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="J200" t="s">
         <v>58</v>
@@ -13039,10 +13050,10 @@
         <v>45463</v>
       </c>
       <c r="H201" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="I201" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="J201" t="s">
         <v>50</v>
@@ -13068,19 +13079,19 @@
         <v>9750</v>
       </c>
       <c r="F202" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G202" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I202" t="s">
         <v>1347</v>
       </c>
-      <c r="H202" t="s">
-        <v>1348</v>
-      </c>
-      <c r="I202" t="s">
-        <v>1349</v>
-      </c>
       <c r="J202" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K202" t="s">
         <v>66</v>
@@ -13106,13 +13117,13 @@
         <v>44893</v>
       </c>
       <c r="H203" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="I203" t="s">
         <v>50</v>
       </c>
       <c r="J203" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K203" t="s">
         <v>65</v>
@@ -13135,16 +13146,16 @@
         <v>-500</v>
       </c>
       <c r="F204" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G204" t="s">
         <v>50</v>
       </c>
       <c r="H204" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="I204" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="J204" t="s">
         <v>60</v>
@@ -13176,7 +13187,7 @@
         <v>43747</v>
       </c>
       <c r="H205" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="I205">
         <v>31292301</v>
@@ -13205,13 +13216,13 @@
         <v>50</v>
       </c>
       <c r="F206" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G206" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="H206" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="I206">
         <f>974-7039-6387</f>
@@ -13247,7 +13258,7 @@
         <v>44341</v>
       </c>
       <c r="H207" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="I207">
         <v>97453827852</v>
@@ -13279,13 +13290,13 @@
         <v>-200</v>
       </c>
       <c r="G208" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H208" t="s">
+        <v>1356</v>
+      </c>
+      <c r="I208" t="s">
         <v>1357</v>
-      </c>
-      <c r="H208" t="s">
-        <v>1358</v>
-      </c>
-      <c r="I208" t="s">
-        <v>1359</v>
       </c>
       <c r="J208" t="s">
         <v>56</v>
@@ -13314,13 +13325,13 @@
         <v>250</v>
       </c>
       <c r="G209" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I209" t="s">
         <v>1360</v>
-      </c>
-      <c r="H209" t="s">
-        <v>1361</v>
-      </c>
-      <c r="I209" t="s">
-        <v>1362</v>
       </c>
       <c r="K209" t="s">
         <v>67</v>
@@ -13346,10 +13357,10 @@
         <v>500</v>
       </c>
       <c r="G210" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="H210" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I210">
         <v>38586796</v>
@@ -13384,13 +13395,13 @@
         <v>45543</v>
       </c>
       <c r="H211" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="I211" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="J211" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K211" t="s">
         <v>62</v>
@@ -13419,10 +13430,10 @@
         <v>51</v>
       </c>
       <c r="H212" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="I212" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="J212" t="s">
         <v>54</v>
@@ -13454,10 +13465,10 @@
         <v>43851</v>
       </c>
       <c r="H213" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="I213" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J213" t="s">
         <v>58</v>
@@ -13483,16 +13494,16 @@
         <v>9000</v>
       </c>
       <c r="F214" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G214" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I214" t="s">
         <v>1369</v>
-      </c>
-      <c r="H214" t="s">
-        <v>1370</v>
-      </c>
-      <c r="I214" t="s">
-        <v>1371</v>
       </c>
       <c r="J214" t="s">
         <v>50</v>
@@ -13524,16 +13535,16 @@
         <v>44595</v>
       </c>
       <c r="H215" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="I215" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="J215" t="s">
         <v>56</v>
       </c>
       <c r="K215" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -13556,10 +13567,10 @@
         <v>250</v>
       </c>
       <c r="G216" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="H216" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="I216">
         <v>43116485</v>
@@ -13591,7 +13602,7 @@
         <v>44213</v>
       </c>
       <c r="H217" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="I217">
         <v>123</v>
@@ -13626,7 +13637,7 @@
         <v>53</v>
       </c>
       <c r="I218" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="J218" t="s">
         <v>962</v>
@@ -13658,7 +13669,7 @@
         <v>45265</v>
       </c>
       <c r="H219" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="I219">
         <v>76938400</v>
@@ -13693,10 +13704,10 @@
         <v>50</v>
       </c>
       <c r="H220" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="I220" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="J220" t="s">
         <v>60</v>
@@ -13722,16 +13733,16 @@
         <v>500</v>
       </c>
       <c r="G221" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H221" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I221" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="J221" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K221" t="s">
         <v>67</v>
@@ -13760,10 +13771,10 @@
         <v>44908</v>
       </c>
       <c r="H222" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="I222" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="J222" t="s">
         <v>48</v>
@@ -13795,7 +13806,7 @@
         <v>45386</v>
       </c>
       <c r="H223" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="I223">
         <v>32986153</v>
@@ -13824,19 +13835,19 @@
         <v>9500</v>
       </c>
       <c r="F224" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G224" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H224" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I224">
         <v>72548506</v>
       </c>
       <c r="J224" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K224" t="s">
         <v>65</v>
@@ -13862,13 +13873,13 @@
         <v>52</v>
       </c>
       <c r="H225" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="I225">
         <v>123</v>
       </c>
       <c r="J225" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K225" t="s">
         <v>66</v>
@@ -13897,10 +13908,10 @@
         <v>44169</v>
       </c>
       <c r="H226" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="I226" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="J226" t="s">
         <v>48</v>
@@ -13929,19 +13940,19 @@
         <v>750</v>
       </c>
       <c r="G227" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="H227" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="I227" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J227" t="s">
         <v>48</v>
       </c>
       <c r="K227" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -13967,7 +13978,7 @@
         <v>44473</v>
       </c>
       <c r="H228" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I228">
         <v>54135163</v>
@@ -14002,13 +14013,13 @@
         <v>44476</v>
       </c>
       <c r="H229" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="I229" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="J229" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K229" t="s">
         <v>50</v>
@@ -14037,13 +14048,13 @@
         <v>44217</v>
       </c>
       <c r="H230" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="I230">
         <v>97470245211</v>
       </c>
       <c r="J230" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K230" t="s">
         <v>62</v>
@@ -14069,10 +14080,10 @@
         <v>959</v>
       </c>
       <c r="G231" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="H231" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="I231">
         <f>974-4456-2027</f>
@@ -14102,16 +14113,16 @@
         <v>48</v>
       </c>
       <c r="F232" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G232" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I232" t="s">
         <v>1398</v>
-      </c>
-      <c r="H232" t="s">
-        <v>1399</v>
-      </c>
-      <c r="I232" t="s">
-        <v>1400</v>
       </c>
       <c r="J232" t="s">
         <v>59</v>
@@ -14140,13 +14151,13 @@
         <v>50</v>
       </c>
       <c r="G233" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I233" t="s">
         <v>1401</v>
-      </c>
-      <c r="H233" t="s">
-        <v>1402</v>
-      </c>
-      <c r="I233" t="s">
-        <v>1403</v>
       </c>
       <c r="J233" t="s">
         <v>48</v>
@@ -14178,7 +14189,7 @@
         <v>44933</v>
       </c>
       <c r="H234" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I234">
         <v>54114963</v>
@@ -14187,7 +14198,7 @@
         <v>56</v>
       </c>
       <c r="K234" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14210,16 +14221,16 @@
         <v>500</v>
       </c>
       <c r="G235" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1403</v>
+      </c>
+      <c r="I235" t="s">
         <v>1404</v>
       </c>
-      <c r="H235" t="s">
-        <v>1405</v>
-      </c>
-      <c r="I235" t="s">
-        <v>1406</v>
-      </c>
       <c r="J235" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -14242,10 +14253,10 @@
         <v>48</v>
       </c>
       <c r="G236" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H236" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="I236">
         <v>53091256</v>
@@ -14280,10 +14291,10 @@
         <v>45646</v>
       </c>
       <c r="H237" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="I237" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="J237" t="s">
         <v>57</v>
@@ -14315,13 +14326,13 @@
         <v>44998</v>
       </c>
       <c r="H238" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="I238" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J238" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K238" t="s">
         <v>67</v>
@@ -14344,16 +14355,16 @@
         <v>-1000</v>
       </c>
       <c r="F239" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G239" s="5">
         <v>43862</v>
       </c>
       <c r="H239" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="I239" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="J239" t="s">
         <v>54</v>
@@ -14382,13 +14393,13 @@
         <v>750</v>
       </c>
       <c r="G240" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H240" t="s">
+        <v>1412</v>
+      </c>
+      <c r="I240" t="s">
         <v>1413</v>
-      </c>
-      <c r="H240" t="s">
-        <v>1414</v>
-      </c>
-      <c r="I240" t="s">
-        <v>1415</v>
       </c>
       <c r="J240" t="s">
         <v>962</v>
@@ -14414,16 +14425,16 @@
         <v>6000</v>
       </c>
       <c r="F241" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G241" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H241" t="s">
+        <v>1415</v>
+      </c>
+      <c r="I241" t="s">
         <v>1416</v>
-      </c>
-      <c r="H241" t="s">
-        <v>1417</v>
-      </c>
-      <c r="I241" t="s">
-        <v>1418</v>
       </c>
       <c r="J241" t="s">
         <v>54</v>
@@ -14452,10 +14463,10 @@
         <v>50</v>
       </c>
       <c r="G242" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="H242" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I242">
         <v>74363062</v>
@@ -14487,19 +14498,19 @@
         <v>33</v>
       </c>
       <c r="G243" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H243" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="I243">
         <v>77639313</v>
       </c>
       <c r="J243" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K243" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -14522,19 +14533,19 @@
         <v>250</v>
       </c>
       <c r="G244" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H244" t="s">
+        <v>1422</v>
+      </c>
+      <c r="I244" t="s">
         <v>1423</v>
-      </c>
-      <c r="H244" t="s">
-        <v>1424</v>
-      </c>
-      <c r="I244" t="s">
-        <v>1425</v>
       </c>
       <c r="J244" t="s">
         <v>54</v>
       </c>
       <c r="K244" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -14560,7 +14571,7 @@
         <v>45429</v>
       </c>
       <c r="H245" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I245">
         <v>49557645</v>
@@ -14592,19 +14603,19 @@
         <v>750</v>
       </c>
       <c r="G246" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H246" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="I246" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="J246" t="s">
         <v>48</v>
       </c>
       <c r="K246" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -14630,13 +14641,13 @@
         <v>45082</v>
       </c>
       <c r="H247" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I247">
         <v>52368330</v>
       </c>
       <c r="J247" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K247" t="s">
         <v>65</v>
@@ -14662,19 +14673,19 @@
         <v>500</v>
       </c>
       <c r="G248" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H248" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I248" t="s">
         <v>1428</v>
-      </c>
-      <c r="H248" t="s">
-        <v>1429</v>
-      </c>
-      <c r="I248" t="s">
-        <v>1430</v>
       </c>
       <c r="J248" t="s">
         <v>58</v>
       </c>
       <c r="K248" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -14697,13 +14708,13 @@
         <v>1000</v>
       </c>
       <c r="G249" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H249" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I249" t="s">
         <v>1431</v>
-      </c>
-      <c r="H249" t="s">
-        <v>1432</v>
-      </c>
-      <c r="I249" t="s">
-        <v>1433</v>
       </c>
       <c r="J249" t="s">
         <v>59</v>
@@ -14735,7 +14746,7 @@
         <v>44303</v>
       </c>
       <c r="H250" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="I250">
         <v>59667239</v>
@@ -14764,10 +14775,10 @@
         <v>45270</v>
       </c>
       <c r="H251" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I251" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J251" t="s">
         <v>962</v>
@@ -14796,13 +14807,13 @@
         <v>750</v>
       </c>
       <c r="G252" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I252" t="s">
         <v>1435</v>
-      </c>
-      <c r="H252" t="s">
-        <v>1436</v>
-      </c>
-      <c r="I252" t="s">
-        <v>1437</v>
       </c>
       <c r="J252" t="s">
         <v>57</v>
@@ -14831,10 +14842,10 @@
         <v>1000</v>
       </c>
       <c r="G253" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="H253" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I253">
         <f>974-3880-9712</f>
@@ -14870,7 +14881,7 @@
         <v>43784</v>
       </c>
       <c r="H254" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="I254">
         <f>974-4292-8120</f>
@@ -14880,7 +14891,7 @@
         <v>57</v>
       </c>
       <c r="K254" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -14903,13 +14914,13 @@
         <v>500</v>
       </c>
       <c r="G255" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H255" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="I255" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="J255" t="s">
         <v>50</v>
@@ -14938,7 +14949,7 @@
         <v>45360</v>
       </c>
       <c r="H256" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I256">
         <f>974-7936-8102</f>
@@ -14948,7 +14959,7 @@
         <v>48</v>
       </c>
       <c r="K256" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -14974,7 +14985,7 @@
         <v>44737</v>
       </c>
       <c r="H257" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="I257">
         <v>32757896</v>
@@ -15006,10 +15017,10 @@
         <v>1250</v>
       </c>
       <c r="G258" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="H258" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="I258">
         <f>974-4989-5430</f>
@@ -15042,13 +15053,13 @@
         <v>1250</v>
       </c>
       <c r="G259" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I259" t="s">
         <v>1446</v>
-      </c>
-      <c r="H259" t="s">
-        <v>1447</v>
-      </c>
-      <c r="I259" t="s">
-        <v>1448</v>
       </c>
       <c r="J259" t="s">
         <v>60</v>
@@ -15074,13 +15085,13 @@
         <v>4500</v>
       </c>
       <c r="F260" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G260" s="5">
         <v>44788</v>
       </c>
       <c r="H260" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="I260">
         <v>63099241</v>
@@ -15089,7 +15100,7 @@
         <v>58</v>
       </c>
       <c r="K260" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -15115,16 +15126,16 @@
         <v>44262</v>
       </c>
       <c r="H261" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="I261" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="J261" t="s">
         <v>55</v>
       </c>
       <c r="K261" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -15150,10 +15161,10 @@
         <v>43521</v>
       </c>
       <c r="H262" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="I262" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="J262" t="s">
         <v>55</v>
@@ -15179,20 +15190,20 @@
         <v>9250</v>
       </c>
       <c r="F263" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G263" s="5">
         <v>44575</v>
       </c>
       <c r="H263" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I263">
         <f>974-6773-4327</f>
         <v>-10126</v>
       </c>
       <c r="J263" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K263" t="s">
         <v>61</v>
@@ -15221,7 +15232,7 @@
         <v>44601</v>
       </c>
       <c r="H264" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="I264" t="s">
         <v>50</v>
@@ -15256,10 +15267,10 @@
         <v>44790</v>
       </c>
       <c r="H265" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="I265" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="J265" t="s">
         <v>48</v>
@@ -15291,7 +15302,7 @@
         <v>44638</v>
       </c>
       <c r="H266" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="I266">
         <v>35756752</v>
@@ -15300,7 +15311,7 @@
         <v>57</v>
       </c>
       <c r="K266" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -15326,10 +15337,10 @@
         <v>43857</v>
       </c>
       <c r="H267" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="I267" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="J267" t="s">
         <v>962</v>
@@ -15361,13 +15372,13 @@
         <v>45657</v>
       </c>
       <c r="H268" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="I268" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="J268" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K268" t="s">
         <v>65</v>
@@ -15393,13 +15404,13 @@
         <v>963</v>
       </c>
       <c r="G269" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H269" t="s">
+        <v>1461</v>
+      </c>
+      <c r="I269" t="s">
         <v>1462</v>
-      </c>
-      <c r="H269" t="s">
-        <v>1463</v>
-      </c>
-      <c r="I269" t="s">
-        <v>1464</v>
       </c>
       <c r="J269" t="s">
         <v>56</v>
@@ -15425,16 +15436,16 @@
         <v>6200</v>
       </c>
       <c r="F270" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G270" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H270" t="s">
+        <v>1464</v>
+      </c>
+      <c r="I270" t="s">
         <v>1465</v>
-      </c>
-      <c r="H270" t="s">
-        <v>1466</v>
-      </c>
-      <c r="I270" t="s">
-        <v>1467</v>
       </c>
       <c r="J270" t="s">
         <v>54</v>
@@ -15463,16 +15474,16 @@
         <v>43877</v>
       </c>
       <c r="H271" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="I271" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="J271" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K271" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -15498,7 +15509,7 @@
         <v>44169</v>
       </c>
       <c r="H272" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="I272">
         <f>974-5072-9970</f>
@@ -15525,13 +15536,13 @@
         <v>50</v>
       </c>
       <c r="F273" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G273" s="5">
         <v>44174</v>
       </c>
       <c r="H273" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="I273">
         <v>54401379</v>
@@ -15563,13 +15574,13 @@
         <v>250</v>
       </c>
       <c r="G274" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H274" t="s">
+        <v>1471</v>
+      </c>
+      <c r="I274" t="s">
         <v>1472</v>
-      </c>
-      <c r="H274" t="s">
-        <v>1473</v>
-      </c>
-      <c r="I274" t="s">
-        <v>1474</v>
       </c>
       <c r="J274" t="s">
         <v>54</v>
@@ -15601,7 +15612,7 @@
         <v>44661</v>
       </c>
       <c r="H275" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="I275">
         <v>123</v>
@@ -15633,10 +15644,10 @@
         <v>500</v>
       </c>
       <c r="G276" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="H276" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="I276">
         <v>51327897</v>
@@ -15671,10 +15682,10 @@
         <v>43818</v>
       </c>
       <c r="H277" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="I277" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="J277" t="s">
         <v>59</v>
@@ -15706,10 +15717,10 @@
         <v>48</v>
       </c>
       <c r="H278" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="I278" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="J278" t="s">
         <v>962</v>
@@ -15738,10 +15749,10 @@
         <v>750</v>
       </c>
       <c r="G279" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="H279" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="I279">
         <f>974-5928-9165</f>
@@ -15751,7 +15762,7 @@
         <v>56</v>
       </c>
       <c r="K279" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -15777,16 +15788,16 @@
         <v>45037</v>
       </c>
       <c r="H280" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I280" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="J280" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K280" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15809,16 +15820,16 @@
         <v>-50</v>
       </c>
       <c r="G281" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H281" t="s">
+        <v>1483</v>
+      </c>
+      <c r="I281" t="s">
         <v>1484</v>
       </c>
-      <c r="H281" t="s">
-        <v>1485</v>
-      </c>
-      <c r="I281" t="s">
-        <v>1486</v>
-      </c>
       <c r="J281" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K281" t="s">
         <v>61</v>
@@ -15847,16 +15858,16 @@
         <v>44907</v>
       </c>
       <c r="H282" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="I282" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="J282" t="s">
         <v>57</v>
       </c>
       <c r="K282" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -15882,10 +15893,10 @@
         <v>44930</v>
       </c>
       <c r="H283" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="I283" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="J283" t="s">
         <v>50</v>
@@ -15914,10 +15925,10 @@
         <v>250</v>
       </c>
       <c r="G284" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="H284" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="I284">
         <v>45342016</v>
@@ -15952,10 +15963,10 @@
         <v>45146</v>
       </c>
       <c r="H285" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="I285" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="J285" t="s">
         <v>55</v>
@@ -15981,19 +15992,19 @@
         <v>8200</v>
       </c>
       <c r="F286" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G286" s="5">
         <v>45524</v>
       </c>
       <c r="H286" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="I286">
         <v>97467633435</v>
       </c>
       <c r="J286" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K286" t="s">
         <v>64</v>
@@ -16019,10 +16030,10 @@
         <v>750</v>
       </c>
       <c r="G287" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="H287" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="I287">
         <v>97431287667</v>
@@ -16057,10 +16068,10 @@
         <v>43500</v>
       </c>
       <c r="H288" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="I288" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="K288" t="s">
         <v>64</v>
@@ -16086,10 +16097,10 @@
         <v>43779</v>
       </c>
       <c r="H289" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="I289" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="J289" t="s">
         <v>55</v>
@@ -16118,10 +16129,10 @@
         <v>250</v>
       </c>
       <c r="G290" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="H290" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="I290">
         <v>58222967</v>
@@ -16150,10 +16161,10 @@
         <v>7500</v>
       </c>
       <c r="F291" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H291" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="I291">
         <f>974-4824-9133</f>
@@ -16186,7 +16197,7 @@
         <v>48</v>
       </c>
       <c r="H292" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="I292">
         <v>46505336</v>
@@ -16218,10 +16229,10 @@
         <v>0</v>
       </c>
       <c r="G293" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="H293" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="I293">
         <f>974-3886-1007</f>
@@ -16257,13 +16268,13 @@
         <v>44249</v>
       </c>
       <c r="H294" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="I294" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="J294" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K294" t="s">
         <v>48</v>
@@ -16292,7 +16303,7 @@
         <v>44463</v>
       </c>
       <c r="H295" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="I295">
         <v>123</v>
@@ -16324,13 +16335,13 @@
         <v>963</v>
       </c>
       <c r="G296" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="H296" t="s">
         <v>53</v>
       </c>
       <c r="I296" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="J296" t="s">
         <v>58</v>
@@ -16359,16 +16370,16 @@
         <v>959</v>
       </c>
       <c r="G297" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="H297" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="I297">
         <v>62509971</v>
       </c>
       <c r="J297" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K297" t="s">
         <v>66</v>
@@ -16391,16 +16402,16 @@
         <v>48</v>
       </c>
       <c r="F298" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G298" t="s">
+        <v>1512</v>
+      </c>
+      <c r="H298" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I298" t="s">
         <v>1514</v>
-      </c>
-      <c r="H298" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I298" t="s">
-        <v>1516</v>
       </c>
       <c r="J298" t="s">
         <v>962</v>
@@ -16432,10 +16443,10 @@
         <v>44997</v>
       </c>
       <c r="H299" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="I299" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="J299" t="s">
         <v>962</v>
@@ -16464,16 +16475,16 @@
         <v>250</v>
       </c>
       <c r="G300" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H300" t="s">
+        <v>1518</v>
+      </c>
+      <c r="I300" t="s">
         <v>1519</v>
       </c>
-      <c r="H300" t="s">
-        <v>1520</v>
-      </c>
-      <c r="I300" t="s">
-        <v>1521</v>
-      </c>
       <c r="J300" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K300" t="s">
         <v>50</v>
@@ -16499,10 +16510,10 @@
         <v>44166</v>
       </c>
       <c r="H301" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="I301" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="J301" t="s">
         <v>60</v>
@@ -16531,10 +16542,10 @@
         <v>44630</v>
       </c>
       <c r="H302" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="I302" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="K302" t="s">
         <v>61</v>
@@ -16557,13 +16568,13 @@
         <v>8000</v>
       </c>
       <c r="F303" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G303" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="H303" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="I303" t="s">
         <v>50</v>
@@ -16595,13 +16606,13 @@
         <v>-200</v>
       </c>
       <c r="G304" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H304" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I304" t="s">
         <v>1527</v>
-      </c>
-      <c r="H304" t="s">
-        <v>1528</v>
-      </c>
-      <c r="I304" t="s">
-        <v>1529</v>
       </c>
       <c r="K304" t="s">
         <v>68</v>
@@ -16624,16 +16635,16 @@
         <v>48</v>
       </c>
       <c r="F305" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G305" s="5">
         <v>45297</v>
       </c>
       <c r="H305" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="I305" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="J305" t="s">
         <v>56</v>
@@ -16659,16 +16670,16 @@
         <v>6500</v>
       </c>
       <c r="F306" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G306" s="5">
         <v>44459</v>
       </c>
       <c r="H306" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="I306" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="J306" t="s">
         <v>58</v>
@@ -16697,13 +16708,13 @@
         <v>750</v>
       </c>
       <c r="G307" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H307" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I307" t="s">
         <v>1534</v>
-      </c>
-      <c r="H307" t="s">
-        <v>1535</v>
-      </c>
-      <c r="I307" t="s">
-        <v>1536</v>
       </c>
       <c r="J307" t="s">
         <v>57</v>
@@ -16732,16 +16743,16 @@
         <v>500</v>
       </c>
       <c r="G308" t="s">
+        <v>1535</v>
+      </c>
+      <c r="H308" t="s">
+        <v>1536</v>
+      </c>
+      <c r="I308" t="s">
         <v>1537</v>
       </c>
-      <c r="H308" t="s">
-        <v>1538</v>
-      </c>
-      <c r="I308" t="s">
-        <v>1539</v>
-      </c>
       <c r="J308" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K308" t="s">
         <v>63</v>
@@ -16767,13 +16778,13 @@
         <v>500</v>
       </c>
       <c r="G309" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1539</v>
+      </c>
+      <c r="I309" t="s">
         <v>1540</v>
-      </c>
-      <c r="H309" t="s">
-        <v>1541</v>
-      </c>
-      <c r="I309" t="s">
-        <v>1542</v>
       </c>
       <c r="J309" t="s">
         <v>58</v>
@@ -16802,13 +16813,13 @@
         <v>250</v>
       </c>
       <c r="G310" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H310" t="s">
+        <v>1542</v>
+      </c>
+      <c r="I310" t="s">
         <v>1543</v>
-      </c>
-      <c r="H310" t="s">
-        <v>1544</v>
-      </c>
-      <c r="I310" t="s">
-        <v>1545</v>
       </c>
       <c r="J310" t="s">
         <v>55</v>
@@ -16840,16 +16851,16 @@
         <v>45018</v>
       </c>
       <c r="H311" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="I311" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J311" t="s">
         <v>59</v>
       </c>
       <c r="K311" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -16875,10 +16886,10 @@
         <v>43600</v>
       </c>
       <c r="H312" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="I312" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="J312" t="s">
         <v>57</v>
@@ -16907,13 +16918,13 @@
         <v>33</v>
       </c>
       <c r="G313" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H313" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I313" t="s">
         <v>1549</v>
-      </c>
-      <c r="H313" t="s">
-        <v>1550</v>
-      </c>
-      <c r="I313" t="s">
-        <v>1551</v>
       </c>
       <c r="J313" t="s">
         <v>56</v>
@@ -16945,14 +16956,14 @@
         <v>48</v>
       </c>
       <c r="H314" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="I314">
         <f>974-7708-5518</f>
         <v>-12252</v>
       </c>
       <c r="J314" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K314" t="s">
         <v>63</v>
@@ -16981,10 +16992,10 @@
         <v>44933</v>
       </c>
       <c r="H315" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="I315" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="J315" t="s">
         <v>54</v>
@@ -17016,10 +17027,10 @@
         <v>44792</v>
       </c>
       <c r="H316" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="I316" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="J316" t="s">
         <v>54</v>
@@ -17048,16 +17059,16 @@
         <v>750</v>
       </c>
       <c r="G317" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H317" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I317" t="s">
         <v>1557</v>
       </c>
-      <c r="H317" t="s">
-        <v>1558</v>
-      </c>
-      <c r="I317" t="s">
-        <v>1559</v>
-      </c>
       <c r="J317" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K317" t="s">
         <v>61</v>
@@ -17080,16 +17091,16 @@
         <v>7200</v>
       </c>
       <c r="F318" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G318" s="5">
         <v>44764</v>
       </c>
       <c r="H318" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="I318" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="J318" t="s">
         <v>54</v>
@@ -17148,16 +17159,16 @@
         <v>48</v>
       </c>
       <c r="F320" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G320" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H320" t="s">
+        <v>1561</v>
+      </c>
+      <c r="I320" t="s">
         <v>1562</v>
-      </c>
-      <c r="H320" t="s">
-        <v>1563</v>
-      </c>
-      <c r="I320" t="s">
-        <v>1564</v>
       </c>
       <c r="J320" t="s">
         <v>58</v>
@@ -17189,10 +17200,10 @@
         <v>43984</v>
       </c>
       <c r="H321" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="I321" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J321" t="s">
         <v>48</v>
@@ -17221,10 +17232,10 @@
         <v>45021</v>
       </c>
       <c r="H322" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I322" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="J322" t="s">
         <v>54</v>
@@ -17253,13 +17264,13 @@
         <v>-200</v>
       </c>
       <c r="G323" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H323" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I323" t="s">
         <v>1569</v>
-      </c>
-      <c r="H323" t="s">
-        <v>1570</v>
-      </c>
-      <c r="I323" t="s">
-        <v>1571</v>
       </c>
       <c r="J323" t="s">
         <v>48</v>
@@ -17288,19 +17299,19 @@
         <v>33</v>
       </c>
       <c r="G324" t="s">
+        <v>1570</v>
+      </c>
+      <c r="H324" t="s">
+        <v>1571</v>
+      </c>
+      <c r="I324" t="s">
         <v>1572</v>
-      </c>
-      <c r="H324" t="s">
-        <v>1573</v>
-      </c>
-      <c r="I324" t="s">
-        <v>1574</v>
       </c>
       <c r="J324" t="s">
         <v>50</v>
       </c>
       <c r="K324" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -17326,7 +17337,7 @@
         <v>44364</v>
       </c>
       <c r="H325" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="I325">
         <v>78411507</v>
@@ -17361,10 +17372,10 @@
         <v>44006</v>
       </c>
       <c r="H326" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="I326" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="K326" t="s">
         <v>66</v>
@@ -17393,7 +17404,7 @@
         <v>44502</v>
       </c>
       <c r="H327" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I327">
         <f>974-7898-3252</f>
@@ -17426,10 +17437,10 @@
         <v>48</v>
       </c>
       <c r="G328" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H328" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I328">
         <f>974-6757-6707</f>
@@ -17462,10 +17473,10 @@
         <v>33</v>
       </c>
       <c r="G329" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H329" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I329">
         <v>79028490</v>
@@ -17497,10 +17508,10 @@
         <v>44318</v>
       </c>
       <c r="H330" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="I330" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="K330" t="s">
         <v>64</v>
@@ -17529,13 +17540,13 @@
         <v>44806</v>
       </c>
       <c r="H331" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="I331">
         <v>34118386</v>
       </c>
       <c r="J331" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K331" t="s">
         <v>67</v>
@@ -17561,16 +17572,16 @@
         <v>0</v>
       </c>
       <c r="G332" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="H332" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="I332">
         <v>65753074</v>
       </c>
       <c r="J332" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K332" t="s">
         <v>67</v>
@@ -17599,13 +17610,13 @@
         <v>43482</v>
       </c>
       <c r="H333" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="I333">
         <v>36442559</v>
       </c>
       <c r="J333" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K333" t="s">
         <v>63</v>
@@ -17631,13 +17642,13 @@
         <v>250</v>
       </c>
       <c r="G334" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H334" t="s">
+        <v>1587</v>
+      </c>
+      <c r="I334" t="s">
         <v>1588</v>
-      </c>
-      <c r="H334" t="s">
-        <v>1589</v>
-      </c>
-      <c r="I334" t="s">
-        <v>1590</v>
       </c>
       <c r="J334" t="s">
         <v>58</v>
@@ -17663,16 +17674,16 @@
         <v>8250</v>
       </c>
       <c r="G335" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="H335" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="I335" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J335" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
@@ -17695,16 +17706,16 @@
         <v>250</v>
       </c>
       <c r="G336" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H336" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I336" t="s">
         <v>1593</v>
       </c>
-      <c r="H336" t="s">
-        <v>1594</v>
-      </c>
-      <c r="I336" t="s">
-        <v>1595</v>
-      </c>
       <c r="J336" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K336" t="s">
         <v>67</v>
@@ -17730,13 +17741,13 @@
         <v>750</v>
       </c>
       <c r="G337" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H337" t="s">
+        <v>1595</v>
+      </c>
+      <c r="I337" t="s">
         <v>1596</v>
-      </c>
-      <c r="H337" t="s">
-        <v>1597</v>
-      </c>
-      <c r="I337" t="s">
-        <v>1598</v>
       </c>
       <c r="J337" t="s">
         <v>48</v>
@@ -17765,13 +17776,13 @@
         <v>500</v>
       </c>
       <c r="G338" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H338" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I338" t="s">
         <v>1599</v>
-      </c>
-      <c r="H338" t="s">
-        <v>1600</v>
-      </c>
-      <c r="I338" t="s">
-        <v>1601</v>
       </c>
       <c r="J338" t="s">
         <v>54</v>
@@ -17800,7 +17811,7 @@
         <v>44532</v>
       </c>
       <c r="H339" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I339">
         <f>974-6012-1457</f>
@@ -17827,16 +17838,16 @@
         <v>6800</v>
       </c>
       <c r="G340" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H340" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="I340">
         <v>50104092</v>
       </c>
       <c r="J340" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -17859,13 +17870,13 @@
         <v>-50</v>
       </c>
       <c r="G341" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H341" t="s">
+        <v>1604</v>
+      </c>
+      <c r="I341" t="s">
         <v>1605</v>
-      </c>
-      <c r="H341" t="s">
-        <v>1606</v>
-      </c>
-      <c r="I341" t="s">
-        <v>1607</v>
       </c>
       <c r="J341" t="s">
         <v>56</v>
@@ -17891,13 +17902,13 @@
         <v>5200</v>
       </c>
       <c r="G342" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H342" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="I342" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="J342" t="s">
         <v>60</v>
@@ -17929,7 +17940,7 @@
         <v>44848</v>
       </c>
       <c r="H343" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I343">
         <f>974-6844-1087</f>
@@ -17956,13 +17967,13 @@
         <v>6500</v>
       </c>
       <c r="F344" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G344" s="5">
         <v>45504</v>
       </c>
       <c r="H344" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="I344">
         <f>974-6536-4904</f>
@@ -17995,16 +18006,16 @@
         <v>500</v>
       </c>
       <c r="G345" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H345" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I345" t="s">
         <v>1612</v>
       </c>
-      <c r="H345" t="s">
-        <v>1613</v>
-      </c>
-      <c r="I345" t="s">
-        <v>1614</v>
-      </c>
       <c r="J345" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K345" t="s">
         <v>48</v>
@@ -18030,13 +18041,13 @@
         <v>45170</v>
       </c>
       <c r="H346" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I346" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J346" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K346" t="s">
         <v>66</v>
@@ -18065,10 +18076,10 @@
         <v>44192</v>
       </c>
       <c r="H347" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I347" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="J347" t="s">
         <v>50</v>
@@ -18100,13 +18111,13 @@
         <v>44323</v>
       </c>
       <c r="H348" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="I348" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J348" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K348" t="s">
         <v>66</v>
@@ -18135,7 +18146,7 @@
         <v>45390</v>
       </c>
       <c r="H349" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="I349">
         <v>37195965</v>
@@ -18167,13 +18178,13 @@
         <v>48</v>
       </c>
       <c r="G350" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="H350" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="J350" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K350" t="s">
         <v>68</v>
@@ -18199,16 +18210,16 @@
         <v>959</v>
       </c>
       <c r="G351" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="H351" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="I351" t="s">
         <v>50</v>
       </c>
       <c r="J351" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K351" t="s">
         <v>61</v>
@@ -18231,19 +18242,19 @@
         <v>6500</v>
       </c>
       <c r="F352" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G352" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="H352" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="I352">
         <v>50079469</v>
       </c>
       <c r="J352" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K352" t="s">
         <v>67</v>
@@ -18272,10 +18283,10 @@
         <v>51</v>
       </c>
       <c r="I353" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="J353" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K353" t="s">
         <v>50</v>
@@ -18301,13 +18312,13 @@
         <v>750</v>
       </c>
       <c r="G354" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H354" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I354" t="s">
         <v>1627</v>
-      </c>
-      <c r="H354" t="s">
-        <v>1628</v>
-      </c>
-      <c r="I354" t="s">
-        <v>1629</v>
       </c>
       <c r="J354" t="s">
         <v>50</v>
@@ -18336,13 +18347,13 @@
         <v>44317</v>
       </c>
       <c r="H355" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="I355">
         <v>123</v>
       </c>
       <c r="J355" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K355" t="s">
         <v>50</v>
@@ -18374,10 +18385,10 @@
         <v>50</v>
       </c>
       <c r="I356" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="J356" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K356" t="s">
         <v>64</v>
@@ -18403,19 +18414,19 @@
         <v>48</v>
       </c>
       <c r="G357" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H357" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I357" t="s">
         <v>1632</v>
-      </c>
-      <c r="H357" t="s">
-        <v>1633</v>
-      </c>
-      <c r="I357" t="s">
-        <v>1634</v>
       </c>
       <c r="J357" t="s">
         <v>58</v>
       </c>
       <c r="K357" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
@@ -18438,13 +18449,13 @@
         <v>33</v>
       </c>
       <c r="G358" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H358" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I358" t="s">
         <v>1635</v>
-      </c>
-      <c r="H358" t="s">
-        <v>1636</v>
-      </c>
-      <c r="I358" t="s">
-        <v>1637</v>
       </c>
       <c r="J358" t="s">
         <v>50</v>
@@ -18470,7 +18481,7 @@
         <v>959</v>
       </c>
       <c r="H359" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="I359">
         <v>51814301</v>
@@ -18499,16 +18510,16 @@
         <v>50</v>
       </c>
       <c r="F360" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G360" s="5">
         <v>44783</v>
       </c>
       <c r="H360" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="I360" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="J360" t="s">
         <v>54</v>
@@ -18534,10 +18545,10 @@
         <v>45447</v>
       </c>
       <c r="H361" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="I361" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="J361" t="s">
         <v>962</v>
@@ -18566,10 +18577,10 @@
         <v>500</v>
       </c>
       <c r="G362" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H362" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="I362">
         <v>97463489342</v>
@@ -18598,17 +18609,17 @@
         <v>6000</v>
       </c>
       <c r="G363" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="H363" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I363">
         <f>974-4293-8360</f>
         <v>-11679</v>
       </c>
       <c r="J363" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K363" t="s">
         <v>63</v>
@@ -18634,10 +18645,10 @@
         <v>750</v>
       </c>
       <c r="G364" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="H364" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="I364">
         <v>97469366785</v>
@@ -18666,19 +18677,19 @@
         <v>9250</v>
       </c>
       <c r="F365" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G365" s="5">
         <v>45135</v>
       </c>
       <c r="H365" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="I365" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="J365" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K365" t="s">
         <v>48</v>
@@ -18707,7 +18718,7 @@
         <v>44450</v>
       </c>
       <c r="H366" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="I366">
         <v>39452418</v>
@@ -18739,13 +18750,13 @@
         <v>250</v>
       </c>
       <c r="G367" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H367" t="s">
+        <v>1649</v>
+      </c>
+      <c r="I367" t="s">
         <v>1650</v>
-      </c>
-      <c r="H367" t="s">
-        <v>1651</v>
-      </c>
-      <c r="I367" t="s">
-        <v>1652</v>
       </c>
       <c r="J367" t="s">
         <v>59</v>
@@ -18777,13 +18788,13 @@
         <v>43681</v>
       </c>
       <c r="H368" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="I368" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="J368" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
@@ -18803,13 +18814,13 @@
         <v>48</v>
       </c>
       <c r="F369" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G369" s="5">
         <v>43943</v>
       </c>
       <c r="H369" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="I369">
         <f>974-6537-3326</f>
@@ -18839,13 +18850,13 @@
         <v>5200</v>
       </c>
       <c r="F370" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G370" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="H370" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="J370" t="s">
         <v>50</v>
@@ -18877,7 +18888,7 @@
         <v>43479</v>
       </c>
       <c r="H371" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="I371">
         <v>44041918</v>
@@ -18912,10 +18923,10 @@
         <v>45339</v>
       </c>
       <c r="H372" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="I372" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="J372" t="s">
         <v>50</v>
@@ -18944,19 +18955,19 @@
         <v>-200</v>
       </c>
       <c r="G373" t="s">
+        <v>1659</v>
+      </c>
+      <c r="H373" t="s">
+        <v>1660</v>
+      </c>
+      <c r="I373" t="s">
         <v>1661</v>
-      </c>
-      <c r="H373" t="s">
-        <v>1662</v>
-      </c>
-      <c r="I373" t="s">
-        <v>1663</v>
       </c>
       <c r="J373" t="s">
         <v>58</v>
       </c>
       <c r="K373" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
@@ -18982,10 +18993,10 @@
         <v>48</v>
       </c>
       <c r="H374" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="I374" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J374" t="s">
         <v>48</v>
@@ -19014,10 +19025,10 @@
         <v>250</v>
       </c>
       <c r="G375" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="H375" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="I375">
         <f>974-6648-1959</f>
@@ -19050,10 +19061,10 @@
         <v>500</v>
       </c>
       <c r="G376" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="H376" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="I376">
         <v>46333602</v>
@@ -19085,13 +19096,13 @@
         <v>500</v>
       </c>
       <c r="G377" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H377" t="s">
+        <v>1668</v>
+      </c>
+      <c r="I377" t="s">
         <v>1669</v>
-      </c>
-      <c r="H377" t="s">
-        <v>1670</v>
-      </c>
-      <c r="I377" t="s">
-        <v>1671</v>
       </c>
       <c r="J377" t="s">
         <v>55</v>
@@ -19123,7 +19134,7 @@
         <v>44100</v>
       </c>
       <c r="H378" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="I378">
         <v>43081686</v>
@@ -19155,10 +19166,10 @@
         <v>45159</v>
       </c>
       <c r="H379" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="I379" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="J379" t="s">
         <v>58</v>
@@ -19184,22 +19195,22 @@
         <v>50</v>
       </c>
       <c r="F380" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G380" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H380" t="s">
+        <v>1673</v>
+      </c>
+      <c r="I380" t="s">
         <v>1674</v>
       </c>
-      <c r="H380" t="s">
-        <v>1675</v>
-      </c>
-      <c r="I380" t="s">
-        <v>1676</v>
-      </c>
       <c r="J380" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K380" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
@@ -19222,13 +19233,13 @@
         <v>48</v>
       </c>
       <c r="G381" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H381" t="s">
+        <v>1676</v>
+      </c>
+      <c r="I381" t="s">
         <v>1677</v>
-      </c>
-      <c r="H381" t="s">
-        <v>1678</v>
-      </c>
-      <c r="I381" t="s">
-        <v>1679</v>
       </c>
       <c r="J381" t="s">
         <v>48</v>
@@ -19257,13 +19268,13 @@
         <v>750</v>
       </c>
       <c r="G382" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="H382" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="I382" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="J382" t="s">
         <v>58</v>
@@ -19295,7 +19306,7 @@
         <v>44114</v>
       </c>
       <c r="H383" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="I383">
         <f>974-3182-5870</f>
@@ -19305,7 +19316,7 @@
         <v>56</v>
       </c>
       <c r="K383" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
@@ -19331,10 +19342,10 @@
         <v>44904</v>
       </c>
       <c r="H384" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I384" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="J384" t="s">
         <v>55</v>
@@ -19363,10 +19374,10 @@
         <v>500</v>
       </c>
       <c r="G385" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="H385" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="I385" t="s">
         <v>48</v>
@@ -19395,22 +19406,22 @@
         <v>7000</v>
       </c>
       <c r="F386" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G386" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H386" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I386" t="s">
         <v>1686</v>
       </c>
-      <c r="H386" t="s">
-        <v>1687</v>
-      </c>
-      <c r="I386" t="s">
-        <v>1688</v>
-      </c>
       <c r="J386" t="s">
         <v>48</v>
       </c>
       <c r="K386" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
@@ -19430,16 +19441,16 @@
         <v>50</v>
       </c>
       <c r="F387" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G387" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H387" t="s">
+        <v>1688</v>
+      </c>
+      <c r="I387" t="s">
         <v>1689</v>
-      </c>
-      <c r="H387" t="s">
-        <v>1690</v>
-      </c>
-      <c r="I387" t="s">
-        <v>1691</v>
       </c>
       <c r="J387" t="s">
         <v>58</v>
@@ -19471,10 +19482,10 @@
         <v>45748</v>
       </c>
       <c r="H388" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="I388" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="J388" t="s">
         <v>60</v>
@@ -19506,16 +19517,16 @@
         <v>44159</v>
       </c>
       <c r="H389" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="I389" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="J389" t="s">
         <v>962</v>
       </c>
       <c r="K389" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
@@ -19538,13 +19549,13 @@
         <v>959</v>
       </c>
       <c r="G390" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H390" t="s">
+        <v>1695</v>
+      </c>
+      <c r="I390" t="s">
         <v>1696</v>
-      </c>
-      <c r="H390" t="s">
-        <v>1697</v>
-      </c>
-      <c r="I390" t="s">
-        <v>1698</v>
       </c>
       <c r="J390" t="s">
         <v>48</v>
@@ -19576,10 +19587,10 @@
         <v>44810</v>
       </c>
       <c r="H391" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="I391" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J391" t="s">
         <v>48</v>
@@ -19608,16 +19619,16 @@
         <v>-200</v>
       </c>
       <c r="G392" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H392" t="s">
+        <v>1699</v>
+      </c>
+      <c r="I392" t="s">
         <v>1700</v>
       </c>
-      <c r="H392" t="s">
-        <v>1701</v>
-      </c>
-      <c r="I392" t="s">
-        <v>1702</v>
-      </c>
       <c r="J392" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K392" t="s">
         <v>65</v>
@@ -19643,13 +19654,13 @@
         <v>48</v>
       </c>
       <c r="G393" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="H393" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="I393" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="J393" t="s">
         <v>58</v>
@@ -19678,16 +19689,16 @@
         <v>44404</v>
       </c>
       <c r="H394" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="I394" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="J394" t="s">
         <v>60</v>
       </c>
       <c r="K394" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
@@ -19713,7 +19724,7 @@
         <v>45601</v>
       </c>
       <c r="H395" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="I395">
         <f>974-4275-8364</f>
@@ -19749,10 +19760,10 @@
         <v>45385</v>
       </c>
       <c r="H396" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="I396" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="J396" t="s">
         <v>59</v>
@@ -19778,10 +19789,10 @@
         <v>250</v>
       </c>
       <c r="G397" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="H397" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="I397">
         <f>974-3133-3171</f>
@@ -19817,7 +19828,7 @@
         <v>43523</v>
       </c>
       <c r="H398" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="I398" t="s">
         <v>48</v>
@@ -19849,13 +19860,13 @@
         <v>500</v>
       </c>
       <c r="G399" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H399" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="I399" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="J399" t="s">
         <v>48</v>
@@ -19887,10 +19898,10 @@
         <v>44660</v>
       </c>
       <c r="H400" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="I400" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="J400" t="s">
         <v>962</v>
@@ -19916,16 +19927,16 @@
         <v>50</v>
       </c>
       <c r="F401" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G401" s="5">
         <v>44454</v>
       </c>
       <c r="H401" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="I401" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="J401" t="s">
         <v>54</v>
@@ -19957,7 +19968,7 @@
         <v>51</v>
       </c>
       <c r="H402" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="I402">
         <v>123</v>
@@ -19966,7 +19977,7 @@
         <v>50</v>
       </c>
       <c r="K402" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
@@ -19992,14 +20003,14 @@
         <v>45094</v>
       </c>
       <c r="H403" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="I403">
         <f>974-7979-1861</f>
         <v>-8866</v>
       </c>
       <c r="J403" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K403" t="s">
         <v>50</v>
@@ -20028,10 +20039,10 @@
         <v>45408</v>
       </c>
       <c r="H404" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="I404" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="K404" t="s">
         <v>62</v>
@@ -20057,13 +20068,13 @@
         <v>300</v>
       </c>
       <c r="G405" t="s">
+        <v>1721</v>
+      </c>
+      <c r="H405" t="s">
+        <v>1722</v>
+      </c>
+      <c r="I405" t="s">
         <v>1723</v>
-      </c>
-      <c r="H405" t="s">
-        <v>1724</v>
-      </c>
-      <c r="I405" t="s">
-        <v>1725</v>
       </c>
       <c r="J405" t="s">
         <v>58</v>
@@ -20092,17 +20103,17 @@
         <v>500</v>
       </c>
       <c r="G406" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="H406" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="I406">
         <f>974-3386-1313</f>
         <v>-3725</v>
       </c>
       <c r="J406" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K406" t="s">
         <v>65</v>
@@ -20128,10 +20139,10 @@
         <v>500</v>
       </c>
       <c r="G407" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="H407" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="I407">
         <v>32899733</v>
@@ -20140,7 +20151,7 @@
         <v>962</v>
       </c>
       <c r="K407" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
@@ -20166,10 +20177,10 @@
         <v>44479</v>
       </c>
       <c r="H408" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="I408" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="J408" t="s">
         <v>57</v>
@@ -20201,10 +20212,10 @@
         <v>43930</v>
       </c>
       <c r="H409" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="I409" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="J409" t="s">
         <v>962</v>
@@ -20233,16 +20244,16 @@
         <v>500</v>
       </c>
       <c r="G410" t="s">
+        <v>1732</v>
+      </c>
+      <c r="H410" t="s">
+        <v>1733</v>
+      </c>
+      <c r="I410" t="s">
         <v>1734</v>
       </c>
-      <c r="H410" t="s">
-        <v>1735</v>
-      </c>
-      <c r="I410" t="s">
-        <v>1736</v>
-      </c>
       <c r="J410" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K410" t="s">
         <v>48</v>
@@ -20268,16 +20279,16 @@
         <v>500</v>
       </c>
       <c r="G411" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H411" t="s">
+        <v>1736</v>
+      </c>
+      <c r="I411" t="s">
         <v>1737</v>
       </c>
-      <c r="H411" t="s">
-        <v>1738</v>
-      </c>
-      <c r="I411" t="s">
-        <v>1739</v>
-      </c>
       <c r="J411" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K411" t="s">
         <v>61</v>
@@ -20306,16 +20317,16 @@
         <v>45574</v>
       </c>
       <c r="H412" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I412" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="J412" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K412" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
@@ -20341,13 +20352,13 @@
         <v>51</v>
       </c>
       <c r="H413" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="I413" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="J413" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K413" t="s">
         <v>63</v>
@@ -20376,10 +20387,10 @@
         <v>45575</v>
       </c>
       <c r="H414" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="I414" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="K414" t="s">
         <v>50</v>
@@ -20408,7 +20419,7 @@
         <v>43792</v>
       </c>
       <c r="H415" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="I415">
         <v>42433957</v>
@@ -20440,13 +20451,13 @@
         <v>750</v>
       </c>
       <c r="G416" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H416" t="s">
+        <v>1745</v>
+      </c>
+      <c r="I416" t="s">
         <v>1746</v>
-      </c>
-      <c r="H416" t="s">
-        <v>1747</v>
-      </c>
-      <c r="I416" t="s">
-        <v>1748</v>
       </c>
       <c r="J416" t="s">
         <v>57</v>
@@ -20478,10 +20489,10 @@
         <v>45383</v>
       </c>
       <c r="H417" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="I417" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="J417" t="s">
         <v>962</v>
@@ -20513,13 +20524,13 @@
         <v>44545</v>
       </c>
       <c r="H418" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="I418">
         <v>52393798</v>
       </c>
       <c r="J418" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K418" t="s">
         <v>63</v>
@@ -20545,19 +20556,19 @@
         <v>300</v>
       </c>
       <c r="G419" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H419" t="s">
+        <v>1751</v>
+      </c>
+      <c r="I419" t="s">
         <v>1752</v>
-      </c>
-      <c r="H419" t="s">
-        <v>1753</v>
-      </c>
-      <c r="I419" t="s">
-        <v>1754</v>
       </c>
       <c r="J419" t="s">
         <v>55</v>
       </c>
       <c r="K419" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
@@ -20580,19 +20591,19 @@
         <v>750</v>
       </c>
       <c r="G420" t="s">
+        <v>1753</v>
+      </c>
+      <c r="H420" t="s">
+        <v>1754</v>
+      </c>
+      <c r="I420" t="s">
         <v>1755</v>
-      </c>
-      <c r="H420" t="s">
-        <v>1756</v>
-      </c>
-      <c r="I420" t="s">
-        <v>1757</v>
       </c>
       <c r="J420" t="s">
         <v>60</v>
       </c>
       <c r="K420" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
@@ -20615,13 +20626,13 @@
         <v>48</v>
       </c>
       <c r="G421" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="H421" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="I421" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J421" t="s">
         <v>56</v>
@@ -20650,17 +20661,17 @@
         <v>300</v>
       </c>
       <c r="G422" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H422" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="I422">
         <f>974-3777-6084</f>
         <v>-8887</v>
       </c>
       <c r="J422" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K422" t="s">
         <v>66</v>
@@ -20686,19 +20697,19 @@
         <v>-200</v>
       </c>
       <c r="G423" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="H423" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I423" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="J423" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K423" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
@@ -20721,10 +20732,10 @@
         <v>500</v>
       </c>
       <c r="G424" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="H424" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="I424">
         <v>32242788</v>
@@ -20753,19 +20764,19 @@
         <v>48</v>
       </c>
       <c r="F425" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G425" t="s">
         <v>50</v>
       </c>
       <c r="H425" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="I425" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="J425" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K425" t="s">
         <v>66</v>
@@ -20788,19 +20799,19 @@
         <v>5250</v>
       </c>
       <c r="F426" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G426" s="5">
         <v>44995</v>
       </c>
       <c r="H426" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="I426" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="J426" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K426" t="s">
         <v>61</v>
@@ -20829,7 +20840,7 @@
         <v>44199</v>
       </c>
       <c r="H427" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="I427">
         <f>974-4343-4332</f>
@@ -20839,7 +20850,7 @@
         <v>57</v>
       </c>
       <c r="K427" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
@@ -20862,19 +20873,19 @@
         <v>-200</v>
       </c>
       <c r="G428" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H428" t="s">
+        <v>1769</v>
+      </c>
+      <c r="I428" t="s">
         <v>1770</v>
       </c>
-      <c r="H428" t="s">
-        <v>1771</v>
-      </c>
-      <c r="I428" t="s">
-        <v>1772</v>
-      </c>
       <c r="J428" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K428" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
@@ -20900,7 +20911,7 @@
         <v>43952</v>
       </c>
       <c r="H429" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="I429">
         <f>974-3432-3162</f>
@@ -20933,10 +20944,10 @@
         <v>500</v>
       </c>
       <c r="G430" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="I430" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="J430" t="s">
         <v>57</v>
@@ -20968,7 +20979,7 @@
         <v>45583</v>
       </c>
       <c r="H431" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="I431">
         <v>64675503</v>
@@ -20997,13 +21008,13 @@
         <v>6800</v>
       </c>
       <c r="F432" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G432" s="5">
         <v>43952</v>
       </c>
       <c r="H432" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="I432">
         <v>97478726309</v>
@@ -21012,7 +21023,7 @@
         <v>59</v>
       </c>
       <c r="K432" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
@@ -21035,13 +21046,13 @@
         <v>500</v>
       </c>
       <c r="G433" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H433" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="I433" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="J433" t="s">
         <v>55</v>
@@ -21070,13 +21081,13 @@
         <v>750</v>
       </c>
       <c r="G434" t="s">
+        <v>1777</v>
+      </c>
+      <c r="H434" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I434" t="s">
         <v>1779</v>
-      </c>
-      <c r="H434" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I434" t="s">
-        <v>1781</v>
       </c>
       <c r="J434" t="s">
         <v>56</v>
@@ -21108,7 +21119,7 @@
         <v>45264</v>
       </c>
       <c r="H435" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="I435">
         <v>35098455</v>
@@ -21117,7 +21128,7 @@
         <v>59</v>
       </c>
       <c r="K435" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
@@ -21143,7 +21154,7 @@
         <v>44000</v>
       </c>
       <c r="I436" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J436" t="s">
         <v>54</v>
@@ -21169,13 +21180,13 @@
         <v>5500</v>
       </c>
       <c r="F437" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G437" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="H437" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="I437">
         <v>57328448</v>
@@ -21184,7 +21195,7 @@
         <v>55</v>
       </c>
       <c r="K437" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
@@ -21204,13 +21215,13 @@
         <v>7000</v>
       </c>
       <c r="F438" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G438" s="5">
         <v>43520</v>
       </c>
       <c r="H438" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="I438">
         <f>974-6629-9664</f>
@@ -21220,7 +21231,7 @@
         <v>57</v>
       </c>
       <c r="K438" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
@@ -21246,14 +21257,14 @@
         <v>45551</v>
       </c>
       <c r="H439" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="I439">
         <f>974-5756-8104</f>
         <v>-12886</v>
       </c>
       <c r="J439" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K439" t="s">
         <v>66</v>
@@ -21279,19 +21290,19 @@
         <v>-50</v>
       </c>
       <c r="G440" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H440" t="s">
+        <v>1786</v>
+      </c>
+      <c r="I440" t="s">
         <v>1787</v>
-      </c>
-      <c r="H440" t="s">
-        <v>1788</v>
-      </c>
-      <c r="I440" t="s">
-        <v>1789</v>
       </c>
       <c r="J440" t="s">
         <v>962</v>
       </c>
       <c r="K440" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
@@ -21317,10 +21328,10 @@
         <v>45650</v>
       </c>
       <c r="H441" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="I441" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="K441" t="s">
         <v>66</v>
@@ -21346,10 +21357,10 @@
         <v>959</v>
       </c>
       <c r="G442" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="H442" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="I442">
         <f>974-6768-7821</f>
@@ -21379,16 +21390,16 @@
         <v>50</v>
       </c>
       <c r="F443" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G443" s="5">
         <v>44291</v>
       </c>
       <c r="H443" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="I443" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="J443" t="s">
         <v>58</v>
@@ -21417,13 +21428,13 @@
         <v>250</v>
       </c>
       <c r="G444" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="H444" t="s">
         <v>50</v>
       </c>
       <c r="I444" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="J444" t="s">
         <v>56</v>
@@ -21455,10 +21466,10 @@
         <v>43533</v>
       </c>
       <c r="H445" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="I445" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="J445" t="s">
         <v>58</v>
@@ -21484,13 +21495,13 @@
         <v>48</v>
       </c>
       <c r="F446" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G446" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="H446" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="I446">
         <f>974-4863-2991</f>
@@ -21523,16 +21534,16 @@
         <v>50</v>
       </c>
       <c r="G447" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H447" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I447" t="s">
         <v>1802</v>
       </c>
-      <c r="H447" t="s">
-        <v>1803</v>
-      </c>
-      <c r="I447" t="s">
-        <v>1804</v>
-      </c>
       <c r="J447" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K447" t="s">
         <v>62</v>
@@ -21558,10 +21569,10 @@
         <v>44697</v>
       </c>
       <c r="H448" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I448" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="J448" t="s">
         <v>962</v>
@@ -21587,7 +21598,7 @@
         <v>-200</v>
       </c>
       <c r="G449" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="H449" t="s">
         <v>50</v>
@@ -21596,7 +21607,7 @@
         <v>50625467</v>
       </c>
       <c r="J449" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K449" t="s">
         <v>61</v>
@@ -21632,7 +21643,7 @@
         <v>48</v>
       </c>
       <c r="K450" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
@@ -21652,13 +21663,13 @@
         <v>8500</v>
       </c>
       <c r="F451" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G451" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="H451" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="I451">
         <v>47353381</v>
@@ -21687,22 +21698,22 @@
         <v>4500</v>
       </c>
       <c r="F452" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G452" t="s">
+        <v>1806</v>
+      </c>
+      <c r="H452" t="s">
+        <v>1807</v>
+      </c>
+      <c r="I452" t="s">
         <v>1808</v>
-      </c>
-      <c r="H452" t="s">
-        <v>1809</v>
-      </c>
-      <c r="I452" t="s">
-        <v>1810</v>
       </c>
       <c r="J452" t="s">
         <v>57</v>
       </c>
       <c r="K452" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
@@ -21728,7 +21739,7 @@
         <v>44623</v>
       </c>
       <c r="H453" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="I453">
         <f>974-6184-8013</f>
@@ -21761,16 +21772,16 @@
         <v>500</v>
       </c>
       <c r="G454" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H454" t="s">
+        <v>1811</v>
+      </c>
+      <c r="I454" t="s">
         <v>1812</v>
       </c>
-      <c r="H454" t="s">
-        <v>1813</v>
-      </c>
-      <c r="I454" t="s">
-        <v>1814</v>
-      </c>
       <c r="J454" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K454" t="s">
         <v>61</v>
@@ -21793,16 +21804,16 @@
         <v>9000</v>
       </c>
       <c r="F455" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G455" s="5">
         <v>44310</v>
       </c>
       <c r="H455" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="I455" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J455" t="s">
         <v>58</v>
@@ -21831,13 +21842,13 @@
         <v>45482</v>
       </c>
       <c r="H456" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="I456" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="J456" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K456" t="s">
         <v>50</v>
@@ -21863,13 +21874,13 @@
         <v>300</v>
       </c>
       <c r="G457" t="s">
+        <v>1815</v>
+      </c>
+      <c r="H457" t="s">
+        <v>1816</v>
+      </c>
+      <c r="I457" t="s">
         <v>1817</v>
-      </c>
-      <c r="H457" t="s">
-        <v>1818</v>
-      </c>
-      <c r="I457" t="s">
-        <v>1819</v>
       </c>
       <c r="J457" t="s">
         <v>962</v>
@@ -21898,10 +21909,10 @@
         <v>50</v>
       </c>
       <c r="G458" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="H458" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="I458">
         <f>974-5701-6106</f>
@@ -21937,10 +21948,10 @@
         <v>44361</v>
       </c>
       <c r="H459" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="I459" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="J459" t="s">
         <v>60</v>
@@ -21969,13 +21980,13 @@
         <v>0</v>
       </c>
       <c r="G460" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H460" t="s">
+        <v>1823</v>
+      </c>
+      <c r="I460" t="s">
         <v>1824</v>
-      </c>
-      <c r="H460" t="s">
-        <v>1825</v>
-      </c>
-      <c r="I460" t="s">
-        <v>1826</v>
       </c>
       <c r="J460" t="s">
         <v>48</v>
@@ -22004,17 +22015,17 @@
         <v>50</v>
       </c>
       <c r="G461" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="H461" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="I461">
         <f>974-6523-9980</f>
         <v>-15529</v>
       </c>
       <c r="J461" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K461" t="s">
         <v>64</v>
@@ -22040,16 +22051,16 @@
         <v>750</v>
       </c>
       <c r="G462" t="s">
+        <v>1827</v>
+      </c>
+      <c r="H462" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I462" t="s">
         <v>1829</v>
       </c>
-      <c r="H462" t="s">
-        <v>1830</v>
-      </c>
-      <c r="I462" t="s">
-        <v>1831</v>
-      </c>
       <c r="J462" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K462" t="s">
         <v>63</v>
@@ -22075,13 +22086,13 @@
         <v>500</v>
       </c>
       <c r="G463" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H463" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I463" t="s">
         <v>1832</v>
-      </c>
-      <c r="H463" t="s">
-        <v>1833</v>
-      </c>
-      <c r="I463" t="s">
-        <v>1834</v>
       </c>
       <c r="J463" t="s">
         <v>48</v>
@@ -22113,16 +22124,16 @@
         <v>43931</v>
       </c>
       <c r="H464" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="I464">
         <v>64491999</v>
       </c>
       <c r="J464" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K464" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -22145,17 +22156,17 @@
         <v>1000</v>
       </c>
       <c r="G465" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H465" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="I465">
         <f>974-7977-1000</f>
         <v>-8003</v>
       </c>
       <c r="J465" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K465" t="s">
         <v>62</v>
@@ -22184,10 +22195,10 @@
         <v>43471</v>
       </c>
       <c r="H466" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="I466" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="J466" t="s">
         <v>48</v>
@@ -22219,7 +22230,7 @@
         <v>45066</v>
       </c>
       <c r="H467" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="I467">
         <f>974-4032-1792</f>
@@ -22252,13 +22263,13 @@
         <v>1250</v>
       </c>
       <c r="G468" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="H468" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="I468" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="J468" t="s">
         <v>55</v>
@@ -22290,7 +22301,7 @@
         <v>45472</v>
       </c>
       <c r="H469" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="I469">
         <v>60232785</v>
@@ -22325,7 +22336,7 @@
         <v>45613</v>
       </c>
       <c r="H470" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="I470">
         <f>974-6307-8049</f>
@@ -22361,13 +22372,13 @@
         <v>44433</v>
       </c>
       <c r="H471" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="I471">
         <v>71195089</v>
       </c>
       <c r="J471" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K471" t="s">
         <v>63</v>
@@ -22396,10 +22407,10 @@
         <v>45607</v>
       </c>
       <c r="H472" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="I472" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="J472" t="s">
         <v>54</v>
@@ -22431,10 +22442,10 @@
         <v>48</v>
       </c>
       <c r="H473" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="I473" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="J473" t="s">
         <v>60</v>
@@ -22466,10 +22477,10 @@
         <v>44677</v>
       </c>
       <c r="H474" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="I474" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="J474" t="s">
         <v>48</v>
@@ -22501,10 +22512,10 @@
         <v>44929</v>
       </c>
       <c r="H475" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="I475" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="J475" t="s">
         <v>48</v>
@@ -22530,16 +22541,16 @@
         <v>-1000</v>
       </c>
       <c r="F476" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G476" s="5">
         <v>43474</v>
       </c>
       <c r="H476" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="I476" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="J476" t="s">
         <v>57</v>
@@ -22565,16 +22576,16 @@
         <v>50</v>
       </c>
       <c r="F477" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G477" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H477" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I477" t="s">
         <v>1852</v>
-      </c>
-      <c r="H477" t="s">
-        <v>1853</v>
-      </c>
-      <c r="I477" t="s">
-        <v>1854</v>
       </c>
       <c r="J477" t="s">
         <v>60</v>
@@ -22606,13 +22617,13 @@
         <v>44970</v>
       </c>
       <c r="H478" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="I478" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="J478" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="K478" t="s">
         <v>62</v>
@@ -22638,13 +22649,13 @@
         <v>300</v>
       </c>
       <c r="G479" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H479" t="s">
+        <v>1856</v>
+      </c>
+      <c r="I479" t="s">
         <v>1857</v>
-      </c>
-      <c r="H479" t="s">
-        <v>1858</v>
-      </c>
-      <c r="I479" t="s">
-        <v>1859</v>
       </c>
       <c r="J479" t="s">
         <v>48</v>
@@ -22673,10 +22684,10 @@
         <v>750</v>
       </c>
       <c r="G480" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="H480" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="I480">
         <f>974-3923-9757</f>
@@ -22709,10 +22720,10 @@
         <v>-50</v>
       </c>
       <c r="G481" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="H481" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="I481">
         <v>31451732</v>
@@ -22744,13 +22755,13 @@
         <v>48</v>
       </c>
       <c r="G482" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H482" t="s">
+        <v>1863</v>
+      </c>
+      <c r="I482" t="s">
         <v>1864</v>
-      </c>
-      <c r="H482" t="s">
-        <v>1865</v>
-      </c>
-      <c r="I482" t="s">
-        <v>1866</v>
       </c>
       <c r="J482" t="s">
         <v>55</v>
@@ -22789,7 +22800,7 @@
         <v>54</v>
       </c>
       <c r="K483" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.25">
@@ -22815,7 +22826,7 @@
         <v>44512</v>
       </c>
       <c r="H484" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="I484">
         <f>974-4801-3564</f>
@@ -22848,10 +22859,10 @@
         <v>44965</v>
       </c>
       <c r="H485" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="I485" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="J485" t="s">
         <v>58</v>
@@ -22877,10 +22888,10 @@
         <v>48</v>
       </c>
       <c r="G486" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="H486" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="J486" t="s">
         <v>48</v>
@@ -22906,16 +22917,16 @@
         <v>4500</v>
       </c>
       <c r="F487" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G487" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H487" t="s">
+        <v>1871</v>
+      </c>
+      <c r="I487" t="s">
         <v>1872</v>
-      </c>
-      <c r="H487" t="s">
-        <v>1873</v>
-      </c>
-      <c r="I487" t="s">
-        <v>1874</v>
       </c>
       <c r="J487" t="s">
         <v>59</v>
@@ -22944,13 +22955,13 @@
         <v>-200</v>
       </c>
       <c r="G488" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H488" t="s">
+        <v>1874</v>
+      </c>
+      <c r="I488" t="s">
         <v>1875</v>
-      </c>
-      <c r="H488" t="s">
-        <v>1876</v>
-      </c>
-      <c r="I488" t="s">
-        <v>1877</v>
       </c>
       <c r="J488" t="s">
         <v>59</v>
@@ -22979,10 +22990,10 @@
         <v>-50</v>
       </c>
       <c r="G489" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="H489" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="I489">
         <v>39632432</v>
@@ -23014,19 +23025,19 @@
         <v>500</v>
       </c>
       <c r="G490" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H490" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I490" t="s">
         <v>1880</v>
       </c>
-      <c r="H490" t="s">
-        <v>1881</v>
-      </c>
-      <c r="I490" t="s">
-        <v>1882</v>
-      </c>
       <c r="J490" t="s">
         <v>48</v>
       </c>
       <c r="K490" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
@@ -23052,10 +23063,10 @@
         <v>45010</v>
       </c>
       <c r="H491" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="I491" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="J491" t="s">
         <v>56</v>
@@ -23084,13 +23095,13 @@
         <v>500</v>
       </c>
       <c r="G492" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="H492" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="I492" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="K492" t="s">
         <v>65</v>
@@ -23116,10 +23127,10 @@
         <v>50</v>
       </c>
       <c r="G493" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="H493" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="I493">
         <v>61387776</v>
@@ -23154,10 +23165,10 @@
         <v>45294</v>
       </c>
       <c r="H494" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="I494" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="J494" t="s">
         <v>60</v>
@@ -23189,10 +23200,10 @@
         <v>44341</v>
       </c>
       <c r="I495" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="J495" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="K495" t="s">
         <v>48</v>
@@ -23218,10 +23229,10 @@
         <v>500</v>
       </c>
       <c r="G496" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H496" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="I496">
         <v>61054008</v>
@@ -23230,7 +23241,7 @@
         <v>58</v>
       </c>
       <c r="K496" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.25">
@@ -23256,7 +23267,7 @@
         <v>43505</v>
       </c>
       <c r="H497" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="I497">
         <v>31753140</v>
@@ -23288,13 +23299,13 @@
         <v>1000</v>
       </c>
       <c r="G498" t="s">
+        <v>1887</v>
+      </c>
+      <c r="H498" t="s">
+        <v>1888</v>
+      </c>
+      <c r="I498" t="s">
         <v>1889</v>
-      </c>
-      <c r="H498" t="s">
-        <v>1890</v>
-      </c>
-      <c r="I498" t="s">
-        <v>1891</v>
       </c>
       <c r="J498" t="s">
         <v>59</v>
@@ -23326,10 +23337,10 @@
         <v>44180</v>
       </c>
       <c r="H499" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="I499" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="J499" t="s">
         <v>55</v>
@@ -23355,13 +23366,13 @@
         <v>7000</v>
       </c>
       <c r="F500" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G500" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="H500" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="I500">
         <f>974-7610-2894</f>
@@ -23391,22 +23402,25 @@
         <v>6200</v>
       </c>
       <c r="G501" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="H501" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I501" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="J501" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K501" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{343C0C78-8CA2-4638-85AD-743B33841C10}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B3AEA4-18F2-4356-8DBD-D3870BA90B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1B22CC-63E3-4C8C-8C1F-535F7962F240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3935" uniqueCount="1899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3936" uniqueCount="1900">
   <si>
     <t xml:space="preserve"> Employee ID </t>
   </si>
@@ -5733,6 +5733,9 @@
   </si>
   <si>
     <t>john.davishotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +6028 1693 </t>
   </si>
 </sst>
 </file>
@@ -6101,9 +6104,9 @@
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.140625" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6340,7 +6343,7 @@
         <v>969</v>
       </c>
       <c r="I7" t="s">
-        <v>970</v>
+        <v>1899</v>
       </c>
       <c r="J7" t="s">
         <v>54</v>
@@ -6461,9 +6464,8 @@
       <c r="H11" t="s">
         <v>978</v>
       </c>
-      <c r="I11">
-        <f>974-7599-3420</f>
-        <v>-10045</v>
+      <c r="I11" t="s">
+        <v>970</v>
       </c>
       <c r="J11" t="s">
         <v>979</v>

--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1E70F2-B944-4E46-8260-41DAAD74D725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC79B16-0647-4D7D-8398-01D85ABF6CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3937" uniqueCount="1896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1979">
   <si>
     <t xml:space="preserve"> Employee ID </t>
   </si>
@@ -5724,15 +5724,261 @@
   </si>
   <si>
     <t xml:space="preserve"> +6028 1693 </t>
+  </si>
+  <si>
+    <t>$5,000</t>
+  </si>
+  <si>
+    <t>$500</t>
+  </si>
+  <si>
+    <t>7,501</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>8,000</t>
+  </si>
+  <si>
+    <t>6,500</t>
+  </si>
+  <si>
+    <t>-50</t>
+  </si>
+  <si>
+    <t>7,200</t>
+  </si>
+  <si>
+    <t>$9,000</t>
+  </si>
+  <si>
+    <t>-5,000</t>
+  </si>
+  <si>
+    <t>10,000</t>
+  </si>
+  <si>
+    <t>1,000</t>
+  </si>
+  <si>
+    <t>5,500</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>7,000</t>
+  </si>
+  <si>
+    <t>$4,500</t>
+  </si>
+  <si>
+    <t>5,200</t>
+  </si>
+  <si>
+    <t>1,250</t>
+  </si>
+  <si>
+    <t>6,800</t>
+  </si>
+  <si>
+    <t>$7,250</t>
+  </si>
+  <si>
+    <t>4,800</t>
+  </si>
+  <si>
+    <t>9,500</t>
+  </si>
+  <si>
+    <t>5,750</t>
+  </si>
+  <si>
+    <t>6,000</t>
+  </si>
+  <si>
+    <t>$8,200</t>
+  </si>
+  <si>
+    <t>-1,000</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>-200</t>
+  </si>
+  <si>
+    <t>$5,500</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>6,250</t>
+  </si>
+  <si>
+    <t>$9,750</t>
+  </si>
+  <si>
+    <t>4,500</t>
+  </si>
+  <si>
+    <t>5,000</t>
+  </si>
+  <si>
+    <t>$7,100</t>
+  </si>
+  <si>
+    <t>-250</t>
+  </si>
+  <si>
+    <t>6,200</t>
+  </si>
+  <si>
+    <t>$8,500</t>
+  </si>
+  <si>
+    <t>5,250</t>
+  </si>
+  <si>
+    <t>$6,000</t>
+  </si>
+  <si>
+    <t>7,500</t>
+  </si>
+  <si>
+    <t>9,000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>$4,800</t>
+  </si>
+  <si>
+    <t>$1,000</t>
+  </si>
+  <si>
+    <t>$5,750</t>
+  </si>
+  <si>
+    <t>-3,000</t>
+  </si>
+  <si>
+    <t>$9,200</t>
+  </si>
+  <si>
+    <t>$750</t>
+  </si>
+  <si>
+    <t>$6,750</t>
+  </si>
+  <si>
+    <t>8,500</t>
+  </si>
+  <si>
+    <t>$5,250</t>
+  </si>
+  <si>
+    <t>$10,000</t>
+  </si>
+  <si>
+    <t>$7,800</t>
+  </si>
+  <si>
+    <t>-1,500</t>
+  </si>
+  <si>
+    <t>$6,200</t>
+  </si>
+  <si>
+    <t>$8,000</t>
+  </si>
+  <si>
+    <t>$9,500</t>
+  </si>
+  <si>
+    <t>5,800</t>
+  </si>
+  <si>
+    <t>8,200</t>
+  </si>
+  <si>
+    <t>-500</t>
+  </si>
+  <si>
+    <t>$6,500</t>
+  </si>
+  <si>
+    <t>$4,750</t>
+  </si>
+  <si>
+    <t>$8,900</t>
+  </si>
+  <si>
+    <t>$6,250</t>
+  </si>
+  <si>
+    <t>$7,500</t>
+  </si>
+  <si>
+    <t>-2,000</t>
+  </si>
+  <si>
+    <t>$6,800</t>
+  </si>
+  <si>
+    <t>$9,250</t>
+  </si>
+  <si>
+    <t>-750</t>
+  </si>
+  <si>
+    <t>$7,200</t>
+  </si>
+  <si>
+    <t>7,750</t>
+  </si>
+  <si>
+    <t>-4,000</t>
+  </si>
+  <si>
+    <t>6,750</t>
+  </si>
+  <si>
+    <t>7,250</t>
+  </si>
+  <si>
+    <t>4,750</t>
+  </si>
+  <si>
+    <t>-2,500</t>
+  </si>
+  <si>
+    <t>9,200</t>
+  </si>
+  <si>
+    <t>9,750</t>
+  </si>
+  <si>
+    <t>8,250</t>
+  </si>
+  <si>
+    <t>9,250</t>
+  </si>
+  <si>
+    <t>8,750</t>
+  </si>
+  <si>
+    <t>1,200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -5776,17 +6022,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6098,6 +6345,8 @@
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.140625" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.28515625" customWidth="1"/>
@@ -6117,10 +6366,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -6152,11 +6401,11 @@
       <c r="D2" s="1">
         <v>25</v>
       </c>
-      <c r="E2" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F2" s="2">
-        <v>500</v>
+      <c r="E2" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G2" t="s">
         <v>50</v>
@@ -6187,13 +6436,13 @@
       <c r="D3" s="1">
         <v>30</v>
       </c>
-      <c r="E3">
-        <v>6000</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="6">
+        <v>16000</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="2">
         <v>51326</v>
       </c>
       <c r="H3" t="s">
@@ -6219,16 +6468,16 @@
       <c r="D4" s="1">
         <v>35</v>
       </c>
-      <c r="E4" s="3">
-        <v>7500.5</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="2">
         <v>43909</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>1893</v>
       </c>
       <c r="I4">
@@ -6254,13 +6503,13 @@
       <c r="D5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5">
-        <v>500</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H5" t="s">
@@ -6289,10 +6538,10 @@
       <c r="D6" s="1">
         <v>42</v>
       </c>
-      <c r="E6" s="4">
-        <v>8000</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
@@ -6324,13 +6573,13 @@
       <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7">
-        <v>6500</v>
-      </c>
-      <c r="F7">
-        <v>-50</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="E7" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G7" s="2">
         <v>44127</v>
       </c>
       <c r="H7" t="s">
@@ -6359,13 +6608,13 @@
       <c r="D8" s="1">
         <v>29</v>
       </c>
-      <c r="E8" s="4">
-        <v>7200</v>
-      </c>
-      <c r="F8">
-        <v>500</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1978</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H8" t="s">
@@ -6391,10 +6640,13 @@
       <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="2">
         <v>51039</v>
       </c>
       <c r="H9" t="s">
@@ -6420,8 +6672,11 @@
       <c r="D10" s="1">
         <v>150</v>
       </c>
-      <c r="E10" s="2">
-        <v>9000</v>
+      <c r="E10" s="5" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
       </c>
       <c r="G10" t="s">
         <v>972</v>
@@ -6446,11 +6701,11 @@
       <c r="D11" s="1">
         <v>-5</v>
       </c>
-      <c r="E11">
-        <v>-5000</v>
-      </c>
-      <c r="F11">
-        <v>500</v>
+      <c r="E11" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G11" t="s">
         <v>975</v>
@@ -6481,11 +6736,11 @@
       <c r="D12" s="1">
         <v>31</v>
       </c>
-      <c r="E12" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F12" s="2">
-        <v>500</v>
+      <c r="E12" s="5" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G12" t="s">
         <v>978</v>
@@ -6516,17 +6771,16 @@
       <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F13">
-        <v>1000</v>
+      <c r="F13" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="H13" t="s">
         <v>981</v>
       </c>
       <c r="I13">
-        <f>974-4653-7608</f>
         <v>-11287</v>
       </c>
       <c r="J13" t="s">
@@ -6549,11 +6803,11 @@
       <c r="D14" s="1">
         <v>27</v>
       </c>
-      <c r="E14">
-        <v>5500</v>
-      </c>
-      <c r="F14">
-        <v>-50</v>
+      <c r="E14" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G14" t="s">
         <v>982</v>
@@ -6584,20 +6838,19 @@
       <c r="D15" s="1">
         <v>33</v>
       </c>
-      <c r="E15" s="4">
-        <v>6500</v>
-      </c>
-      <c r="F15">
-        <v>300</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="E15" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G15" s="2">
         <v>44197</v>
       </c>
       <c r="H15" t="s">
         <v>984</v>
       </c>
       <c r="I15">
-        <f>974-5656-2009</f>
         <v>-6691</v>
       </c>
       <c r="J15" t="s">
@@ -6620,11 +6873,11 @@
       <c r="D16" s="1">
         <v>40</v>
       </c>
-      <c r="E16">
-        <v>7000</v>
-      </c>
-      <c r="F16">
-        <v>-50</v>
+      <c r="E16" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G16" t="s">
         <v>985</v>
@@ -6655,10 +6908,10 @@
       <c r="D17" s="1">
         <v>33</v>
       </c>
-      <c r="E17" s="4">
-        <v>6500</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G17" t="s">
@@ -6690,10 +6943,10 @@
       <c r="D18" s="1">
         <v>22</v>
       </c>
-      <c r="E18" s="2">
-        <v>4500</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="5" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G18" t="s">
@@ -6725,13 +6978,13 @@
       <c r="D19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E19">
-        <v>5200</v>
-      </c>
-      <c r="F19">
-        <v>1250</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="E19" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G19" s="2">
         <v>45639</v>
       </c>
       <c r="H19" t="s">
@@ -6760,13 +7013,13 @@
       <c r="D20" s="1">
         <v>45</v>
       </c>
-      <c r="E20" s="4">
-        <v>6800</v>
-      </c>
-      <c r="F20">
-        <v>500</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="E20" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G20" s="2">
         <v>44493</v>
       </c>
       <c r="H20" t="s">
@@ -6795,11 +7048,11 @@
       <c r="D21" s="1">
         <v>28</v>
       </c>
-      <c r="E21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21">
-        <v>300</v>
+      <c r="E21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G21" t="s">
         <v>997</v>
@@ -6830,10 +7083,10 @@
       <c r="D22" s="1">
         <v>36</v>
       </c>
-      <c r="E22" s="2">
-        <v>7250</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="5" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G22" t="s">
@@ -6865,10 +7118,10 @@
       <c r="D23" s="1">
         <v>19</v>
       </c>
-      <c r="E23">
-        <v>4800</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G23" t="s">
@@ -6900,8 +7153,11 @@
       <c r="D24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="4">
-        <v>9500</v>
+      <c r="E24" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
       </c>
       <c r="G24" t="s">
         <v>1005</v>
@@ -6932,10 +7188,10 @@
       <c r="D25" s="1">
         <v>125</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G25" t="s">
@@ -6967,10 +7223,10 @@
       <c r="D26" s="1">
         <v>-2</v>
       </c>
-      <c r="E26" s="4">
-        <v>5750</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>1010</v>
       </c>
       <c r="G26" t="s">
@@ -7002,10 +7258,10 @@
       <c r="D27" s="1">
         <v>34</v>
       </c>
-      <c r="E27">
-        <v>6000</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G27" t="s">
@@ -7037,10 +7293,10 @@
       <c r="D28" s="1">
         <v>41</v>
       </c>
-      <c r="E28" s="2">
-        <v>8200</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="5" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G28" t="s">
@@ -7069,13 +7325,13 @@
       <c r="D29" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="E29">
-        <v>-1000</v>
-      </c>
-      <c r="F29">
-        <v>250</v>
-      </c>
-      <c r="G29" s="5">
+      <c r="E29" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G29" s="2">
         <v>45352</v>
       </c>
       <c r="H29" t="s">
@@ -7104,13 +7360,13 @@
       <c r="D30" s="1">
         <v>26</v>
       </c>
-      <c r="E30" s="4">
-        <v>7000</v>
-      </c>
-      <c r="F30">
-        <v>-200</v>
-      </c>
-      <c r="G30" s="5">
+      <c r="E30" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G30" s="2">
         <v>44116</v>
       </c>
       <c r="H30" t="s">
@@ -7139,11 +7395,11 @@
       <c r="D31" s="1">
         <v>38</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="F31">
-        <v>250</v>
+      <c r="F31" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G31" t="s">
         <v>1021</v>
@@ -7174,11 +7430,11 @@
       <c r="D32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E32">
-        <v>6500</v>
-      </c>
-      <c r="F32">
-        <v>1000</v>
+      <c r="E32" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G32" t="s">
         <v>1024</v>
@@ -7209,20 +7465,19 @@
       <c r="D33" s="1">
         <v>23</v>
       </c>
-      <c r="E33" s="2">
-        <v>5500</v>
-      </c>
-      <c r="F33">
-        <v>250</v>
-      </c>
-      <c r="G33" s="5">
+      <c r="E33" s="5" t="s">
+        <v>1924</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G33" s="2">
         <v>45512</v>
       </c>
       <c r="H33" t="s">
         <v>1027</v>
       </c>
       <c r="I33">
-        <f>974-4124-5950</f>
         <v>-9100</v>
       </c>
       <c r="J33" t="s">
@@ -7245,11 +7500,11 @@
       <c r="D34" s="1">
         <v>44</v>
       </c>
-      <c r="E34">
-        <v>7200</v>
-      </c>
-      <c r="F34">
-        <v>750</v>
+      <c r="E34" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G34" t="s">
         <v>1028</v>
@@ -7280,13 +7535,13 @@
       <c r="D35" s="1">
         <v>32</v>
       </c>
-      <c r="E35" s="4">
-        <v>6250</v>
-      </c>
-      <c r="F35">
-        <v>500</v>
-      </c>
-      <c r="G35" s="5">
+      <c r="E35" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G35" s="2">
         <v>45102</v>
       </c>
       <c r="H35" t="s">
@@ -7315,11 +7570,11 @@
       <c r="D36" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36">
-        <v>250</v>
+      <c r="E36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G36" t="s">
         <v>1031</v>
@@ -7328,7 +7583,6 @@
         <v>1032</v>
       </c>
       <c r="I36">
-        <f>974-5264-7387</f>
         <v>-11677</v>
       </c>
       <c r="J36" t="s">
@@ -7351,11 +7605,11 @@
       <c r="D37" s="1">
         <v>29</v>
       </c>
-      <c r="E37">
-        <v>8000</v>
-      </c>
-      <c r="F37">
-        <v>250</v>
+      <c r="E37" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G37" t="s">
         <v>1033</v>
@@ -7386,13 +7640,13 @@
       <c r="D38" s="1">
         <v>17</v>
       </c>
-      <c r="E38" s="2">
-        <v>9750</v>
-      </c>
-      <c r="F38">
-        <v>-50</v>
-      </c>
-      <c r="G38" s="5">
+      <c r="E38" s="5" t="s">
+        <v>1927</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G38" s="2">
         <v>45083</v>
       </c>
       <c r="H38" t="s">
@@ -7421,8 +7675,11 @@
       <c r="D39" s="1">
         <v>55</v>
       </c>
-      <c r="E39">
-        <v>4500</v>
+      <c r="E39" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F39" s="5">
+        <v>0</v>
       </c>
       <c r="G39" t="s">
         <v>50</v>
@@ -7453,10 +7710,10 @@
       <c r="D40" s="1">
         <v>200</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G40" t="s">
@@ -7488,13 +7745,13 @@
       <c r="D41" s="1">
         <v>24</v>
       </c>
-      <c r="E41" s="4">
-        <v>5000</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="2">
         <v>44173</v>
       </c>
       <c r="H41" t="s">
@@ -7523,13 +7780,13 @@
       <c r="D42" s="1">
         <v>39</v>
       </c>
-      <c r="E42">
-        <v>6800</v>
-      </c>
-      <c r="F42">
-        <v>500</v>
-      </c>
-      <c r="G42" s="5">
+      <c r="E42" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G42" s="2">
         <v>43860</v>
       </c>
       <c r="H42" t="s">
@@ -7555,11 +7812,11 @@
       <c r="D43" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="2">
-        <v>7100</v>
-      </c>
-      <c r="F43">
-        <v>500</v>
+      <c r="E43" s="5" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G43" t="s">
         <v>1045</v>
@@ -7590,13 +7847,13 @@
       <c r="D44" s="1">
         <v>31</v>
       </c>
-      <c r="E44">
-        <v>5500</v>
-      </c>
-      <c r="F44">
-        <v>1000</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="E44" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G44" s="2">
         <v>44652</v>
       </c>
       <c r="H44" t="s">
@@ -7625,8 +7882,11 @@
       <c r="D45" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E45">
-        <v>-250</v>
+      <c r="E45" s="5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F45" s="5">
+        <v>0</v>
       </c>
       <c r="G45" t="s">
         <v>1049</v>
@@ -7657,17 +7917,19 @@
       <c r="D46" s="1">
         <v>28</v>
       </c>
-      <c r="E46">
-        <v>6200</v>
-      </c>
-      <c r="G46" s="5">
+      <c r="E46" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F46" s="5">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
         <v>44394</v>
       </c>
       <c r="H46" t="s">
         <v>1052</v>
       </c>
       <c r="I46">
-        <f>974-6091-2981</f>
         <v>-8098</v>
       </c>
       <c r="J46" t="s">
@@ -7690,13 +7952,13 @@
       <c r="D47" s="1">
         <v>46</v>
       </c>
-      <c r="E47" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47">
-        <v>500</v>
-      </c>
-      <c r="G47" s="5">
+      <c r="E47" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G47" s="2">
         <v>45384</v>
       </c>
       <c r="H47" t="s">
@@ -7725,20 +7987,19 @@
       <c r="D48" s="1">
         <v>33</v>
       </c>
-      <c r="E48" s="2">
-        <v>8500</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E48" s="5" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="2">
         <v>43577</v>
       </c>
       <c r="H48" t="s">
         <v>1056</v>
       </c>
       <c r="I48">
-        <f>974-4964-4959</f>
         <v>-8949</v>
       </c>
       <c r="J48" t="s">
@@ -7761,13 +8022,13 @@
       <c r="D49" s="1">
         <v>21</v>
       </c>
-      <c r="E49">
-        <v>7000</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E49" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="2">
         <v>44248</v>
       </c>
       <c r="H49" t="s">
@@ -7796,20 +8057,19 @@
       <c r="D50" s="1">
         <v>37</v>
       </c>
-      <c r="E50" s="4">
-        <v>5250</v>
-      </c>
-      <c r="F50">
-        <v>250</v>
-      </c>
-      <c r="G50" s="5">
+      <c r="E50" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G50" s="2">
         <v>44270</v>
       </c>
       <c r="H50" t="s">
         <v>1059</v>
       </c>
       <c r="I50">
-        <f>974-4026-1290</f>
         <v>-4342</v>
       </c>
       <c r="J50" t="s">
@@ -7832,11 +8092,11 @@
       <c r="D51" s="1">
         <v>-10</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F51">
-        <v>1000</v>
+      <c r="F51" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G51" t="s">
         <v>1060</v>
@@ -7845,7 +8105,6 @@
         <v>1061</v>
       </c>
       <c r="I51">
-        <f>974-7656-1972</f>
         <v>-8654</v>
       </c>
       <c r="J51" t="s">
@@ -7868,8 +8127,11 @@
       <c r="D52" s="1">
         <v>43</v>
       </c>
-      <c r="E52" s="2">
-        <v>6000</v>
+      <c r="E52" s="5" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F52" s="5">
+        <v>0</v>
       </c>
       <c r="G52" t="s">
         <v>1062</v>
@@ -7900,13 +8162,13 @@
       <c r="D53" s="1">
         <v>27</v>
       </c>
-      <c r="E53" s="4">
-        <v>7500</v>
-      </c>
-      <c r="F53">
-        <v>500</v>
-      </c>
-      <c r="G53" s="5">
+      <c r="E53" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G53" s="2">
         <v>44567</v>
       </c>
       <c r="H53" t="s">
@@ -7935,11 +8197,11 @@
       <c r="D54" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E54">
-        <v>5200</v>
-      </c>
-      <c r="F54">
-        <v>250</v>
+      <c r="E54" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G54" t="s">
         <v>50</v>
@@ -7948,7 +8210,6 @@
         <v>1066</v>
       </c>
       <c r="I54">
-        <f>974-4176-4361</f>
         <v>-7563</v>
       </c>
       <c r="J54" t="s">
@@ -7971,13 +8232,13 @@
       <c r="D55" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="E55" t="s">
-        <v>48</v>
-      </c>
-      <c r="F55">
-        <v>1250</v>
-      </c>
-      <c r="G55" s="5">
+      <c r="E55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G55" s="2">
         <v>45549</v>
       </c>
       <c r="H55" t="s">
@@ -8006,11 +8267,11 @@
       <c r="D56" s="1">
         <v>30</v>
       </c>
-      <c r="E56" s="4">
-        <v>9000</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
+      <c r="E56" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>1938</v>
       </c>
       <c r="G56" t="s">
         <v>1068</v>
@@ -8038,11 +8299,11 @@
       <c r="D57" s="1">
         <v>49</v>
       </c>
-      <c r="E57" s="2">
-        <v>4800</v>
-      </c>
-      <c r="F57" s="2">
-        <v>1000</v>
+      <c r="E57" s="5" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>1940</v>
       </c>
       <c r="G57" t="s">
         <v>50</v>
@@ -8073,10 +8334,10 @@
       <c r="D58" s="1">
         <v>18</v>
       </c>
-      <c r="E58">
-        <v>6500</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E58" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" t="s">
@@ -8108,10 +8369,10 @@
       <c r="D59" s="1">
         <v>140</v>
       </c>
-      <c r="E59">
-        <v>7200</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E59" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G59" t="s">
@@ -8143,11 +8404,11 @@
       <c r="D60" s="1">
         <v>35</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F60">
-        <v>-200</v>
+      <c r="F60" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G60" t="s">
         <v>1078</v>
@@ -8175,10 +8436,10 @@
       <c r="D61" s="1">
         <v>26</v>
       </c>
-      <c r="E61" s="2">
-        <v>5750</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E61" s="5" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>33</v>
       </c>
       <c r="H61" t="s">
@@ -8207,13 +8468,13 @@
       <c r="D62" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E62">
-        <v>-3000</v>
-      </c>
-      <c r="F62">
-        <v>1250</v>
-      </c>
-      <c r="G62" s="5">
+      <c r="E62" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G62" s="2">
         <v>45140</v>
       </c>
       <c r="H62" t="s">
@@ -8242,11 +8503,11 @@
       <c r="D63" s="1">
         <v>40</v>
       </c>
-      <c r="E63">
-        <v>8000</v>
-      </c>
-      <c r="F63">
-        <v>500</v>
+      <c r="E63" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G63" t="s">
         <v>1084</v>
@@ -8277,10 +8538,10 @@
       <c r="D64" s="1">
         <v>22</v>
       </c>
-      <c r="E64" s="4">
-        <v>6500</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E64" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G64" t="s">
@@ -8312,10 +8573,10 @@
       <c r="D65" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E65" t="s">
-        <v>48</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E65" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G65" t="s">
@@ -8325,7 +8586,6 @@
         <v>1090</v>
       </c>
       <c r="I65">
-        <f>974-6131-4658</f>
         <v>-9815</v>
       </c>
       <c r="J65" t="s">
@@ -8345,10 +8605,10 @@
       <c r="D66" s="1">
         <v>34</v>
       </c>
-      <c r="E66" s="2">
-        <v>9200</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="E66" s="5" t="s">
+        <v>1943</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G66" t="s">
@@ -8380,11 +8640,11 @@
       <c r="D67" s="1">
         <v>29</v>
       </c>
-      <c r="E67">
-        <v>5500</v>
-      </c>
-      <c r="F67" s="2">
-        <v>750</v>
+      <c r="E67" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G67" t="s">
         <v>1092</v>
@@ -8415,11 +8675,11 @@
       <c r="D68" s="1">
         <v>41</v>
       </c>
-      <c r="E68" s="4">
-        <v>7000</v>
-      </c>
-      <c r="F68" s="2">
-        <v>500</v>
+      <c r="E68" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G68" t="s">
         <v>1095</v>
@@ -8450,11 +8710,11 @@
       <c r="D69" s="1">
         <v>250</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F69">
-        <v>300</v>
+      <c r="F69" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G69" t="s">
         <v>1097</v>
@@ -8485,13 +8745,13 @@
       <c r="D70" s="1">
         <v>31</v>
       </c>
-      <c r="E70" s="2">
-        <v>6750</v>
-      </c>
-      <c r="F70">
-        <v>1000</v>
-      </c>
-      <c r="G70" s="5">
+      <c r="E70" s="5" t="s">
+        <v>1945</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G70" s="2">
         <v>44270</v>
       </c>
       <c r="H70" t="s">
@@ -8520,13 +8780,13 @@
       <c r="D71" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="E71">
-        <v>4800</v>
-      </c>
-      <c r="F71">
-        <v>300</v>
-      </c>
-      <c r="G71" s="5">
+      <c r="E71" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G71" s="2">
         <v>43599</v>
       </c>
       <c r="H71" t="s">
@@ -8555,11 +8815,11 @@
       <c r="D72" s="1">
         <v>37</v>
       </c>
-      <c r="E72" s="4">
-        <v>8500</v>
-      </c>
-      <c r="F72">
-        <v>500</v>
+      <c r="E72" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G72" t="s">
         <v>48</v>
@@ -8568,7 +8828,6 @@
         <v>1102</v>
       </c>
       <c r="I72">
-        <f>974-4947-2658</f>
         <v>-6631</v>
       </c>
       <c r="J72" t="s">
@@ -8588,13 +8847,13 @@
       <c r="D73" s="1">
         <v>20</v>
       </c>
-      <c r="E73" t="s">
-        <v>48</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="E73" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="2">
         <v>44532</v>
       </c>
       <c r="H73" t="s">
@@ -8623,8 +8882,11 @@
       <c r="D74" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E74" s="2">
-        <v>5250</v>
+      <c r="E74" s="5" t="s">
+        <v>1947</v>
+      </c>
+      <c r="F74" s="5">
+        <v>0</v>
       </c>
       <c r="G74" t="s">
         <v>1105</v>
@@ -8655,13 +8917,13 @@
       <c r="D75" s="1">
         <v>32</v>
       </c>
-      <c r="E75">
-        <v>6000</v>
-      </c>
-      <c r="F75">
-        <v>250</v>
-      </c>
-      <c r="G75" s="5">
+      <c r="E75" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G75" s="2">
         <v>45376</v>
       </c>
       <c r="H75" t="s">
@@ -8690,13 +8952,13 @@
       <c r="D76" s="1">
         <v>44</v>
       </c>
-      <c r="E76">
-        <v>7200</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E76" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="2">
         <v>44237</v>
       </c>
       <c r="H76" t="s">
@@ -8725,13 +8987,13 @@
       <c r="D77" s="1">
         <v>28</v>
       </c>
-      <c r="E77" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F77">
-        <v>-200</v>
-      </c>
-      <c r="G77" s="5">
+      <c r="E77" s="5" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G77" s="2">
         <v>45601</v>
       </c>
       <c r="H77" t="s">
@@ -8760,17 +9022,16 @@
       <c r="D78" s="1">
         <v>-1</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="5" t="s">
         <v>50</v>
       </c>
       <c r="H78" t="s">
         <v>1111</v>
       </c>
       <c r="I78">
-        <f>974-7015-9325</f>
         <v>-15366</v>
       </c>
       <c r="J78" t="s">
@@ -8793,13 +9054,13 @@
       <c r="D79" s="1">
         <v>39</v>
       </c>
-      <c r="E79">
-        <v>6500</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="E79" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="2">
         <v>45328</v>
       </c>
       <c r="H79" t="s">
@@ -8828,20 +9089,19 @@
       <c r="D80" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E80" s="4">
-        <v>4500</v>
-      </c>
-      <c r="F80">
-        <v>300</v>
-      </c>
-      <c r="G80" s="5">
+      <c r="E80" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G80" s="2">
         <v>45481</v>
       </c>
       <c r="H80" t="s">
         <v>1114</v>
       </c>
       <c r="I80">
-        <f>974-6366-4372</f>
         <v>-9764</v>
       </c>
       <c r="J80" t="s">
@@ -8864,13 +9124,13 @@
       <c r="D81" s="1">
         <v>23</v>
       </c>
-      <c r="E81" t="s">
-        <v>48</v>
-      </c>
-      <c r="F81" s="2">
-        <v>750</v>
-      </c>
-      <c r="G81" s="5">
+      <c r="E81" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G81" s="2">
         <v>44748</v>
       </c>
       <c r="H81" t="s">
@@ -8899,13 +9159,13 @@
       <c r="D82" s="1">
         <v>36</v>
       </c>
-      <c r="E82" s="2">
-        <v>7800</v>
-      </c>
-      <c r="F82">
-        <v>1250</v>
-      </c>
-      <c r="G82" s="5">
+      <c r="E82" s="5" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G82" s="2">
         <v>45575</v>
       </c>
       <c r="H82" t="s">
@@ -8934,13 +9194,13 @@
       <c r="D83" s="1">
         <v>45</v>
       </c>
-      <c r="E83" s="4">
-        <v>5500</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E83" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="2">
         <v>44584</v>
       </c>
       <c r="H83" t="s">
@@ -8963,13 +9223,13 @@
       <c r="D84" s="1">
         <v>19</v>
       </c>
-      <c r="E84">
-        <v>-1500</v>
-      </c>
-      <c r="F84" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G84" s="5">
+      <c r="E84" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G84" s="2">
         <v>44353</v>
       </c>
       <c r="H84" t="s">
@@ -8998,13 +9258,13 @@
       <c r="D85" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E85">
-        <v>9000</v>
-      </c>
-      <c r="F85">
-        <v>1250</v>
-      </c>
-      <c r="G85" s="5">
+      <c r="E85" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G85" s="2">
         <v>45208</v>
       </c>
       <c r="H85" t="s">
@@ -9033,20 +9293,19 @@
       <c r="D86" s="1">
         <v>52</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F86" s="2">
-        <v>750</v>
-      </c>
-      <c r="G86" s="5">
+      <c r="F86" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G86" s="2">
         <v>44073</v>
       </c>
       <c r="H86" t="s">
         <v>1122</v>
       </c>
       <c r="I86">
-        <f>974-5655-8022</f>
         <v>-12703</v>
       </c>
       <c r="J86" t="s">
@@ -9069,13 +9328,13 @@
       <c r="D87" s="1">
         <v>33</v>
       </c>
-      <c r="E87" s="2">
-        <v>6200</v>
-      </c>
-      <c r="F87">
-        <v>1000</v>
-      </c>
-      <c r="G87" s="5">
+      <c r="E87" s="5" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G87" s="2">
         <v>45401</v>
       </c>
       <c r="H87" t="s">
@@ -9104,13 +9363,13 @@
       <c r="D88" s="1">
         <v>160</v>
       </c>
-      <c r="E88">
-        <v>7500</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="E88" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G88" s="5">
+      <c r="G88" s="2">
         <v>44295</v>
       </c>
       <c r="H88" t="s">
@@ -9139,11 +9398,11 @@
       <c r="D89" s="1">
         <v>27</v>
       </c>
-      <c r="E89" t="s">
-        <v>48</v>
-      </c>
-      <c r="F89">
-        <v>300</v>
+      <c r="E89" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G89" t="s">
         <v>1125</v>
@@ -9174,13 +9433,13 @@
       <c r="D90" s="1">
         <v>30</v>
       </c>
-      <c r="E90" s="2">
-        <v>8000</v>
-      </c>
-      <c r="F90">
-        <v>-200</v>
-      </c>
-      <c r="G90" s="5">
+      <c r="E90" s="5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G90" s="2">
         <v>43600</v>
       </c>
       <c r="H90" t="s">
@@ -9209,10 +9468,10 @@
       <c r="D91" s="1">
         <v>42</v>
       </c>
-      <c r="E91">
-        <v>5200</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="E91" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G91" t="s">
@@ -9244,10 +9503,10 @@
       <c r="D92" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E92">
-        <v>6500</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="E92" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G92" t="s">
@@ -9279,11 +9538,11 @@
       <c r="D93" s="1">
         <v>24</v>
       </c>
-      <c r="E93" s="2">
-        <v>9500</v>
-      </c>
-      <c r="F93">
-        <v>500</v>
+      <c r="E93" s="5" t="s">
+        <v>1953</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G93" t="s">
         <v>1133</v>
@@ -9314,13 +9573,13 @@
       <c r="D94" s="1">
         <v>38</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F94">
-        <v>1250</v>
-      </c>
-      <c r="G94" s="5">
+      <c r="F94" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G94" s="2">
         <v>44414</v>
       </c>
       <c r="H94" t="s">
@@ -9349,11 +9608,11 @@
       <c r="D95" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E95">
-        <v>5800</v>
-      </c>
-      <c r="F95" s="2">
-        <v>500</v>
+      <c r="E95" s="5" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G95" t="s">
         <v>1137</v>
@@ -9384,13 +9643,13 @@
       <c r="D96" s="1">
         <v>35</v>
       </c>
-      <c r="E96" s="4">
-        <v>7200</v>
-      </c>
-      <c r="F96" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G96" s="5">
+      <c r="E96" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G96" s="2">
         <v>44113</v>
       </c>
       <c r="H96" t="s">
@@ -9419,13 +9678,13 @@
       <c r="D97" s="1">
         <v>29</v>
       </c>
-      <c r="E97" t="s">
-        <v>48</v>
-      </c>
-      <c r="F97" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G97" s="5">
+      <c r="E97" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G97" s="2">
         <v>43761</v>
       </c>
       <c r="H97" t="s">
@@ -9451,13 +9710,13 @@
       <c r="D98" s="1">
         <v>47</v>
       </c>
-      <c r="E98" s="2">
-        <v>5000</v>
-      </c>
-      <c r="F98">
-        <v>250</v>
-      </c>
-      <c r="G98" s="5">
+      <c r="E98" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G98" s="2">
         <v>43466</v>
       </c>
       <c r="H98" t="s">
@@ -9486,11 +9745,11 @@
       <c r="D99" s="1">
         <v>21</v>
       </c>
-      <c r="E99">
-        <v>8200</v>
-      </c>
-      <c r="F99">
-        <v>250</v>
+      <c r="E99" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G99" t="s">
         <v>1144</v>
@@ -9521,11 +9780,11 @@
       <c r="D100" s="1">
         <v>-8</v>
       </c>
-      <c r="E100">
-        <v>-500</v>
-      </c>
-      <c r="F100">
-        <v>750</v>
+      <c r="E100" s="5" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G100" t="s">
         <v>1137</v>
@@ -9556,11 +9815,11 @@
       <c r="D101" s="1">
         <v>31</v>
       </c>
-      <c r="E101" s="2">
-        <v>6500</v>
-      </c>
-      <c r="F101">
-        <v>500</v>
+      <c r="E101" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G101" t="s">
         <v>1148</v>
@@ -9591,20 +9850,19 @@
       <c r="D102" s="1">
         <v>40</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F102" s="2">
-        <v>500</v>
-      </c>
-      <c r="G102" s="5">
+      <c r="F102" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G102" s="2">
         <v>45471</v>
       </c>
       <c r="H102" t="s">
         <v>1151</v>
       </c>
       <c r="I102">
-        <f>974-7583-3609</f>
         <v>-10218</v>
       </c>
       <c r="J102" t="s">
@@ -9627,11 +9885,11 @@
       <c r="D103" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E103">
-        <v>7200</v>
-      </c>
-      <c r="F103">
-        <v>1000</v>
+      <c r="E103" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G103" t="s">
         <v>1152</v>
@@ -9659,11 +9917,11 @@
       <c r="D104" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="E104" s="2">
-        <v>4750</v>
-      </c>
-      <c r="F104">
-        <v>250</v>
+      <c r="E104" s="5" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G104" t="s">
         <v>1154</v>
@@ -9694,13 +9952,13 @@
       <c r="D105" s="1">
         <v>34</v>
       </c>
-      <c r="E105">
-        <v>6000</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="E105" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F105" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="2">
         <v>45043</v>
       </c>
       <c r="H105" t="s">
@@ -9729,10 +9987,10 @@
       <c r="D106" s="1">
         <v>43</v>
       </c>
-      <c r="E106" t="s">
-        <v>48</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="E106" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G106" t="s">
@@ -9761,11 +10019,11 @@
       <c r="D107" s="1">
         <v>26</v>
       </c>
-      <c r="E107" s="2">
-        <v>8900</v>
-      </c>
-      <c r="F107">
-        <v>500</v>
+      <c r="E107" s="5" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G107" t="s">
         <v>1163</v>
@@ -9774,7 +10032,6 @@
         <v>1164</v>
       </c>
       <c r="I107">
-        <f>974-4077-6878</f>
         <v>-9981</v>
       </c>
       <c r="J107" t="s">
@@ -9797,17 +10054,16 @@
       <c r="D108" s="1">
         <v>18</v>
       </c>
-      <c r="E108" s="4">
-        <v>5500</v>
-      </c>
-      <c r="F108" s="2">
-        <v>500</v>
+      <c r="E108" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="H108" t="s">
         <v>1165</v>
       </c>
       <c r="I108">
-        <f>974-7672-8067</f>
         <v>-14765</v>
       </c>
       <c r="J108" t="s">
@@ -9830,13 +10086,13 @@
       <c r="D109" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E109">
-        <v>7000</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="E109" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F109" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="2">
         <v>45509</v>
       </c>
       <c r="H109" t="s">
@@ -9865,11 +10121,11 @@
       <c r="D110" s="1">
         <v>56</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F110">
-        <v>1000</v>
+      <c r="F110" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G110" t="s">
         <v>1168</v>
@@ -9900,10 +10156,10 @@
       <c r="D111" s="1">
         <v>32</v>
       </c>
-      <c r="E111" s="2">
-        <v>6250</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="E111" s="5" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F111" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G111" t="s">
@@ -9935,20 +10191,19 @@
       <c r="D112" s="1">
         <v>145</v>
       </c>
-      <c r="E112">
-        <v>4800</v>
-      </c>
-      <c r="F112">
-        <v>250</v>
-      </c>
-      <c r="G112" s="5">
+      <c r="E112" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G112" s="2">
         <v>44633</v>
       </c>
       <c r="H112" t="s">
         <v>1174</v>
       </c>
       <c r="I112">
-        <f>974-3760-6321</f>
         <v>-9107</v>
       </c>
       <c r="J112" t="s">
@@ -9971,13 +10226,13 @@
       <c r="D113" s="1">
         <v>25</v>
       </c>
-      <c r="E113" s="4">
-        <v>9000</v>
-      </c>
-      <c r="F113">
-        <v>0</v>
-      </c>
-      <c r="G113" s="5">
+      <c r="E113" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G113" s="2">
         <v>44060</v>
       </c>
       <c r="H113" t="s">
@@ -10006,10 +10261,10 @@
       <c r="D114" s="1">
         <v>39</v>
       </c>
-      <c r="E114" t="s">
-        <v>48</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="E114" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F114" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G114" t="s">
@@ -10041,13 +10296,13 @@
       <c r="D115" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E115" s="2">
-        <v>7500</v>
-      </c>
-      <c r="F115">
-        <v>1250</v>
-      </c>
-      <c r="G115" s="5">
+      <c r="E115" s="5" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G115" s="2">
         <v>44646</v>
       </c>
       <c r="H115" t="s">
@@ -10076,13 +10331,13 @@
       <c r="D116" s="1">
         <v>30</v>
       </c>
-      <c r="E116">
-        <v>6500</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="E116" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F116" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G116" s="5">
+      <c r="G116" s="2">
         <v>43971</v>
       </c>
       <c r="H116" t="s">
@@ -10111,11 +10366,11 @@
       <c r="D117" s="1">
         <v>48</v>
       </c>
-      <c r="E117">
-        <v>-2000</v>
-      </c>
-      <c r="F117">
-        <v>-200</v>
+      <c r="E117" s="5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G117" t="s">
         <v>1182</v>
@@ -10146,11 +10401,11 @@
       <c r="D118" s="1">
         <v>22</v>
       </c>
-      <c r="E118" s="2">
-        <v>5750</v>
-      </c>
-      <c r="F118">
-        <v>500</v>
+      <c r="E118" s="5" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G118" t="s">
         <v>1185</v>
@@ -10181,13 +10436,13 @@
       <c r="D119" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F119">
-        <v>1250</v>
-      </c>
-      <c r="G119" s="5">
+      <c r="F119" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G119" s="2">
         <v>44427</v>
       </c>
       <c r="H119" t="s">
@@ -10216,13 +10471,13 @@
       <c r="D120" s="1">
         <v>37</v>
       </c>
-      <c r="E120">
-        <v>8000</v>
-      </c>
-      <c r="F120">
-        <v>500</v>
-      </c>
-      <c r="G120" s="5">
+      <c r="E120" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G120" s="2">
         <v>45601</v>
       </c>
       <c r="H120" t="s">
@@ -10251,20 +10506,19 @@
       <c r="D121" s="1">
         <v>28</v>
       </c>
-      <c r="E121" s="2">
-        <v>6800</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="E121" s="5" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F121" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G121" s="5">
+      <c r="G121" s="2">
         <v>45635</v>
       </c>
       <c r="H121" t="s">
         <v>1192</v>
       </c>
       <c r="I121">
-        <f>974-5371-2208</f>
         <v>-6605</v>
       </c>
       <c r="J121" t="s">
@@ -10287,10 +10541,10 @@
       <c r="D122" s="1">
         <v>41</v>
       </c>
-      <c r="E122">
-        <v>5200</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="E122" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F122" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G122" t="s">
@@ -10322,10 +10576,10 @@
       <c r="D123" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E123" t="s">
-        <v>48</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="E123" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G123" t="s">
@@ -10335,7 +10589,6 @@
         <v>1197</v>
       </c>
       <c r="I123">
-        <f>974-4609-2392</f>
         <v>-6027</v>
       </c>
       <c r="J123" t="s">
@@ -10358,10 +10611,10 @@
       <c r="D124" s="1">
         <v>19</v>
       </c>
-      <c r="E124" s="2">
-        <v>9250</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="E124" s="5" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G124" t="s">
@@ -10393,13 +10646,13 @@
       <c r="D125" s="1">
         <v>35</v>
       </c>
-      <c r="E125">
-        <v>7000</v>
-      </c>
-      <c r="F125">
-        <v>750</v>
-      </c>
-      <c r="G125" s="5">
+      <c r="E125" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G125" s="2">
         <v>44502</v>
       </c>
       <c r="H125" t="s">
@@ -10428,20 +10681,19 @@
       <c r="D126" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E126">
-        <v>4500</v>
-      </c>
-      <c r="F126">
-        <v>750</v>
-      </c>
-      <c r="G126" s="5">
+      <c r="E126" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G126" s="2">
         <v>44508</v>
       </c>
       <c r="H126" t="s">
         <v>1201</v>
       </c>
       <c r="I126">
-        <f>974-6803-1824</f>
         <v>-7653</v>
       </c>
       <c r="K126" t="s">
@@ -10461,11 +10713,11 @@
       <c r="D127" s="1">
         <v>33</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F127">
-        <v>750</v>
+      <c r="F127" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G127" t="s">
         <v>1202</v>
@@ -10474,7 +10726,6 @@
         <v>1079</v>
       </c>
       <c r="I127">
-        <f>974-6419-2081</f>
         <v>-7526</v>
       </c>
       <c r="J127" t="s">
@@ -10497,11 +10748,11 @@
       <c r="D128" s="1">
         <v>-3</v>
       </c>
-      <c r="E128" s="2">
-        <v>5500</v>
-      </c>
-      <c r="F128">
-        <v>1000</v>
+      <c r="E128" s="5" t="s">
+        <v>1924</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G128" t="s">
         <v>1203</v>
@@ -10532,10 +10783,10 @@
       <c r="D129" s="1">
         <v>46</v>
       </c>
-      <c r="E129">
-        <v>7500</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="E129" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G129" t="s">
@@ -10567,10 +10818,10 @@
       <c r="D130" s="1">
         <v>24</v>
       </c>
-      <c r="E130" s="4">
-        <v>6250</v>
-      </c>
-      <c r="F130" t="s">
+      <c r="E130" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G130" t="s">
@@ -10602,10 +10853,13 @@
       <c r="D131" s="1">
         <v>31</v>
       </c>
-      <c r="E131" t="s">
-        <v>48</v>
-      </c>
-      <c r="G131" s="5">
+      <c r="E131" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F131" s="5">
+        <v>0</v>
+      </c>
+      <c r="G131" s="2">
         <v>44708</v>
       </c>
       <c r="H131" t="s">
@@ -10634,13 +10888,13 @@
       <c r="D132" s="1">
         <v>40</v>
       </c>
-      <c r="E132" s="2">
-        <v>8000</v>
-      </c>
-      <c r="F132">
-        <v>250</v>
-      </c>
-      <c r="G132" s="5">
+      <c r="E132" s="5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G132" s="2">
         <v>45611</v>
       </c>
       <c r="H132" t="s">
@@ -10669,11 +10923,11 @@
       <c r="D133" s="1">
         <v>29</v>
       </c>
-      <c r="E133">
-        <v>-750</v>
-      </c>
-      <c r="F133">
-        <v>500</v>
+      <c r="E133" s="5" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G133" t="s">
         <v>1212</v>
@@ -10704,13 +10958,13 @@
       <c r="D134" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E134" s="2">
-        <v>7200</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="E134" s="5" t="s">
+        <v>1966</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="G134" s="5">
+      <c r="G134" s="2">
         <v>44988</v>
       </c>
       <c r="H134" t="s">
@@ -10739,10 +10993,10 @@
       <c r="D135" s="1">
         <v>170</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G135" t="s">
@@ -10774,13 +11028,13 @@
       <c r="D136" s="1">
         <v>36</v>
       </c>
-      <c r="E136">
-        <v>5500</v>
-      </c>
-      <c r="F136" s="2">
-        <v>500</v>
-      </c>
-      <c r="G136" s="5">
+      <c r="E136" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G136" s="2">
         <v>44052</v>
       </c>
       <c r="H136" t="s">
@@ -10809,11 +11063,11 @@
       <c r="D137" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="E137" s="2">
-        <v>9000</v>
-      </c>
-      <c r="F137">
-        <v>-200</v>
+      <c r="E137" s="5" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G137" t="s">
         <v>1221</v>
@@ -10822,7 +11076,6 @@
         <v>1222</v>
       </c>
       <c r="I137">
-        <f>974-3175-6106</f>
         <v>-8307</v>
       </c>
       <c r="J137" t="s">
@@ -10845,13 +11098,13 @@
       <c r="D138" s="1">
         <v>27</v>
       </c>
-      <c r="E138">
-        <v>6200</v>
-      </c>
-      <c r="F138">
-        <v>-50</v>
-      </c>
-      <c r="G138" s="5">
+      <c r="E138" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G138" s="2">
         <v>43608</v>
       </c>
       <c r="H138" t="s">
@@ -10880,11 +11133,11 @@
       <c r="D139" s="1">
         <v>44</v>
       </c>
-      <c r="E139" t="s">
-        <v>48</v>
-      </c>
-      <c r="F139">
-        <v>-200</v>
+      <c r="E139" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G139" t="s">
         <v>1225</v>
@@ -10915,13 +11168,13 @@
       <c r="D140" s="1">
         <v>21</v>
       </c>
-      <c r="E140" s="2">
-        <v>4800</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="E140" s="5" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F140" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G140" s="5">
+      <c r="G140" s="2">
         <v>44912</v>
       </c>
       <c r="H140" t="s">
@@ -10950,11 +11203,11 @@
       <c r="D141" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E141">
-        <v>7200</v>
-      </c>
-      <c r="F141" s="2">
-        <v>500</v>
+      <c r="E141" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G141" t="s">
         <v>1229</v>
@@ -10985,13 +11238,13 @@
       <c r="D142" s="1">
         <v>38</v>
       </c>
-      <c r="E142" s="2">
-        <v>6500</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="E142" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="F142" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="G142" s="5">
+      <c r="G142" s="2">
         <v>44042</v>
       </c>
       <c r="H142" t="s">
@@ -11020,13 +11273,13 @@
       <c r="D143" s="1">
         <v>32</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F143" t="s">
-        <v>48</v>
-      </c>
-      <c r="G143" s="5">
+      <c r="F143" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G143" s="2">
         <v>45191</v>
       </c>
       <c r="H143" t="s">
@@ -11055,13 +11308,13 @@
       <c r="D144" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E144">
-        <v>8500</v>
-      </c>
-      <c r="F144" t="s">
-        <v>48</v>
-      </c>
-      <c r="G144" s="5">
+      <c r="E144" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G144" s="2">
         <v>45119</v>
       </c>
       <c r="H144" t="s">
@@ -11090,10 +11343,10 @@
       <c r="D145" s="1">
         <v>25</v>
       </c>
-      <c r="E145">
-        <v>5250</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="E145" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F145" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="G145" t="s">
@@ -11103,7 +11356,6 @@
         <v>1239</v>
       </c>
       <c r="I145">
-        <f>974-7810-4322</f>
         <v>-11158</v>
       </c>
       <c r="K145" t="s">
@@ -11123,13 +11375,13 @@
       <c r="D146" s="1">
         <v>43</v>
       </c>
-      <c r="E146">
-        <v>6000</v>
-      </c>
-      <c r="F146">
-        <v>1000</v>
-      </c>
-      <c r="G146" s="5">
+      <c r="E146" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G146" s="2">
         <v>43656</v>
       </c>
       <c r="H146" t="s">
@@ -11158,8 +11410,11 @@
       <c r="D147" s="1">
         <v>30</v>
       </c>
-      <c r="E147" t="s">
-        <v>48</v>
+      <c r="E147" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F147" s="5">
+        <v>0</v>
       </c>
       <c r="G147" t="s">
         <v>1242</v>
@@ -11190,10 +11445,10 @@
       <c r="D148" s="1">
         <v>15</v>
       </c>
-      <c r="E148">
-        <v>7750</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="E148" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F148" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G148" t="s">
@@ -11225,13 +11480,13 @@
       <c r="D149" s="1">
         <v>49</v>
       </c>
-      <c r="E149">
-        <v>4800</v>
-      </c>
-      <c r="F149">
-        <v>500</v>
-      </c>
-      <c r="G149" s="5">
+      <c r="E149" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G149" s="2">
         <v>45564</v>
       </c>
       <c r="H149" t="s">
@@ -11260,11 +11515,11 @@
       <c r="D150" s="1">
         <v>34</v>
       </c>
-      <c r="E150">
-        <v>-4000</v>
-      </c>
-      <c r="F150">
-        <v>750</v>
+      <c r="E150" s="5" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G150" t="s">
         <v>1248</v>
@@ -11292,20 +11547,19 @@
       <c r="D151" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E151">
-        <v>6000</v>
-      </c>
-      <c r="F151">
-        <v>-200</v>
-      </c>
-      <c r="G151" s="5">
+      <c r="E151" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G151" s="2">
         <v>45354</v>
       </c>
       <c r="H151" t="s">
         <v>1250</v>
       </c>
       <c r="I151">
-        <f>974-4309-1345</f>
         <v>-4680</v>
       </c>
       <c r="J151" t="s">
@@ -11328,10 +11582,10 @@
       <c r="D152" s="1">
         <v>37</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F152" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G152" t="s">
@@ -11363,10 +11617,10 @@
       <c r="D153" s="1">
         <v>28</v>
       </c>
-      <c r="E153">
-        <v>9000</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="E153" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F153" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G153" t="s">
@@ -11398,11 +11652,11 @@
       <c r="D154" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E154">
-        <v>5500</v>
-      </c>
-      <c r="F154">
-        <v>-200</v>
+      <c r="E154" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G154" t="s">
         <v>48</v>
@@ -11433,11 +11687,11 @@
       <c r="D155" s="1">
         <v>41</v>
       </c>
-      <c r="E155">
-        <v>6500</v>
-      </c>
-      <c r="F155">
-        <v>250</v>
+      <c r="E155" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G155" t="s">
         <v>1257</v>
@@ -11468,11 +11722,11 @@
       <c r="D156" s="1">
         <v>23</v>
       </c>
-      <c r="E156" t="s">
-        <v>48</v>
-      </c>
-      <c r="F156">
-        <v>500</v>
+      <c r="E156" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G156" t="s">
         <v>1260</v>
@@ -11503,10 +11757,10 @@
       <c r="D157" s="1">
         <v>135</v>
       </c>
-      <c r="E157">
-        <v>8200</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="E157" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G157" t="s">
@@ -11516,7 +11770,6 @@
         <v>1264</v>
       </c>
       <c r="I157">
-        <f>974-4119-5778</f>
         <v>-8923</v>
       </c>
       <c r="K157" t="s">
@@ -11536,13 +11789,13 @@
       <c r="D158" s="1">
         <v>31</v>
       </c>
-      <c r="E158">
-        <v>5200</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="E158" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F158" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G158" s="5">
+      <c r="G158" s="2">
         <v>43659</v>
       </c>
       <c r="H158" t="s">
@@ -11571,10 +11824,10 @@
       <c r="D159" s="1">
         <v>45</v>
       </c>
-      <c r="E159">
-        <v>7000</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="E159" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F159" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G159" t="s">
@@ -11606,11 +11859,11 @@
       <c r="D160" s="1">
         <v>26</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F160">
-        <v>750</v>
+      <c r="F160" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G160" t="s">
         <v>1270</v>
@@ -11641,13 +11894,13 @@
       <c r="D161" s="1">
         <v>39</v>
       </c>
-      <c r="E161">
-        <v>6750</v>
-      </c>
-      <c r="F161" t="s">
+      <c r="E161" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F161" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G161" s="5">
+      <c r="G161" s="2">
         <v>44451</v>
       </c>
       <c r="H161" t="s">
@@ -11676,13 +11929,13 @@
       <c r="D162" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E162">
-        <v>4500</v>
-      </c>
-      <c r="F162">
-        <v>750</v>
-      </c>
-      <c r="G162" s="5">
+      <c r="E162" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G162" s="2">
         <v>45632</v>
       </c>
       <c r="H162" t="s">
@@ -11711,10 +11964,10 @@
       <c r="D163" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="E163" t="s">
-        <v>48</v>
-      </c>
-      <c r="F163" t="s">
+      <c r="E163" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G163" t="s">
@@ -11746,10 +11999,10 @@
       <c r="D164" s="1">
         <v>33</v>
       </c>
-      <c r="E164">
-        <v>9500</v>
-      </c>
-      <c r="F164" t="s">
+      <c r="E164" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F164" s="5" t="s">
         <v>1010</v>
       </c>
       <c r="G164" t="s">
@@ -11781,17 +12034,19 @@
       <c r="D165" s="1">
         <v>20</v>
       </c>
-      <c r="E165">
-        <v>6000</v>
-      </c>
-      <c r="G165" s="5">
+      <c r="E165" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F165" s="5">
+        <v>0</v>
+      </c>
+      <c r="G165" s="2">
         <v>44053</v>
       </c>
       <c r="H165" t="s">
         <v>1279</v>
       </c>
       <c r="I165">
-        <f>974-3580-1261</f>
         <v>-3867</v>
       </c>
       <c r="J165" t="s">
@@ -11814,10 +12069,10 @@
       <c r="D166" s="1">
         <v>42</v>
       </c>
-      <c r="E166">
-        <v>7200</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="E166" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G166" t="s">
@@ -11846,13 +12101,13 @@
       <c r="D167" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E167">
-        <v>5000</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="E167" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F167" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G167" s="5">
+      <c r="G167" s="2">
         <v>45624</v>
       </c>
       <c r="H167" t="s">
@@ -11881,13 +12136,13 @@
       <c r="D168" s="1">
         <v>29</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F168">
-        <v>-50</v>
-      </c>
-      <c r="G168" s="5">
+      <c r="F168" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G168" s="2">
         <v>45100</v>
       </c>
       <c r="H168" t="s">
@@ -11916,13 +12171,13 @@
       <c r="D169" s="1">
         <v>36</v>
       </c>
-      <c r="E169">
-        <v>8200</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="E169" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F169" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G169" s="5">
+      <c r="G169" s="2">
         <v>44014</v>
       </c>
       <c r="H169" t="s">
@@ -11951,11 +12206,11 @@
       <c r="D170" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E170" t="s">
-        <v>48</v>
-      </c>
-      <c r="F170">
-        <v>300</v>
+      <c r="E170" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G170" t="s">
         <v>1286</v>
@@ -11964,7 +12219,6 @@
         <v>1287</v>
       </c>
       <c r="I170">
-        <f>974-6166-3886</f>
         <v>-9078</v>
       </c>
       <c r="J170" t="s">
@@ -11987,11 +12241,11 @@
       <c r="D171" s="1">
         <v>-6</v>
       </c>
-      <c r="E171">
-        <v>7250</v>
-      </c>
-      <c r="F171">
-        <v>250</v>
+      <c r="E171" s="5" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G171" t="s">
         <v>1288</v>
@@ -12000,7 +12254,6 @@
         <v>1289</v>
       </c>
       <c r="I171">
-        <f>974-4572-7261</f>
         <v>-10859</v>
       </c>
       <c r="J171" t="s">
@@ -12023,10 +12276,10 @@
       <c r="D172" s="1">
         <v>47</v>
       </c>
-      <c r="E172">
-        <v>5500</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="E172" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F172" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G172" t="s">
@@ -12058,10 +12311,10 @@
       <c r="D173" s="1">
         <v>25</v>
       </c>
-      <c r="E173">
-        <v>-1000</v>
-      </c>
-      <c r="F173" t="s">
+      <c r="E173" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F173" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G173" t="s">
@@ -12093,11 +12346,11 @@
       <c r="D174" s="1">
         <v>30</v>
       </c>
-      <c r="E174">
-        <v>6500</v>
-      </c>
-      <c r="F174" s="2">
-        <v>1000</v>
+      <c r="E174" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>1940</v>
       </c>
       <c r="G174" t="s">
         <v>51</v>
@@ -12128,20 +12381,19 @@
       <c r="D175" s="1">
         <v>40</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F175" t="s">
-        <v>48</v>
-      </c>
-      <c r="G175" s="5">
+      <c r="F175" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G175" s="2">
         <v>44912</v>
       </c>
       <c r="H175" t="s">
         <v>1296</v>
       </c>
       <c r="I175">
-        <f>974-3608-9364</f>
         <v>-11998</v>
       </c>
       <c r="J175" t="s">
@@ -12164,10 +12416,10 @@
       <c r="D176" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E176">
-        <v>9000</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="E176" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F176" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G176" t="s">
@@ -12199,13 +12451,13 @@
       <c r="D177" s="1">
         <v>22</v>
       </c>
-      <c r="E177">
-        <v>4750</v>
-      </c>
-      <c r="F177">
-        <v>500</v>
-      </c>
-      <c r="G177" s="5">
+      <c r="E177" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G177" s="2">
         <v>44842</v>
       </c>
       <c r="H177" t="s">
@@ -12234,13 +12486,13 @@
       <c r="D178" s="1">
         <v>34</v>
       </c>
-      <c r="E178">
-        <v>6800</v>
-      </c>
-      <c r="F178" t="s">
-        <v>48</v>
-      </c>
-      <c r="G178" s="5">
+      <c r="E178" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G178" s="2">
         <v>44599</v>
       </c>
       <c r="H178" t="s">
@@ -12269,10 +12521,10 @@
       <c r="D179" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E179" t="s">
-        <v>48</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="E179" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F179" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G179" t="s">
@@ -12282,7 +12534,6 @@
         <v>1305</v>
       </c>
       <c r="I179">
-        <f>974-5456-8226</f>
         <v>-12708</v>
       </c>
       <c r="J179" t="s">
@@ -12305,13 +12556,13 @@
       <c r="D180" s="1">
         <v>180</v>
       </c>
-      <c r="E180">
-        <v>8500</v>
-      </c>
-      <c r="F180">
-        <v>750</v>
-      </c>
-      <c r="G180" s="5">
+      <c r="E180" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G180" s="2">
         <v>44141</v>
       </c>
       <c r="H180" t="s">
@@ -12340,11 +12591,11 @@
       <c r="D181" s="1">
         <v>27</v>
       </c>
-      <c r="E181">
-        <v>5200</v>
-      </c>
-      <c r="F181">
-        <v>500</v>
+      <c r="E181" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G181" t="s">
         <v>1307</v>
@@ -12375,13 +12626,13 @@
       <c r="D182" s="1">
         <v>38</v>
       </c>
-      <c r="E182">
-        <v>7000</v>
-      </c>
-      <c r="F182">
-        <v>300</v>
-      </c>
-      <c r="G182" s="5">
+      <c r="E182" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G182" s="2">
         <v>45169</v>
       </c>
       <c r="H182" t="s">
@@ -12410,13 +12661,13 @@
       <c r="D183" s="1">
         <v>31</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F183">
-        <v>250</v>
-      </c>
-      <c r="G183" s="5">
+      <c r="F183" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G183" s="2">
         <v>43648</v>
       </c>
       <c r="H183" t="s">
@@ -12445,20 +12696,19 @@
       <c r="D184" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="E184">
-        <v>6000</v>
-      </c>
-      <c r="F184">
-        <v>750</v>
-      </c>
-      <c r="G184" s="5">
+      <c r="E184" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G184" s="2">
         <v>45171</v>
       </c>
       <c r="H184" t="s">
         <v>1313</v>
       </c>
       <c r="I184">
-        <f>974-5084-8026</f>
         <v>-12136</v>
       </c>
       <c r="J184" t="s">
@@ -12478,13 +12728,13 @@
       <c r="D185" s="1">
         <v>44</v>
       </c>
-      <c r="E185">
-        <v>5750</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="E185" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F185" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G185" s="5">
+      <c r="G185" s="2">
         <v>43776</v>
       </c>
       <c r="H185" t="s">
@@ -12513,13 +12763,13 @@
       <c r="D186" s="1">
         <v>19</v>
       </c>
-      <c r="E186" t="s">
-        <v>48</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="E186" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F186" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G186" s="5">
+      <c r="G186" s="2">
         <v>45146</v>
       </c>
       <c r="H186" t="s">
@@ -12548,13 +12798,13 @@
       <c r="D187" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E187">
-        <v>7500</v>
-      </c>
-      <c r="F187" t="s">
+      <c r="E187" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F187" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G187" s="5">
+      <c r="G187" s="2">
         <v>44113</v>
       </c>
       <c r="H187" t="s">
@@ -12583,13 +12833,13 @@
       <c r="D188" s="1">
         <v>35</v>
       </c>
-      <c r="E188">
-        <v>-2500</v>
-      </c>
-      <c r="F188" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G188" s="5">
+      <c r="E188" s="5" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G188" s="2">
         <v>43575</v>
       </c>
       <c r="H188" t="s">
@@ -12618,11 +12868,11 @@
       <c r="D189" s="1">
         <v>29</v>
       </c>
-      <c r="E189">
-        <v>9200</v>
-      </c>
-      <c r="F189">
-        <v>1000</v>
+      <c r="E189" s="5" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G189" t="s">
         <v>1318</v>
@@ -12653,11 +12903,11 @@
       <c r="D190" s="1">
         <v>42</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F190">
-        <v>1000</v>
+      <c r="F190" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G190" t="s">
         <v>1320</v>
@@ -12688,11 +12938,11 @@
       <c r="D191" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E191">
-        <v>6500</v>
-      </c>
-      <c r="F191">
-        <v>250</v>
+      <c r="E191" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G191" t="s">
         <v>1323</v>
@@ -12723,10 +12973,10 @@
       <c r="D192" s="1">
         <v>24</v>
       </c>
-      <c r="E192">
-        <v>6250</v>
-      </c>
-      <c r="F192" t="s">
+      <c r="E192" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F192" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G192" t="s">
@@ -12736,7 +12986,6 @@
         <v>1326</v>
       </c>
       <c r="I192">
-        <f>974-5065-5995</f>
         <v>-10086</v>
       </c>
       <c r="K192" t="s">
@@ -12756,8 +13005,11 @@
       <c r="D193" s="1">
         <v>37</v>
       </c>
-      <c r="E193">
-        <v>4800</v>
+      <c r="E193" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F193" s="5">
+        <v>0</v>
       </c>
       <c r="G193" t="s">
         <v>1327</v>
@@ -12766,7 +13018,6 @@
         <v>1328</v>
       </c>
       <c r="I193">
-        <f>974-6461-6902</f>
         <v>-12389</v>
       </c>
       <c r="J193" t="s">
@@ -12789,13 +13040,13 @@
       <c r="D194" s="1">
         <v>16</v>
       </c>
-      <c r="E194" t="s">
-        <v>48</v>
-      </c>
-      <c r="F194">
-        <v>250</v>
-      </c>
-      <c r="G194" s="5">
+      <c r="E194" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G194" s="2">
         <v>44758</v>
       </c>
       <c r="H194" t="s">
@@ -12824,10 +13075,10 @@
       <c r="D195" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E195">
-        <v>8000</v>
-      </c>
-      <c r="F195" t="s">
+      <c r="E195" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F195" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G195" t="s">
@@ -12859,11 +13110,11 @@
       <c r="D196" s="1">
         <v>33</v>
       </c>
-      <c r="E196">
-        <v>5500</v>
-      </c>
-      <c r="F196">
-        <v>500</v>
+      <c r="E196" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G196" t="s">
         <v>1333</v>
@@ -12872,7 +13123,6 @@
         <v>1334</v>
       </c>
       <c r="I196">
-        <f>974-3131-1256</f>
         <v>-3413</v>
       </c>
       <c r="J196" t="s">
@@ -12895,11 +13145,11 @@
       <c r="D197" s="1">
         <v>41</v>
       </c>
-      <c r="E197">
-        <v>7500</v>
-      </c>
-      <c r="F197">
-        <v>250</v>
+      <c r="E197" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G197" t="s">
         <v>1335</v>
@@ -12930,20 +13180,19 @@
       <c r="D198" s="1">
         <v>28</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F198">
-        <v>0</v>
-      </c>
-      <c r="G198" s="5">
+      <c r="F198" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G198" s="2">
         <v>44657</v>
       </c>
       <c r="H198" t="s">
         <v>1337</v>
       </c>
       <c r="I198">
-        <f>974-3314-4764</f>
         <v>-7104</v>
       </c>
       <c r="J198" t="s">
@@ -12966,11 +13215,11 @@
       <c r="D199" s="1">
         <v>-4</v>
       </c>
-      <c r="E199">
-        <v>7200</v>
-      </c>
-      <c r="F199">
-        <v>1000</v>
+      <c r="E199" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G199" t="s">
         <v>1338</v>
@@ -13001,13 +13250,13 @@
       <c r="D200" s="1">
         <v>46</v>
       </c>
-      <c r="E200">
-        <v>5000</v>
-      </c>
-      <c r="F200">
-        <v>250</v>
-      </c>
-      <c r="G200" s="5">
+      <c r="E200" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G200" s="2">
         <v>44442</v>
       </c>
       <c r="H200" t="s">
@@ -13036,13 +13285,13 @@
       <c r="D201" s="1">
         <v>30</v>
       </c>
-      <c r="E201" t="s">
-        <v>48</v>
-      </c>
-      <c r="F201" t="s">
+      <c r="E201" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F201" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G201" s="5">
+      <c r="G201" s="2">
         <v>45463</v>
       </c>
       <c r="H201" t="s">
@@ -13071,10 +13320,10 @@
       <c r="D202" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E202">
-        <v>9750</v>
-      </c>
-      <c r="F202" t="s">
+      <c r="E202" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F202" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="G202" t="s">
@@ -13106,10 +13355,13 @@
       <c r="D203" s="1">
         <v>39</v>
       </c>
-      <c r="E203">
-        <v>6000</v>
-      </c>
-      <c r="G203" s="5">
+      <c r="E203" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F203" s="5">
+        <v>0</v>
+      </c>
+      <c r="G203" s="2">
         <v>44893</v>
       </c>
       <c r="H203" t="s">
@@ -13138,10 +13390,10 @@
       <c r="D204" s="1">
         <v>21</v>
       </c>
-      <c r="E204">
-        <v>-500</v>
-      </c>
-      <c r="F204" t="s">
+      <c r="E204" s="5" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F204" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G204" t="s">
@@ -13173,13 +13425,13 @@
       <c r="D205" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E205">
-        <v>6800</v>
-      </c>
-      <c r="F205" s="2">
-        <v>500</v>
-      </c>
-      <c r="G205" s="5">
+      <c r="E205" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G205" s="2">
         <v>43747</v>
       </c>
       <c r="H205" t="s">
@@ -13208,10 +13460,10 @@
       <c r="D206" s="1">
         <v>34</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F206" t="s">
+      <c r="F206" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G206" t="s">
@@ -13221,7 +13473,6 @@
         <v>1351</v>
       </c>
       <c r="I206">
-        <f>974-7039-6387</f>
         <v>-12452</v>
       </c>
       <c r="J206" t="s">
@@ -13244,13 +13495,13 @@
       <c r="D207" s="1">
         <v>25</v>
       </c>
-      <c r="E207">
-        <v>4500</v>
-      </c>
-      <c r="F207" t="s">
-        <v>48</v>
-      </c>
-      <c r="G207" s="5">
+      <c r="E207" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G207" s="2">
         <v>44341</v>
       </c>
       <c r="H207" t="s">
@@ -13279,11 +13530,11 @@
       <c r="D208" s="1">
         <v>43</v>
       </c>
-      <c r="E208">
-        <v>8250</v>
-      </c>
-      <c r="F208">
-        <v>-200</v>
+      <c r="E208" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G208" t="s">
         <v>1353</v>
@@ -13314,11 +13565,11 @@
       <c r="D209" s="1">
         <v>32</v>
       </c>
-      <c r="E209" t="s">
-        <v>48</v>
-      </c>
-      <c r="F209">
-        <v>250</v>
+      <c r="E209" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G209" t="s">
         <v>1356</v>
@@ -13346,11 +13597,11 @@
       <c r="D210" s="1">
         <v>155</v>
       </c>
-      <c r="E210">
-        <v>7000</v>
-      </c>
-      <c r="F210">
-        <v>500</v>
+      <c r="E210" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G210" t="s">
         <v>1359</v>
@@ -13381,13 +13632,13 @@
       <c r="D211" s="1">
         <v>27</v>
       </c>
-      <c r="E211">
-        <v>5200</v>
-      </c>
-      <c r="F211">
-        <v>500</v>
-      </c>
-      <c r="G211" s="5">
+      <c r="E211" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G211" s="2">
         <v>45543</v>
       </c>
       <c r="H211" t="s">
@@ -13416,11 +13667,11 @@
       <c r="D212" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E212">
-        <v>5500</v>
-      </c>
-      <c r="F212">
-        <v>500</v>
+      <c r="E212" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G212" t="s">
         <v>51</v>
@@ -13451,13 +13702,13 @@
       <c r="D213" s="1">
         <v>36</v>
       </c>
-      <c r="E213" t="s">
+      <c r="E213" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F213">
-        <v>500</v>
-      </c>
-      <c r="G213" s="5">
+      <c r="F213" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G213" s="2">
         <v>43851</v>
       </c>
       <c r="H213" t="s">
@@ -13486,10 +13737,10 @@
       <c r="D214" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E214">
-        <v>9000</v>
-      </c>
-      <c r="F214" t="s">
+      <c r="E214" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F214" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G214" t="s">
@@ -13521,13 +13772,13 @@
       <c r="D215" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E215">
-        <v>6250</v>
-      </c>
-      <c r="F215">
-        <v>-50</v>
-      </c>
-      <c r="G215" s="5">
+      <c r="E215" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G215" s="2">
         <v>44595</v>
       </c>
       <c r="H215" t="s">
@@ -13556,11 +13807,11 @@
       <c r="D216" s="1">
         <v>40</v>
       </c>
-      <c r="E216" t="s">
-        <v>48</v>
-      </c>
-      <c r="F216">
-        <v>250</v>
+      <c r="E216" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G216" t="s">
         <v>1370</v>
@@ -13588,13 +13839,13 @@
       <c r="D217" s="1">
         <v>23</v>
       </c>
-      <c r="E217">
-        <v>4800</v>
-      </c>
-      <c r="F217">
-        <v>250</v>
-      </c>
-      <c r="G217" s="5">
+      <c r="E217" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G217" s="2">
         <v>44213</v>
       </c>
       <c r="H217" t="s">
@@ -13620,13 +13871,13 @@
       <c r="D218" s="1">
         <v>31</v>
       </c>
-      <c r="E218">
-        <v>7200</v>
-      </c>
-      <c r="F218">
-        <v>1000</v>
-      </c>
-      <c r="G218" s="5">
+      <c r="E218" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G218" s="2">
         <v>44597</v>
       </c>
       <c r="H218" t="s">
@@ -13655,13 +13906,13 @@
       <c r="D219" s="1">
         <v>48</v>
       </c>
-      <c r="E219">
-        <v>6500</v>
-      </c>
-      <c r="F219" s="2">
-        <v>750</v>
-      </c>
-      <c r="G219" s="5">
+      <c r="E219" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G219" s="2">
         <v>45265</v>
       </c>
       <c r="H219" t="s">
@@ -13690,11 +13941,11 @@
       <c r="D220" s="1">
         <v>29</v>
       </c>
-      <c r="E220">
-        <v>-3000</v>
-      </c>
-      <c r="F220">
-        <v>250</v>
+      <c r="E220" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G220" t="s">
         <v>50</v>
@@ -13722,11 +13973,11 @@
       <c r="D221" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E221">
-        <v>8000</v>
-      </c>
-      <c r="F221">
-        <v>500</v>
+      <c r="E221" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G221" t="s">
         <v>1377</v>
@@ -13757,13 +14008,13 @@
       <c r="D222" s="1">
         <v>34</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E222" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F222">
-        <v>300</v>
-      </c>
-      <c r="G222" s="5">
+      <c r="F222" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G222" s="2">
         <v>44908</v>
       </c>
       <c r="H222" t="s">
@@ -13792,13 +14043,13 @@
       <c r="D223" s="1">
         <v>44</v>
       </c>
-      <c r="E223">
-        <v>5500</v>
-      </c>
-      <c r="F223" t="s">
-        <v>48</v>
-      </c>
-      <c r="G223" s="5">
+      <c r="E223" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G223" s="2">
         <v>45386</v>
       </c>
       <c r="H223" t="s">
@@ -13827,10 +14078,10 @@
       <c r="D224" s="1">
         <v>18</v>
       </c>
-      <c r="E224">
-        <v>9500</v>
-      </c>
-      <c r="F224" t="s">
+      <c r="E224" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F224" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G224" t="s">
@@ -13862,8 +14113,11 @@
       <c r="D225" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E225" t="s">
-        <v>48</v>
+      <c r="E225" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F225" s="5">
+        <v>0</v>
       </c>
       <c r="G225" t="s">
         <v>52</v>
@@ -13894,13 +14148,13 @@
       <c r="D226" s="1">
         <v>37</v>
       </c>
-      <c r="E226">
-        <v>6200</v>
-      </c>
-      <c r="F226" s="2">
-        <v>500</v>
-      </c>
-      <c r="G226" s="5">
+      <c r="E226" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G226" s="2">
         <v>44169</v>
       </c>
       <c r="H226" t="s">
@@ -13929,11 +14183,11 @@
       <c r="D227" s="1">
         <v>26</v>
       </c>
-      <c r="E227">
-        <v>4750</v>
-      </c>
-      <c r="F227" s="2">
-        <v>750</v>
+      <c r="E227" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G227" t="s">
         <v>1386</v>
@@ -13964,13 +14218,13 @@
       <c r="D228" s="1">
         <v>-9</v>
       </c>
-      <c r="E228">
-        <v>7000</v>
-      </c>
-      <c r="F228">
-        <v>250</v>
-      </c>
-      <c r="G228" s="5">
+      <c r="E228" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G228" s="2">
         <v>44473</v>
       </c>
       <c r="H228" t="s">
@@ -13999,13 +14253,13 @@
       <c r="D229" s="1">
         <v>42</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F229">
-        <v>300</v>
-      </c>
-      <c r="G229" s="5">
+      <c r="F229" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G229" s="2">
         <v>44476</v>
       </c>
       <c r="H229" t="s">
@@ -14034,13 +14288,13 @@
       <c r="D230" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E230">
-        <v>6500</v>
-      </c>
-      <c r="F230">
-        <v>750</v>
-      </c>
-      <c r="G230" s="5">
+      <c r="E230" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G230" s="2">
         <v>44217</v>
       </c>
       <c r="H230" t="s">
@@ -14069,10 +14323,10 @@
       <c r="D231" s="1">
         <v>30</v>
       </c>
-      <c r="E231">
-        <v>8200</v>
-      </c>
-      <c r="F231" t="s">
+      <c r="E231" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F231" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G231" t="s">
@@ -14082,7 +14336,6 @@
         <v>1393</v>
       </c>
       <c r="I231">
-        <f>974-4456-2027</f>
         <v>-5509</v>
       </c>
       <c r="J231" t="s">
@@ -14105,10 +14358,10 @@
       <c r="D232" s="1">
         <v>35</v>
       </c>
-      <c r="E232" t="s">
-        <v>48</v>
-      </c>
-      <c r="F232" t="s">
+      <c r="E232" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F232" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="G232" t="s">
@@ -14140,10 +14393,10 @@
       <c r="D233" s="1">
         <v>22</v>
       </c>
-      <c r="E233">
-        <v>5250</v>
-      </c>
-      <c r="F233" t="s">
+      <c r="E233" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F233" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G233" t="s">
@@ -14175,13 +14428,13 @@
       <c r="D234" s="1">
         <v>50</v>
       </c>
-      <c r="E234">
-        <v>4800</v>
-      </c>
-      <c r="F234">
-        <v>250</v>
-      </c>
-      <c r="G234" s="5">
+      <c r="E234" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G234" s="2">
         <v>44933</v>
       </c>
       <c r="H234" t="s">
@@ -14210,11 +14463,11 @@
       <c r="D235" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="E235">
-        <v>9000</v>
-      </c>
-      <c r="F235">
-        <v>500</v>
+      <c r="E235" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G235" t="s">
         <v>1400</v>
@@ -14242,10 +14495,10 @@
       <c r="D236" s="1">
         <v>39</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E236" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F236" t="s">
+      <c r="F236" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G236" t="s">
@@ -14277,13 +14530,13 @@
       <c r="D237" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E237">
-        <v>6500</v>
-      </c>
-      <c r="F237">
-        <v>300</v>
-      </c>
-      <c r="G237" s="5">
+      <c r="E237" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G237" s="2">
         <v>45646</v>
       </c>
       <c r="H237" t="s">
@@ -14312,13 +14565,13 @@
       <c r="D238" s="1">
         <v>27</v>
       </c>
-      <c r="E238">
-        <v>7750</v>
-      </c>
-      <c r="F238">
-        <v>500</v>
-      </c>
-      <c r="G238" s="5">
+      <c r="E238" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G238" s="2">
         <v>44998</v>
       </c>
       <c r="H238" t="s">
@@ -14347,13 +14600,13 @@
       <c r="D239" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E239">
-        <v>-1000</v>
-      </c>
-      <c r="F239" t="s">
+      <c r="E239" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F239" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G239" s="5">
+      <c r="G239" s="2">
         <v>43862</v>
       </c>
       <c r="H239" t="s">
@@ -14382,11 +14635,11 @@
       <c r="D240" s="1">
         <v>41</v>
       </c>
-      <c r="E240" t="s">
-        <v>48</v>
-      </c>
-      <c r="F240">
-        <v>750</v>
+      <c r="E240" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G240" t="s">
         <v>1409</v>
@@ -14417,10 +14670,10 @@
       <c r="D241" s="1">
         <v>32</v>
       </c>
-      <c r="E241">
-        <v>6000</v>
-      </c>
-      <c r="F241" t="s">
+      <c r="E241" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F241" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G241" t="s">
@@ -14452,10 +14705,10 @@
       <c r="D242" s="1">
         <v>24</v>
       </c>
-      <c r="E242">
-        <v>7200</v>
-      </c>
-      <c r="F242" t="s">
+      <c r="E242" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F242" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G242" t="s">
@@ -14487,10 +14740,10 @@
       <c r="D243" s="1">
         <v>145</v>
       </c>
-      <c r="E243">
-        <v>5500</v>
-      </c>
-      <c r="F243" t="s">
+      <c r="E243" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F243" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G243" t="s">
@@ -14522,11 +14775,11 @@
       <c r="D244" s="1">
         <v>36</v>
       </c>
-      <c r="E244" t="s">
+      <c r="E244" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F244">
-        <v>250</v>
+      <c r="F244" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G244" t="s">
         <v>1419</v>
@@ -14557,13 +14810,13 @@
       <c r="D245" s="1">
         <v>28</v>
       </c>
-      <c r="E245">
-        <v>8500</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="E245" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F245" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G245" s="5">
+      <c r="G245" s="2">
         <v>45429</v>
       </c>
       <c r="H245" t="s">
@@ -14592,11 +14845,11 @@
       <c r="D246" s="1">
         <v>43</v>
       </c>
-      <c r="E246">
-        <v>4500</v>
-      </c>
-      <c r="F246" s="2">
-        <v>750</v>
+      <c r="E246" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G246" t="s">
         <v>1137</v>
@@ -14627,13 +14880,13 @@
       <c r="D247" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E247" t="s">
-        <v>48</v>
-      </c>
-      <c r="F247">
-        <v>750</v>
-      </c>
-      <c r="G247" s="5">
+      <c r="E247" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G247" s="2">
         <v>45082</v>
       </c>
       <c r="H247" t="s">
@@ -14662,11 +14915,11 @@
       <c r="D248" s="1">
         <v>19</v>
       </c>
-      <c r="E248">
-        <v>7000</v>
-      </c>
-      <c r="F248">
-        <v>500</v>
+      <c r="E248" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G248" t="s">
         <v>1424</v>
@@ -14697,11 +14950,11 @@
       <c r="D249" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E249">
-        <v>6200</v>
-      </c>
-      <c r="F249" s="2">
-        <v>1000</v>
+      <c r="E249" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>1940</v>
       </c>
       <c r="G249" t="s">
         <v>1427</v>
@@ -14732,13 +14985,13 @@
       <c r="D250" s="1">
         <v>33</v>
       </c>
-      <c r="E250">
-        <v>5750</v>
-      </c>
-      <c r="F250">
-        <v>300</v>
-      </c>
-      <c r="G250" s="5">
+      <c r="E250" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G250" s="2">
         <v>44303</v>
       </c>
       <c r="H250" t="s">
@@ -14761,13 +15014,13 @@
       <c r="D251" s="1">
         <v>38</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E251" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F251">
-        <v>-50</v>
-      </c>
-      <c r="G251" s="5">
+      <c r="F251" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G251" s="2">
         <v>45270</v>
       </c>
       <c r="H251" t="s">
@@ -14796,11 +15049,11 @@
       <c r="D252" s="1">
         <v>25</v>
       </c>
-      <c r="E252">
-        <v>9000</v>
-      </c>
-      <c r="F252" s="2">
-        <v>750</v>
+      <c r="E252" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G252" t="s">
         <v>1431</v>
@@ -14831,11 +15084,11 @@
       <c r="D253" s="1">
         <v>-7</v>
       </c>
-      <c r="E253">
-        <v>6250</v>
-      </c>
-      <c r="F253">
-        <v>1000</v>
+      <c r="E253" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G253" t="s">
         <v>1434</v>
@@ -14844,7 +15097,6 @@
         <v>1008</v>
       </c>
       <c r="I253">
-        <f>974-3880-9712</f>
         <v>-12618</v>
       </c>
       <c r="J253" t="s">
@@ -14867,20 +15119,19 @@
       <c r="D254" s="1">
         <v>47</v>
       </c>
-      <c r="E254" t="s">
-        <v>48</v>
-      </c>
-      <c r="F254">
-        <v>0</v>
-      </c>
-      <c r="G254" s="5">
+      <c r="E254" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G254" s="2">
         <v>43784</v>
       </c>
       <c r="H254" t="s">
         <v>1435</v>
       </c>
       <c r="I254">
-        <f>974-4292-8120</f>
         <v>-11438</v>
       </c>
       <c r="J254" t="s">
@@ -14903,11 +15154,11 @@
       <c r="D255" s="1">
         <v>30</v>
       </c>
-      <c r="E255">
-        <v>5200</v>
-      </c>
-      <c r="F255">
-        <v>500</v>
+      <c r="E255" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G255" t="s">
         <v>1137</v>
@@ -14935,20 +15186,19 @@
       <c r="D256" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E256">
-        <v>8000</v>
-      </c>
-      <c r="F256">
-        <v>-50</v>
-      </c>
-      <c r="G256" s="5">
+      <c r="E256" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G256" s="2">
         <v>45360</v>
       </c>
       <c r="H256" t="s">
         <v>1438</v>
       </c>
       <c r="I256">
-        <f>974-7936-8102</f>
         <v>-15064</v>
       </c>
       <c r="J256" t="s">
@@ -14971,13 +15221,13 @@
       <c r="D257" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="E257">
-        <v>-250</v>
-      </c>
-      <c r="F257">
-        <v>1000</v>
-      </c>
-      <c r="G257" s="5">
+      <c r="E257" s="5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G257" s="2">
         <v>44737</v>
       </c>
       <c r="H257" t="s">
@@ -15006,11 +15256,11 @@
       <c r="D258" s="1">
         <v>41</v>
       </c>
-      <c r="E258">
-        <v>6500</v>
-      </c>
-      <c r="F258">
-        <v>1250</v>
+      <c r="E258" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>1913</v>
       </c>
       <c r="G258" t="s">
         <v>1440</v>
@@ -15019,7 +15269,6 @@
         <v>1441</v>
       </c>
       <c r="I258">
-        <f>974-4989-5430</f>
         <v>-9445</v>
       </c>
       <c r="J258" t="s">
@@ -15042,11 +15291,11 @@
       <c r="D259" s="1">
         <v>29</v>
       </c>
-      <c r="E259" t="s">
+      <c r="E259" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F259">
-        <v>1250</v>
+      <c r="F259" s="5" t="s">
+        <v>1913</v>
       </c>
       <c r="G259" t="s">
         <v>1442</v>
@@ -15077,13 +15326,13 @@
       <c r="D260" s="1">
         <v>34</v>
       </c>
-      <c r="E260">
-        <v>4500</v>
-      </c>
-      <c r="F260" t="s">
+      <c r="E260" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F260" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G260" s="5">
+      <c r="G260" s="2">
         <v>44788</v>
       </c>
       <c r="H260" t="s">
@@ -15112,13 +15361,13 @@
       <c r="D261" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E261">
-        <v>7200</v>
-      </c>
-      <c r="F261">
-        <v>0</v>
-      </c>
-      <c r="G261" s="5">
+      <c r="E261" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G261" s="2">
         <v>44262</v>
       </c>
       <c r="H261" t="s">
@@ -15147,13 +15396,13 @@
       <c r="D262" s="1">
         <v>21</v>
       </c>
-      <c r="E262" t="s">
-        <v>48</v>
-      </c>
-      <c r="F262">
-        <v>500</v>
-      </c>
-      <c r="G262" s="5">
+      <c r="E262" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G262" s="2">
         <v>43521</v>
       </c>
       <c r="H262" t="s">
@@ -15182,20 +15431,19 @@
       <c r="D263" s="1">
         <v>36</v>
       </c>
-      <c r="E263">
-        <v>9250</v>
-      </c>
-      <c r="F263" t="s">
+      <c r="E263" s="5" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F263" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G263" s="5">
+      <c r="G263" s="2">
         <v>44575</v>
       </c>
       <c r="H263" t="s">
         <v>1018</v>
       </c>
       <c r="I263">
-        <f>974-6773-4327</f>
         <v>-10126</v>
       </c>
       <c r="J263" t="s">
@@ -15218,13 +15466,13 @@
       <c r="D264" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E264">
-        <v>5500</v>
-      </c>
-      <c r="F264">
-        <v>500</v>
-      </c>
-      <c r="G264" s="5">
+      <c r="E264" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G264" s="2">
         <v>44601</v>
       </c>
       <c r="H264" t="s">
@@ -15253,13 +15501,13 @@
       <c r="D265" s="1">
         <v>160</v>
       </c>
-      <c r="E265">
-        <v>6500</v>
-      </c>
-      <c r="F265" t="s">
+      <c r="E265" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F265" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G265" s="5">
+      <c r="G265" s="2">
         <v>44790</v>
       </c>
       <c r="H265" t="s">
@@ -15288,13 +15536,13 @@
       <c r="D266" s="1">
         <v>27</v>
       </c>
-      <c r="E266" t="s">
+      <c r="E266" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F266" s="2">
-        <v>750</v>
-      </c>
-      <c r="G266" s="5">
+      <c r="F266" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G266" s="2">
         <v>44638</v>
       </c>
       <c r="H266" t="s">
@@ -15323,13 +15571,13 @@
       <c r="D267" s="1">
         <v>45</v>
       </c>
-      <c r="E267">
-        <v>8000</v>
-      </c>
-      <c r="F267">
-        <v>500</v>
-      </c>
-      <c r="G267" s="5">
+      <c r="E267" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G267" s="2">
         <v>43857</v>
       </c>
       <c r="H267" t="s">
@@ -15358,13 +15606,13 @@
       <c r="D268" s="1">
         <v>31</v>
       </c>
-      <c r="E268">
-        <v>5000</v>
-      </c>
-      <c r="F268">
-        <v>500</v>
-      </c>
-      <c r="G268" s="5">
+      <c r="E268" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G268" s="2">
         <v>45657</v>
       </c>
       <c r="H268" t="s">
@@ -15393,10 +15641,10 @@
       <c r="D269" s="1">
         <v>24</v>
       </c>
-      <c r="E269" t="s">
-        <v>48</v>
-      </c>
-      <c r="F269" t="s">
+      <c r="E269" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F269" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G269" t="s">
@@ -15428,10 +15676,10 @@
       <c r="D270" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E270">
-        <v>6200</v>
-      </c>
-      <c r="F270" t="s">
+      <c r="E270" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F270" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G270" t="s">
@@ -15460,13 +15708,13 @@
       <c r="D271" s="1">
         <v>39</v>
       </c>
-      <c r="E271">
-        <v>7500</v>
-      </c>
-      <c r="F271">
-        <v>0</v>
-      </c>
-      <c r="G271" s="5">
+      <c r="E271" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G271" s="2">
         <v>43877</v>
       </c>
       <c r="H271" t="s">
@@ -15495,20 +15743,19 @@
       <c r="D272" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E272">
-        <v>4800</v>
-      </c>
-      <c r="F272" s="2">
-        <v>750</v>
-      </c>
-      <c r="G272" s="5">
+      <c r="E272" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G272" s="2">
         <v>44169</v>
       </c>
       <c r="H272" t="s">
         <v>1466</v>
       </c>
       <c r="I272">
-        <f>974-5072-9970</f>
         <v>-14068</v>
       </c>
       <c r="J272" t="s">
@@ -15528,13 +15775,13 @@
       <c r="D273" s="1">
         <v>33</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E273" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F273" t="s">
+      <c r="F273" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G273" s="5">
+      <c r="G273" s="2">
         <v>44174</v>
       </c>
       <c r="H273" t="s">
@@ -15563,11 +15810,11 @@
       <c r="D274" s="1">
         <v>42</v>
       </c>
-      <c r="E274">
-        <v>8750</v>
-      </c>
-      <c r="F274">
-        <v>250</v>
+      <c r="E274" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G274" t="s">
         <v>1468</v>
@@ -15598,13 +15845,13 @@
       <c r="D275" s="1">
         <v>28</v>
       </c>
-      <c r="E275">
-        <v>6500</v>
-      </c>
-      <c r="F275">
-        <v>-50</v>
-      </c>
-      <c r="G275" s="5">
+      <c r="E275" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G275" s="2">
         <v>44661</v>
       </c>
       <c r="H275" t="s">
@@ -15633,11 +15880,11 @@
       <c r="D276" s="1">
         <v>17</v>
       </c>
-      <c r="E276">
-        <v>-1500</v>
-      </c>
-      <c r="F276" s="2">
-        <v>500</v>
+      <c r="E276" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G276" t="s">
         <v>1472</v>
@@ -15668,13 +15915,13 @@
       <c r="D277" s="1">
         <v>35</v>
       </c>
-      <c r="E277" t="s">
-        <v>48</v>
-      </c>
-      <c r="F277">
-        <v>250</v>
-      </c>
-      <c r="G277" s="5">
+      <c r="E277" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G277" s="2">
         <v>43818</v>
       </c>
       <c r="H277" t="s">
@@ -15703,11 +15950,11 @@
       <c r="D278" s="1">
         <v>40</v>
       </c>
-      <c r="E278">
-        <v>5500</v>
-      </c>
-      <c r="F278">
-        <v>500</v>
+      <c r="E278" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G278" t="s">
         <v>48</v>
@@ -15738,11 +15985,11 @@
       <c r="D279" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E279">
-        <v>7200</v>
-      </c>
-      <c r="F279">
-        <v>750</v>
+      <c r="E279" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G279" t="s">
         <v>1478</v>
@@ -15751,7 +15998,6 @@
         <v>1194</v>
       </c>
       <c r="I279">
-        <f>974-5928-9165</f>
         <v>-14119</v>
       </c>
       <c r="J279" t="s">
@@ -15774,13 +16020,13 @@
       <c r="D280" s="1">
         <v>26</v>
       </c>
-      <c r="E280">
-        <v>6250</v>
-      </c>
-      <c r="F280" t="s">
-        <v>48</v>
-      </c>
-      <c r="G280" s="5">
+      <c r="E280" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G280" s="2">
         <v>45037</v>
       </c>
       <c r="H280" t="s">
@@ -15809,11 +16055,11 @@
       <c r="D281" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E281" t="s">
+      <c r="E281" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F281">
-        <v>-50</v>
+      <c r="F281" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G281" t="s">
         <v>1480</v>
@@ -15844,13 +16090,13 @@
       <c r="D282" s="1">
         <v>44</v>
       </c>
-      <c r="E282">
-        <v>9000</v>
-      </c>
-      <c r="F282">
-        <v>500</v>
-      </c>
-      <c r="G282" s="5">
+      <c r="E282" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G282" s="2">
         <v>44907</v>
       </c>
       <c r="H282" t="s">
@@ -15879,13 +16125,13 @@
       <c r="D283" s="1">
         <v>-3</v>
       </c>
-      <c r="E283" t="s">
-        <v>48</v>
-      </c>
-      <c r="F283">
-        <v>250</v>
-      </c>
-      <c r="G283" s="5">
+      <c r="E283" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G283" s="2">
         <v>44930</v>
       </c>
       <c r="H283" t="s">
@@ -15914,11 +16160,11 @@
       <c r="D284" s="1">
         <v>30</v>
       </c>
-      <c r="E284">
-        <v>4800</v>
-      </c>
-      <c r="F284">
-        <v>250</v>
+      <c r="E284" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G284" t="s">
         <v>1486</v>
@@ -15949,13 +16195,13 @@
       <c r="D285" s="1">
         <v>37</v>
       </c>
-      <c r="E285">
-        <v>7000</v>
-      </c>
-      <c r="F285">
-        <v>500</v>
-      </c>
-      <c r="G285" s="5">
+      <c r="E285" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G285" s="2">
         <v>45146</v>
       </c>
       <c r="H285" t="s">
@@ -15984,13 +16230,13 @@
       <c r="D286" s="1">
         <v>23</v>
       </c>
-      <c r="E286">
-        <v>8200</v>
-      </c>
-      <c r="F286" t="s">
+      <c r="E286" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F286" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G286" s="5">
+      <c r="G286" s="2">
         <v>45524</v>
       </c>
       <c r="H286" t="s">
@@ -16019,11 +16265,11 @@
       <c r="D287" s="1">
         <v>48</v>
       </c>
-      <c r="E287">
-        <v>5200</v>
-      </c>
-      <c r="F287">
-        <v>750</v>
+      <c r="E287" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G287" t="s">
         <v>1491</v>
@@ -16054,13 +16300,13 @@
       <c r="D288" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E288" t="s">
+      <c r="E288" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F288">
-        <v>500</v>
-      </c>
-      <c r="G288" s="5">
+      <c r="F288" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G288" s="2">
         <v>43500</v>
       </c>
       <c r="H288" t="s">
@@ -16086,10 +16332,13 @@
       <c r="D289" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="E289">
-        <v>6500</v>
-      </c>
-      <c r="G289" s="5">
+      <c r="E289" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F289" s="5">
+        <v>0</v>
+      </c>
+      <c r="G289" s="2">
         <v>43779</v>
       </c>
       <c r="H289" t="s">
@@ -16118,11 +16367,11 @@
       <c r="D290" s="1">
         <v>34</v>
       </c>
-      <c r="E290" t="s">
-        <v>48</v>
-      </c>
-      <c r="F290">
-        <v>250</v>
+      <c r="E290" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G290" t="s">
         <v>1497</v>
@@ -16153,17 +16402,16 @@
       <c r="D291" s="1">
         <v>31</v>
       </c>
-      <c r="E291">
-        <v>7500</v>
-      </c>
-      <c r="F291" t="s">
+      <c r="E291" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F291" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="H291" t="s">
         <v>1499</v>
       </c>
       <c r="I291">
-        <f>974-4824-9133</f>
         <v>-12983</v>
       </c>
       <c r="J291" t="s">
@@ -16186,10 +16434,10 @@
       <c r="D292" s="1">
         <v>41</v>
       </c>
-      <c r="E292">
-        <v>5250</v>
-      </c>
-      <c r="F292" t="s">
+      <c r="E292" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F292" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H292" t="s">
@@ -16218,11 +16466,11 @@
       <c r="D293" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E293">
-        <v>-5000</v>
-      </c>
-      <c r="F293">
-        <v>0</v>
+      <c r="E293" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>1938</v>
       </c>
       <c r="G293" t="s">
         <v>1501</v>
@@ -16231,7 +16479,6 @@
         <v>1502</v>
       </c>
       <c r="I293">
-        <f>974-3886-1007</f>
         <v>-3919</v>
       </c>
       <c r="J293" t="s">
@@ -16254,13 +16501,13 @@
       <c r="D294" s="1">
         <v>20</v>
       </c>
-      <c r="E294">
-        <v>6200</v>
-      </c>
-      <c r="F294">
-        <v>750</v>
-      </c>
-      <c r="G294" s="5">
+      <c r="E294" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G294" s="2">
         <v>44249</v>
       </c>
       <c r="H294" t="s">
@@ -16289,13 +16536,13 @@
       <c r="D295" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E295" t="s">
+      <c r="E295" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F295">
-        <v>250</v>
-      </c>
-      <c r="G295" s="5">
+      <c r="F295" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G295" s="2">
         <v>44463</v>
       </c>
       <c r="H295" t="s">
@@ -16324,10 +16571,10 @@
       <c r="D296" s="1">
         <v>43</v>
       </c>
-      <c r="E296">
-        <v>9000</v>
-      </c>
-      <c r="F296" t="s">
+      <c r="E296" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F296" s="5" t="s">
         <v>962</v>
       </c>
       <c r="G296" t="s">
@@ -16359,10 +16606,10 @@
       <c r="D297" s="1">
         <v>27</v>
       </c>
-      <c r="E297">
-        <v>4500</v>
-      </c>
-      <c r="F297" t="s">
+      <c r="E297" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F297" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G297" t="s">
@@ -16394,10 +16641,10 @@
       <c r="D298" s="1">
         <v>36</v>
       </c>
-      <c r="E298" t="s">
-        <v>48</v>
-      </c>
-      <c r="F298" t="s">
+      <c r="E298" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F298" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G298" t="s">
@@ -16429,13 +16676,13 @@
       <c r="D299" s="1">
         <v>150</v>
       </c>
-      <c r="E299">
-        <v>7200</v>
-      </c>
-      <c r="F299" t="s">
+      <c r="E299" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F299" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G299" s="5">
+      <c r="G299" s="2">
         <v>44997</v>
       </c>
       <c r="H299" t="s">
@@ -16464,11 +16711,11 @@
       <c r="D300" s="1">
         <v>32</v>
       </c>
-      <c r="E300">
-        <v>5500</v>
-      </c>
-      <c r="F300">
-        <v>250</v>
+      <c r="E300" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G300" t="s">
         <v>1515</v>
@@ -16499,10 +16746,13 @@
       <c r="D301" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E301">
-        <v>6750</v>
-      </c>
-      <c r="G301" s="5">
+      <c r="E301" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F301" s="5">
+        <v>0</v>
+      </c>
+      <c r="G301" s="2">
         <v>44166</v>
       </c>
       <c r="H301" t="s">
@@ -16528,13 +16778,13 @@
       <c r="D302" s="1">
         <v>25</v>
       </c>
-      <c r="E302" t="s">
+      <c r="E302" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F302">
-        <v>500</v>
-      </c>
-      <c r="G302" s="5">
+      <c r="F302" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G302" s="2">
         <v>44630</v>
       </c>
       <c r="H302" t="s">
@@ -16560,10 +16810,10 @@
       <c r="D303" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E303">
-        <v>8000</v>
-      </c>
-      <c r="F303" t="s">
+      <c r="E303" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F303" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G303" t="s">
@@ -16595,11 +16845,11 @@
       <c r="D304" s="1">
         <v>39</v>
       </c>
-      <c r="E304">
-        <v>5000</v>
-      </c>
-      <c r="F304">
-        <v>-200</v>
+      <c r="E304" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G304" t="s">
         <v>1523</v>
@@ -16627,13 +16877,13 @@
       <c r="D305" s="1">
         <v>46</v>
       </c>
-      <c r="E305" t="s">
-        <v>48</v>
-      </c>
-      <c r="F305" t="s">
+      <c r="E305" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F305" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="G305" s="5">
+      <c r="G305" s="2">
         <v>45297</v>
       </c>
       <c r="H305" t="s">
@@ -16662,13 +16912,13 @@
       <c r="D306" s="1">
         <v>29</v>
       </c>
-      <c r="E306">
-        <v>6500</v>
-      </c>
-      <c r="F306" t="s">
+      <c r="E306" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F306" s="5" t="s">
         <v>1055</v>
       </c>
-      <c r="G306" s="5">
+      <c r="G306" s="2">
         <v>44459</v>
       </c>
       <c r="H306" t="s">
@@ -16697,11 +16947,11 @@
       <c r="D307" s="1">
         <v>-5</v>
       </c>
-      <c r="E307">
-        <v>8500</v>
-      </c>
-      <c r="F307" s="2">
-        <v>750</v>
+      <c r="E307" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G307" t="s">
         <v>1530</v>
@@ -16732,11 +16982,11 @@
       <c r="D308" s="1">
         <v>35</v>
       </c>
-      <c r="E308">
-        <v>4800</v>
-      </c>
-      <c r="F308">
-        <v>500</v>
+      <c r="E308" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F308" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G308" t="s">
         <v>1533</v>
@@ -16767,11 +17017,11 @@
       <c r="D309" s="1">
         <v>22</v>
       </c>
-      <c r="E309" t="s">
+      <c r="E309" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F309">
-        <v>500</v>
+      <c r="F309" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G309" t="s">
         <v>1536</v>
@@ -16802,11 +17052,11 @@
       <c r="D310" s="1">
         <v>40</v>
       </c>
-      <c r="E310">
-        <v>7000</v>
-      </c>
-      <c r="F310">
-        <v>250</v>
+      <c r="E310" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G310" t="s">
         <v>1539</v>
@@ -16837,13 +17087,13 @@
       <c r="D311" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E311">
-        <v>6200</v>
-      </c>
-      <c r="F311">
-        <v>250</v>
-      </c>
-      <c r="G311" s="5">
+      <c r="E311" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G311" s="2">
         <v>45018</v>
       </c>
       <c r="H311" t="s">
@@ -16872,13 +17122,13 @@
       <c r="D312" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="E312" t="s">
-        <v>48</v>
-      </c>
-      <c r="F312">
-        <v>750</v>
-      </c>
-      <c r="G312" s="5">
+      <c r="E312" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G312" s="2">
         <v>43600</v>
       </c>
       <c r="H312" t="s">
@@ -16907,10 +17157,10 @@
       <c r="D313" s="1">
         <v>31</v>
       </c>
-      <c r="E313">
-        <v>5750</v>
-      </c>
-      <c r="F313" t="s">
+      <c r="E313" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F313" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G313" t="s">
@@ -16942,11 +17192,11 @@
       <c r="D314" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E314">
-        <v>9000</v>
-      </c>
-      <c r="F314">
-        <v>250</v>
+      <c r="E314" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F314" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G314" t="s">
         <v>48</v>
@@ -16955,7 +17205,6 @@
         <v>1548</v>
       </c>
       <c r="I314">
-        <f>974-7708-5518</f>
         <v>-12252</v>
       </c>
       <c r="J314" t="s">
@@ -16978,13 +17227,13 @@
       <c r="D315" s="1">
         <v>24</v>
       </c>
-      <c r="E315">
-        <v>-2000</v>
-      </c>
-      <c r="F315" t="s">
+      <c r="E315" s="5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F315" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G315" s="5">
+      <c r="G315" s="2">
         <v>44933</v>
       </c>
       <c r="H315" t="s">
@@ -17013,13 +17262,13 @@
       <c r="D316" s="1">
         <v>42</v>
       </c>
-      <c r="E316">
-        <v>6500</v>
-      </c>
-      <c r="F316" t="s">
-        <v>48</v>
-      </c>
-      <c r="G316" s="5">
+      <c r="E316" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F316" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G316" s="2">
         <v>44792</v>
       </c>
       <c r="H316" t="s">
@@ -17048,11 +17297,11 @@
       <c r="D317" s="1">
         <v>38</v>
       </c>
-      <c r="E317" t="s">
+      <c r="E317" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F317">
-        <v>750</v>
+      <c r="F317" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G317" t="s">
         <v>1553</v>
@@ -17083,13 +17332,13 @@
       <c r="D318" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E318">
-        <v>7200</v>
-      </c>
-      <c r="F318" t="s">
+      <c r="E318" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F318" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="G318" s="5">
+      <c r="G318" s="2">
         <v>44764</v>
       </c>
       <c r="H318" t="s">
@@ -17118,17 +17367,16 @@
       <c r="D319" s="1">
         <v>18</v>
       </c>
-      <c r="E319">
-        <v>4750</v>
-      </c>
-      <c r="F319">
-        <v>500</v>
-      </c>
-      <c r="G319" s="5">
+      <c r="E319" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F319" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G319" s="2">
         <v>43613</v>
       </c>
       <c r="I319">
-        <f>974-5730-6261</f>
         <v>-11017</v>
       </c>
       <c r="J319" t="s">
@@ -17151,10 +17399,10 @@
       <c r="D320" s="1">
         <v>30</v>
       </c>
-      <c r="E320" t="s">
-        <v>48</v>
-      </c>
-      <c r="F320" t="s">
+      <c r="E320" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F320" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="G320" t="s">
@@ -17186,13 +17434,13 @@
       <c r="D321" s="1">
         <v>45</v>
       </c>
-      <c r="E321">
-        <v>8000</v>
-      </c>
-      <c r="F321">
-        <v>750</v>
-      </c>
-      <c r="G321" s="5">
+      <c r="E321" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F321" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G321" s="2">
         <v>43984</v>
       </c>
       <c r="H321" t="s">
@@ -17218,13 +17466,13 @@
       <c r="D322" s="1">
         <v>27</v>
       </c>
-      <c r="E322">
-        <v>5500</v>
-      </c>
-      <c r="F322" t="s">
+      <c r="E322" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F322" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G322" s="5">
+      <c r="G322" s="2">
         <v>45021</v>
       </c>
       <c r="H322" t="s">
@@ -17253,11 +17501,11 @@
       <c r="D323" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E323">
-        <v>7500</v>
-      </c>
-      <c r="F323">
-        <v>-200</v>
+      <c r="E323" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F323" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G323" t="s">
         <v>1565</v>
@@ -17288,10 +17536,10 @@
       <c r="D324" s="1">
         <v>34</v>
       </c>
-      <c r="E324" t="s">
+      <c r="E324" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F324" t="s">
+      <c r="F324" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G324" t="s">
@@ -17323,13 +17571,13 @@
       <c r="D325" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E325">
-        <v>6500</v>
-      </c>
-      <c r="F325">
-        <v>250</v>
-      </c>
-      <c r="G325" s="5">
+      <c r="E325" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F325" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G325" s="2">
         <v>44364</v>
       </c>
       <c r="H325" t="s">
@@ -17358,13 +17606,13 @@
       <c r="D326" s="1">
         <v>175</v>
       </c>
-      <c r="E326" t="s">
-        <v>48</v>
-      </c>
-      <c r="F326" t="s">
+      <c r="E326" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F326" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G326" s="5">
+      <c r="G326" s="2">
         <v>44006</v>
       </c>
       <c r="H326" t="s">
@@ -17390,20 +17638,19 @@
       <c r="D327" s="1">
         <v>26</v>
       </c>
-      <c r="E327">
-        <v>9500</v>
-      </c>
-      <c r="F327" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G327" s="5">
+      <c r="E327" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F327" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G327" s="2">
         <v>44502</v>
       </c>
       <c r="H327" t="s">
         <v>1574</v>
       </c>
       <c r="I327">
-        <f>974-7898-3252</f>
         <v>-10176</v>
       </c>
       <c r="J327" t="s">
@@ -17426,10 +17673,10 @@
       <c r="D328" s="1">
         <v>41</v>
       </c>
-      <c r="E328">
-        <v>4800</v>
-      </c>
-      <c r="F328" t="s">
+      <c r="E328" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F328" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G328" t="s">
@@ -17439,7 +17686,6 @@
         <v>1576</v>
       </c>
       <c r="I328">
-        <f>974-6757-6707</f>
         <v>-12490</v>
       </c>
       <c r="J328" t="s">
@@ -17462,10 +17708,10 @@
       <c r="D329" s="1">
         <v>22</v>
       </c>
-      <c r="E329">
-        <v>6250</v>
-      </c>
-      <c r="F329" t="s">
+      <c r="E329" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F329" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G329" t="s">
@@ -17494,13 +17740,13 @@
       <c r="D330" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="E330">
-        <v>-750</v>
-      </c>
-      <c r="F330">
-        <v>500</v>
-      </c>
-      <c r="G330" s="5">
+      <c r="E330" s="5" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F330" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G330" s="2">
         <v>44318</v>
       </c>
       <c r="H330" t="s">
@@ -17526,13 +17772,13 @@
       <c r="D331" s="1">
         <v>37</v>
       </c>
-      <c r="E331" t="s">
+      <c r="E331" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F331">
-        <v>-200</v>
-      </c>
-      <c r="G331" s="5">
+      <c r="F331" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G331" s="2">
         <v>44806</v>
       </c>
       <c r="H331" t="s">
@@ -17561,11 +17807,11 @@
       <c r="D332" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E332">
-        <v>5500</v>
-      </c>
-      <c r="F332">
-        <v>0</v>
+      <c r="E332" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F332" s="5" t="s">
+        <v>1938</v>
       </c>
       <c r="G332" t="s">
         <v>1581</v>
@@ -17596,13 +17842,13 @@
       <c r="D333" s="1">
         <v>33</v>
       </c>
-      <c r="E333">
-        <v>7200</v>
-      </c>
-      <c r="F333">
-        <v>750</v>
-      </c>
-      <c r="G333" s="5">
+      <c r="E333" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F333" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G333" s="2">
         <v>43482</v>
       </c>
       <c r="H333" t="s">
@@ -17631,11 +17877,11 @@
       <c r="D334" s="1">
         <v>29</v>
       </c>
-      <c r="E334" t="s">
-        <v>48</v>
-      </c>
-      <c r="F334">
-        <v>250</v>
+      <c r="E334" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F334" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G334" t="s">
         <v>1584</v>
@@ -17666,8 +17912,11 @@
       <c r="D335" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E335">
-        <v>8250</v>
+      <c r="E335" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F335" s="5">
+        <v>0</v>
       </c>
       <c r="G335" t="s">
         <v>1587</v>
@@ -17695,11 +17944,11 @@
       <c r="D336" s="1">
         <v>44</v>
       </c>
-      <c r="E336">
-        <v>6200</v>
-      </c>
-      <c r="F336">
-        <v>250</v>
+      <c r="E336" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F336" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G336" t="s">
         <v>1589</v>
@@ -17730,11 +17979,11 @@
       <c r="D337" s="1">
         <v>19</v>
       </c>
-      <c r="E337">
-        <v>4500</v>
-      </c>
-      <c r="F337">
-        <v>750</v>
+      <c r="E337" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F337" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G337" t="s">
         <v>1592</v>
@@ -17765,11 +18014,11 @@
       <c r="D338" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E338" t="s">
+      <c r="E338" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F338">
-        <v>500</v>
+      <c r="F338" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G338" t="s">
         <v>1595</v>
@@ -17797,20 +18046,19 @@
       <c r="D339" s="1">
         <v>36</v>
       </c>
-      <c r="E339">
-        <v>7000</v>
-      </c>
-      <c r="F339">
-        <v>1250</v>
-      </c>
-      <c r="G339" s="5">
+      <c r="E339" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F339" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G339" s="2">
         <v>44532</v>
       </c>
       <c r="H339" t="s">
         <v>1598</v>
       </c>
       <c r="I339">
-        <f>974-6012-1457</f>
         <v>-6495</v>
       </c>
       <c r="K339" t="s">
@@ -17830,8 +18078,11 @@
       <c r="D340" s="1">
         <v>31</v>
       </c>
-      <c r="E340">
-        <v>6800</v>
+      <c r="E340" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F340" s="5">
+        <v>0</v>
       </c>
       <c r="G340" t="s">
         <v>1599</v>
@@ -17859,11 +18110,11 @@
       <c r="D341" s="1">
         <v>-2</v>
       </c>
-      <c r="E341" t="s">
-        <v>48</v>
-      </c>
-      <c r="F341">
-        <v>-50</v>
+      <c r="E341" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F341" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G341" t="s">
         <v>1601</v>
@@ -17894,8 +18145,11 @@
       <c r="D342" s="1">
         <v>40</v>
       </c>
-      <c r="E342">
-        <v>5200</v>
+      <c r="E342" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F342" s="5">
+        <v>0</v>
       </c>
       <c r="G342" t="s">
         <v>978</v>
@@ -17926,20 +18180,19 @@
       <c r="D343" s="1">
         <v>25</v>
       </c>
-      <c r="E343">
-        <v>9000</v>
-      </c>
-      <c r="F343">
-        <v>1000</v>
-      </c>
-      <c r="G343" s="5">
+      <c r="E343" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F343" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G343" s="2">
         <v>44848</v>
       </c>
       <c r="H343" t="s">
         <v>1606</v>
       </c>
       <c r="I343">
-        <f>974-6844-1087</f>
         <v>-6957</v>
       </c>
       <c r="K343" t="s">
@@ -17959,20 +18212,19 @@
       <c r="D344" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E344">
-        <v>6500</v>
-      </c>
-      <c r="F344" t="s">
+      <c r="E344" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F344" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G344" s="5">
+      <c r="G344" s="2">
         <v>45504</v>
       </c>
       <c r="H344" t="s">
         <v>1607</v>
       </c>
       <c r="I344">
-        <f>974-6536-4904</f>
         <v>-10466</v>
       </c>
       <c r="J344" t="s">
@@ -17995,11 +18247,11 @@
       <c r="D345" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E345" t="s">
+      <c r="E345" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F345">
-        <v>500</v>
+      <c r="F345" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G345" t="s">
         <v>1608</v>
@@ -18030,10 +18282,13 @@
       <c r="D346" s="1">
         <v>43</v>
       </c>
-      <c r="E346">
-        <v>5250</v>
-      </c>
-      <c r="G346" s="5">
+      <c r="E346" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F346" s="5">
+        <v>0</v>
+      </c>
+      <c r="G346" s="2">
         <v>45170</v>
       </c>
       <c r="H346" t="s">
@@ -18062,13 +18317,13 @@
       <c r="D347" s="1">
         <v>28</v>
       </c>
-      <c r="E347">
-        <v>8000</v>
-      </c>
-      <c r="F347">
-        <v>0</v>
-      </c>
-      <c r="G347" s="5">
+      <c r="E347" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F347" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G347" s="2">
         <v>44192</v>
       </c>
       <c r="H347" t="s">
@@ -18097,13 +18352,13 @@
       <c r="D348" s="1">
         <v>35</v>
       </c>
-      <c r="E348">
-        <v>-3000</v>
-      </c>
-      <c r="F348">
-        <v>1000</v>
-      </c>
-      <c r="G348" s="5">
+      <c r="E348" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F348" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G348" s="2">
         <v>44323</v>
       </c>
       <c r="H348" t="s">
@@ -18132,13 +18387,13 @@
       <c r="D349" s="1">
         <v>155</v>
       </c>
-      <c r="E349" t="s">
-        <v>48</v>
-      </c>
-      <c r="F349">
-        <v>-50</v>
-      </c>
-      <c r="G349" s="5">
+      <c r="E349" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F349" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G349" s="2">
         <v>45390</v>
       </c>
       <c r="H349" t="s">
@@ -18167,10 +18422,10 @@
       <c r="D350" s="1">
         <v>24</v>
       </c>
-      <c r="E350">
-        <v>7200</v>
-      </c>
-      <c r="F350" t="s">
+      <c r="E350" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F350" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G350" t="s">
@@ -18199,10 +18454,10 @@
       <c r="D351" s="1">
         <v>42</v>
       </c>
-      <c r="E351">
-        <v>5500</v>
-      </c>
-      <c r="F351" t="s">
+      <c r="E351" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F351" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G351" t="s">
@@ -18234,10 +18489,10 @@
       <c r="D352" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E352">
-        <v>6500</v>
-      </c>
-      <c r="F352" t="s">
+      <c r="E352" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F352" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G352" t="s">
@@ -18269,11 +18524,11 @@
       <c r="D353" s="1">
         <v>30</v>
       </c>
-      <c r="E353" t="s">
+      <c r="E353" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F353">
-        <v>1000</v>
+      <c r="F353" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G353" t="s">
         <v>51</v>
@@ -18301,11 +18556,11 @@
       <c r="D354" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E354">
-        <v>9000</v>
-      </c>
-      <c r="F354">
-        <v>750</v>
+      <c r="E354" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F354" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G354" t="s">
         <v>1623</v>
@@ -18336,10 +18591,13 @@
       <c r="D355" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="E355">
-        <v>4800</v>
-      </c>
-      <c r="G355" s="5">
+      <c r="E355" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F355" s="5">
+        <v>0</v>
+      </c>
+      <c r="G355" s="2">
         <v>44317</v>
       </c>
       <c r="H355" t="s">
@@ -18368,13 +18626,13 @@
       <c r="D356" s="1">
         <v>39</v>
       </c>
-      <c r="E356" t="s">
-        <v>48</v>
-      </c>
-      <c r="F356">
-        <v>500</v>
-      </c>
-      <c r="G356" s="5">
+      <c r="E356" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F356" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G356" s="2">
         <v>43862</v>
       </c>
       <c r="H356" t="s">
@@ -18403,10 +18661,10 @@
       <c r="D357" s="1">
         <v>27</v>
       </c>
-      <c r="E357">
-        <v>8500</v>
-      </c>
-      <c r="F357" t="s">
+      <c r="E357" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F357" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G357" t="s">
@@ -18438,10 +18696,10 @@
       <c r="D358" s="1">
         <v>46</v>
       </c>
-      <c r="E358">
-        <v>6200</v>
-      </c>
-      <c r="F358" t="s">
+      <c r="E358" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F358" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G358" t="s">
@@ -18470,10 +18728,10 @@
       <c r="D359" s="1">
         <v>32</v>
       </c>
-      <c r="E359">
-        <v>5750</v>
-      </c>
-      <c r="F359" t="s">
+      <c r="E359" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F359" s="5" t="s">
         <v>958</v>
       </c>
       <c r="H359" t="s">
@@ -18502,13 +18760,13 @@
       <c r="D360" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E360" t="s">
+      <c r="E360" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F360" t="s">
+      <c r="F360" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G360" s="5">
+      <c r="G360" s="2">
         <v>44783</v>
       </c>
       <c r="H360" t="s">
@@ -18534,10 +18792,13 @@
       <c r="D361" s="1">
         <v>41</v>
       </c>
-      <c r="E361">
-        <v>7000</v>
-      </c>
-      <c r="G361" s="5">
+      <c r="E361" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F361" s="5">
+        <v>0</v>
+      </c>
+      <c r="G361" s="2">
         <v>45447</v>
       </c>
       <c r="H361" t="s">
@@ -18566,11 +18827,11 @@
       <c r="D362" s="1">
         <v>23</v>
       </c>
-      <c r="E362" t="s">
-        <v>48</v>
-      </c>
-      <c r="F362">
-        <v>500</v>
+      <c r="E362" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F362" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G362" t="s">
         <v>1137</v>
@@ -18601,8 +18862,11 @@
       <c r="D363" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E363">
-        <v>6000</v>
+      <c r="E363" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F363" s="5">
+        <v>0</v>
       </c>
       <c r="G363" t="s">
         <v>1640</v>
@@ -18611,7 +18875,6 @@
         <v>1059</v>
       </c>
       <c r="I363">
-        <f>974-4293-8360</f>
         <v>-11679</v>
       </c>
       <c r="J363" t="s">
@@ -18634,11 +18897,11 @@
       <c r="D364" s="1">
         <v>36</v>
       </c>
-      <c r="E364">
-        <v>4500</v>
-      </c>
-      <c r="F364">
-        <v>750</v>
+      <c r="E364" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G364" t="s">
         <v>1641</v>
@@ -18669,13 +18932,13 @@
       <c r="D365" s="1">
         <v>18</v>
       </c>
-      <c r="E365">
-        <v>9250</v>
-      </c>
-      <c r="F365" t="s">
+      <c r="E365" s="5" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F365" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G365" s="5">
+      <c r="G365" s="2">
         <v>45135</v>
       </c>
       <c r="H365" t="s">
@@ -18704,13 +18967,13 @@
       <c r="D366" s="1">
         <v>-10</v>
       </c>
-      <c r="E366" t="s">
+      <c r="E366" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F366">
-        <v>500</v>
-      </c>
-      <c r="G366" s="5">
+      <c r="F366" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G366" s="2">
         <v>44450</v>
       </c>
       <c r="H366" t="s">
@@ -18739,11 +19002,11 @@
       <c r="D367" s="1">
         <v>34</v>
       </c>
-      <c r="E367">
-        <v>6500</v>
-      </c>
-      <c r="F367">
-        <v>250</v>
+      <c r="E367" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F367" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G367" t="s">
         <v>1646</v>
@@ -18774,13 +19037,13 @@
       <c r="D368" s="1">
         <v>29</v>
       </c>
-      <c r="E368">
-        <v>7500</v>
-      </c>
-      <c r="F368">
-        <v>750</v>
-      </c>
-      <c r="G368" s="5">
+      <c r="E368" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F368" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G368" s="2">
         <v>43681</v>
       </c>
       <c r="H368" t="s">
@@ -18806,20 +19069,19 @@
       <c r="D369" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E369" t="s">
-        <v>48</v>
-      </c>
-      <c r="F369" t="s">
+      <c r="E369" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F369" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G369" s="5">
+      <c r="G369" s="2">
         <v>43943</v>
       </c>
       <c r="H369" t="s">
         <v>1651</v>
       </c>
       <c r="I369">
-        <f>974-6537-3326</f>
         <v>-8889</v>
       </c>
       <c r="J369" t="s">
@@ -18842,10 +19104,10 @@
       <c r="D370" s="1">
         <v>47</v>
       </c>
-      <c r="E370">
-        <v>5200</v>
-      </c>
-      <c r="F370" t="s">
+      <c r="E370" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F370" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G370" t="s">
@@ -18874,13 +19136,13 @@
       <c r="D371" s="1">
         <v>25</v>
       </c>
-      <c r="E371">
-        <v>8000</v>
-      </c>
-      <c r="F371" t="s">
+      <c r="E371" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F371" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G371" s="5">
+      <c r="G371" s="2">
         <v>43479</v>
       </c>
       <c r="H371" t="s">
@@ -18909,13 +19171,13 @@
       <c r="D372" s="1">
         <v>40</v>
       </c>
-      <c r="E372">
-        <v>-1000</v>
-      </c>
-      <c r="F372">
-        <v>0</v>
-      </c>
-      <c r="G372" s="5">
+      <c r="E372" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F372" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G372" s="2">
         <v>45339</v>
       </c>
       <c r="H372" t="s">
@@ -18944,11 +19206,11 @@
       <c r="D373" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E373" t="s">
+      <c r="E373" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F373">
-        <v>-200</v>
+      <c r="F373" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G373" t="s">
         <v>1657</v>
@@ -18979,11 +19241,11 @@
       <c r="D374" s="1">
         <v>33</v>
       </c>
-      <c r="E374">
-        <v>5500</v>
-      </c>
-      <c r="F374">
-        <v>250</v>
+      <c r="E374" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F374" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G374" t="s">
         <v>48</v>
@@ -19014,11 +19276,11 @@
       <c r="D375" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E375">
-        <v>7200</v>
-      </c>
-      <c r="F375">
-        <v>250</v>
+      <c r="E375" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F375" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G375" t="s">
         <v>1661</v>
@@ -19027,7 +19289,6 @@
         <v>1662</v>
       </c>
       <c r="I375">
-        <f>974-6648-1959</f>
         <v>-7633</v>
       </c>
       <c r="J375" t="s">
@@ -19050,11 +19311,11 @@
       <c r="D376" s="1">
         <v>38</v>
       </c>
-      <c r="E376" t="s">
-        <v>48</v>
-      </c>
-      <c r="F376">
-        <v>500</v>
+      <c r="E376" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F376" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G376" t="s">
         <v>1663</v>
@@ -19085,11 +19346,11 @@
       <c r="D377" s="1">
         <v>21</v>
       </c>
-      <c r="E377">
-        <v>6750</v>
-      </c>
-      <c r="F377">
-        <v>500</v>
+      <c r="E377" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F377" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G377" t="s">
         <v>1665</v>
@@ -19120,13 +19381,13 @@
       <c r="D378" s="1">
         <v>145</v>
       </c>
-      <c r="E378">
-        <v>4800</v>
-      </c>
-      <c r="F378" t="s">
-        <v>48</v>
-      </c>
-      <c r="G378" s="5">
+      <c r="E378" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F378" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G378" s="2">
         <v>44100</v>
       </c>
       <c r="H378" t="s">
@@ -19152,13 +19413,13 @@
       <c r="D379" s="1">
         <v>31</v>
       </c>
-      <c r="E379">
-        <v>9000</v>
-      </c>
-      <c r="F379">
-        <v>500</v>
-      </c>
-      <c r="G379" s="5">
+      <c r="E379" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F379" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G379" s="2">
         <v>45159</v>
       </c>
       <c r="H379" t="s">
@@ -19187,10 +19448,10 @@
       <c r="D380" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="E380" t="s">
+      <c r="E380" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F380" t="s">
+      <c r="F380" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G380" t="s">
@@ -19222,10 +19483,10 @@
       <c r="D381" s="1">
         <v>44</v>
       </c>
-      <c r="E381">
-        <v>6200</v>
-      </c>
-      <c r="F381" t="s">
+      <c r="E381" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F381" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G381" t="s">
@@ -19257,11 +19518,11 @@
       <c r="D382" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E382">
-        <v>4750</v>
-      </c>
-      <c r="F382">
-        <v>750</v>
+      <c r="E382" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F382" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G382" t="s">
         <v>1049</v>
@@ -19292,20 +19553,19 @@
       <c r="D383" s="1">
         <v>30</v>
       </c>
-      <c r="E383" t="s">
-        <v>48</v>
-      </c>
-      <c r="F383">
-        <v>250</v>
-      </c>
-      <c r="G383" s="5">
+      <c r="E383" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F383" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G383" s="2">
         <v>44114</v>
       </c>
       <c r="H383" t="s">
         <v>1678</v>
       </c>
       <c r="I383">
-        <f>974-3182-5870</f>
         <v>-8078</v>
       </c>
       <c r="J383" t="s">
@@ -19328,13 +19588,13 @@
       <c r="D384" s="1">
         <v>26</v>
       </c>
-      <c r="E384">
-        <v>8200</v>
-      </c>
-      <c r="F384">
-        <v>-50</v>
-      </c>
-      <c r="G384" s="5">
+      <c r="E384" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F384" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G384" s="2">
         <v>44904</v>
       </c>
       <c r="H384" t="s">
@@ -19363,11 +19623,11 @@
       <c r="D385" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E385">
-        <v>5500</v>
-      </c>
-      <c r="F385" s="2">
-        <v>500</v>
+      <c r="E385" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G385" t="s">
         <v>1680</v>
@@ -19398,10 +19658,10 @@
       <c r="D386" s="1">
         <v>37</v>
       </c>
-      <c r="E386">
-        <v>7000</v>
-      </c>
-      <c r="F386" t="s">
+      <c r="E386" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F386" s="5" t="s">
         <v>1010</v>
       </c>
       <c r="G386" t="s">
@@ -19433,10 +19693,10 @@
       <c r="D387" s="1">
         <v>19</v>
       </c>
-      <c r="E387" t="s">
+      <c r="E387" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F387" t="s">
+      <c r="F387" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G387" t="s">
@@ -19468,13 +19728,13 @@
       <c r="D388" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E388">
-        <v>6500</v>
-      </c>
-      <c r="F388" t="s">
+      <c r="E388" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F388" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G388" s="5">
+      <c r="G388" s="2">
         <v>45748</v>
       </c>
       <c r="H388" t="s">
@@ -19503,13 +19763,13 @@
       <c r="D389" s="1">
         <v>42</v>
       </c>
-      <c r="E389">
-        <v>5250</v>
-      </c>
-      <c r="F389">
-        <v>1250</v>
-      </c>
-      <c r="G389" s="5">
+      <c r="E389" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G389" s="2">
         <v>44159</v>
       </c>
       <c r="H389" t="s">
@@ -19538,10 +19798,10 @@
       <c r="D390" s="1">
         <v>35</v>
       </c>
-      <c r="E390" t="s">
-        <v>48</v>
-      </c>
-      <c r="F390" t="s">
+      <c r="E390" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F390" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G390" t="s">
@@ -19573,13 +19833,13 @@
       <c r="D391" s="1">
         <v>28</v>
       </c>
-      <c r="E391">
-        <v>9000</v>
-      </c>
-      <c r="F391">
-        <v>1000</v>
-      </c>
-      <c r="G391" s="5">
+      <c r="E391" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F391" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G391" s="2">
         <v>44810</v>
       </c>
       <c r="H391" t="s">
@@ -19608,11 +19868,11 @@
       <c r="D392" s="1">
         <v>-4</v>
       </c>
-      <c r="E392">
-        <v>6500</v>
-      </c>
-      <c r="F392">
-        <v>-200</v>
+      <c r="E392" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G392" t="s">
         <v>1696</v>
@@ -19643,10 +19903,10 @@
       <c r="D393" s="1">
         <v>49</v>
       </c>
-      <c r="E393">
-        <v>-500</v>
-      </c>
-      <c r="F393" t="s">
+      <c r="E393" s="5" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F393" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G393" t="s">
@@ -19678,10 +19938,13 @@
       <c r="D394" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E394" t="s">
+      <c r="E394" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G394" s="5">
+      <c r="F394" s="5">
+        <v>0</v>
+      </c>
+      <c r="G394" s="2">
         <v>44404</v>
       </c>
       <c r="H394" t="s">
@@ -19710,20 +19973,19 @@
       <c r="D395" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E395">
-        <v>7750</v>
-      </c>
-      <c r="F395">
-        <v>250</v>
-      </c>
-      <c r="G395" s="5">
+      <c r="E395" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F395" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G395" s="2">
         <v>45601</v>
       </c>
       <c r="H395" t="s">
         <v>1703</v>
       </c>
       <c r="I395">
-        <f>974-4275-8364</f>
         <v>-11665</v>
       </c>
       <c r="J395" t="s">
@@ -19746,13 +20008,13 @@
       <c r="D396" s="1">
         <v>32</v>
       </c>
-      <c r="E396">
-        <v>4800</v>
-      </c>
-      <c r="F396">
-        <v>1000</v>
-      </c>
-      <c r="G396" s="5">
+      <c r="E396" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F396" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G396" s="2">
         <v>45385</v>
       </c>
       <c r="H396" t="s">
@@ -19778,11 +20040,11 @@
       <c r="D397" s="1">
         <v>41</v>
       </c>
-      <c r="E397" t="s">
-        <v>48</v>
-      </c>
-      <c r="F397">
-        <v>250</v>
+      <c r="E397" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F397" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G397" t="s">
         <v>1706</v>
@@ -19791,7 +20053,6 @@
         <v>1707</v>
       </c>
       <c r="I397">
-        <f>974-3133-3171</f>
         <v>-5330</v>
       </c>
       <c r="J397" t="s">
@@ -19814,13 +20075,13 @@
       <c r="D398" s="1">
         <v>24</v>
       </c>
-      <c r="E398">
-        <v>5000</v>
-      </c>
-      <c r="F398" t="s">
-        <v>48</v>
-      </c>
-      <c r="G398" s="5">
+      <c r="E398" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F398" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G398" s="2">
         <v>43523</v>
       </c>
       <c r="H398" t="s">
@@ -19849,11 +20110,11 @@
       <c r="D399" s="1">
         <v>36</v>
       </c>
-      <c r="E399">
-        <v>7200</v>
-      </c>
-      <c r="F399" s="2">
-        <v>500</v>
+      <c r="E399" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F399" s="5" t="s">
+        <v>1897</v>
       </c>
       <c r="G399" t="s">
         <v>1003</v>
@@ -19884,13 +20145,13 @@
       <c r="D400" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E400">
-        <v>8500</v>
-      </c>
-      <c r="F400">
-        <v>500</v>
-      </c>
-      <c r="G400" s="5">
+      <c r="E400" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F400" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G400" s="2">
         <v>44660</v>
       </c>
       <c r="H400" t="s">
@@ -19919,13 +20180,13 @@
       <c r="D401" s="1">
         <v>27</v>
       </c>
-      <c r="E401" t="s">
+      <c r="E401" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F401" t="s">
+      <c r="F401" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G401" s="5">
+      <c r="G401" s="2">
         <v>44454</v>
       </c>
       <c r="H401" t="s">
@@ -19954,11 +20215,11 @@
       <c r="D402" s="1">
         <v>43</v>
       </c>
-      <c r="E402">
-        <v>6200</v>
-      </c>
-      <c r="F402">
-        <v>750</v>
+      <c r="E402" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F402" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G402" t="s">
         <v>51</v>
@@ -19989,20 +20250,19 @@
       <c r="D403" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E403">
-        <v>6250</v>
-      </c>
-      <c r="F403" t="s">
+      <c r="E403" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F403" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G403" s="5">
+      <c r="G403" s="2">
         <v>45094</v>
       </c>
       <c r="H403" t="s">
         <v>1716</v>
       </c>
       <c r="I403">
-        <f>974-7979-1861</f>
         <v>-8866</v>
       </c>
       <c r="J403" t="s">
@@ -20025,13 +20285,13 @@
       <c r="D404" s="1">
         <v>30</v>
       </c>
-      <c r="E404" t="s">
-        <v>48</v>
-      </c>
-      <c r="F404">
-        <v>1000</v>
-      </c>
-      <c r="G404" s="5">
+      <c r="E404" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F404" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G404" s="2">
         <v>45408</v>
       </c>
       <c r="H404" t="s">
@@ -20057,11 +20317,11 @@
       <c r="D405" s="1">
         <v>160</v>
       </c>
-      <c r="E405">
-        <v>4500</v>
-      </c>
-      <c r="F405">
-        <v>300</v>
+      <c r="E405" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F405" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G405" t="s">
         <v>1719</v>
@@ -20092,11 +20352,11 @@
       <c r="D406" s="1">
         <v>39</v>
       </c>
-      <c r="E406">
-        <v>9500</v>
-      </c>
-      <c r="F406">
-        <v>500</v>
+      <c r="E406" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F406" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G406" t="s">
         <v>1722</v>
@@ -20105,7 +20365,6 @@
         <v>1723</v>
       </c>
       <c r="I406">
-        <f>974-3386-1313</f>
         <v>-3725</v>
       </c>
       <c r="J406" t="s">
@@ -20128,11 +20387,11 @@
       <c r="D407" s="1">
         <v>22</v>
       </c>
-      <c r="E407">
-        <v>6500</v>
-      </c>
-      <c r="F407">
-        <v>500</v>
+      <c r="E407" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F407" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G407" t="s">
         <v>1724</v>
@@ -20163,13 +20422,13 @@
       <c r="D408" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E408" t="s">
+      <c r="E408" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F408" t="s">
-        <v>48</v>
-      </c>
-      <c r="G408" s="5">
+      <c r="F408" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G408" s="2">
         <v>44479</v>
       </c>
       <c r="H408" t="s">
@@ -20198,13 +20457,13 @@
       <c r="D409" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E409">
-        <v>5750</v>
-      </c>
-      <c r="F409">
-        <v>500</v>
-      </c>
-      <c r="G409" s="5">
+      <c r="E409" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F409" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G409" s="2">
         <v>43930</v>
       </c>
       <c r="H409" t="s">
@@ -20233,11 +20492,11 @@
       <c r="D410" s="1">
         <v>34</v>
       </c>
-      <c r="E410">
-        <v>8000</v>
-      </c>
-      <c r="F410">
-        <v>500</v>
+      <c r="E410" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F410" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G410" t="s">
         <v>1730</v>
@@ -20268,11 +20527,11 @@
       <c r="D411" s="1">
         <v>45</v>
       </c>
-      <c r="E411" t="s">
-        <v>48</v>
-      </c>
-      <c r="F411">
-        <v>500</v>
+      <c r="E411" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F411" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G411" t="s">
         <v>1733</v>
@@ -20303,13 +20562,13 @@
       <c r="D412" s="1">
         <v>29</v>
       </c>
-      <c r="E412">
-        <v>7200</v>
-      </c>
-      <c r="F412">
-        <v>250</v>
-      </c>
-      <c r="G412" s="5">
+      <c r="E412" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F412" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G412" s="2">
         <v>45574</v>
       </c>
       <c r="H412" t="s">
@@ -20338,11 +20597,11 @@
       <c r="D413" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E413">
-        <v>5200</v>
-      </c>
-      <c r="F413">
-        <v>-200</v>
+      <c r="E413" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F413" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G413" t="s">
         <v>51</v>
@@ -20373,13 +20632,13 @@
       <c r="D414" s="1">
         <v>18</v>
       </c>
-      <c r="E414">
-        <v>-2000</v>
-      </c>
-      <c r="F414" t="s">
+      <c r="E414" s="5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F414" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G414" s="5">
+      <c r="G414" s="2">
         <v>45575</v>
       </c>
       <c r="H414" t="s">
@@ -20405,13 +20664,13 @@
       <c r="D415" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E415" t="s">
+      <c r="E415" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F415">
-        <v>0</v>
-      </c>
-      <c r="G415" s="5">
+      <c r="F415" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G415" s="2">
         <v>43792</v>
       </c>
       <c r="H415" t="s">
@@ -20440,11 +20699,11 @@
       <c r="D416" s="1">
         <v>37</v>
       </c>
-      <c r="E416">
-        <v>6500</v>
-      </c>
-      <c r="F416">
-        <v>750</v>
+      <c r="E416" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F416" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G416" t="s">
         <v>1742</v>
@@ -20475,13 +20734,13 @@
       <c r="D417" s="1">
         <v>25</v>
       </c>
-      <c r="E417">
-        <v>9000</v>
-      </c>
-      <c r="F417">
-        <v>1000</v>
-      </c>
-      <c r="G417" s="5">
+      <c r="E417" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F417" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G417" s="2">
         <v>45383</v>
       </c>
       <c r="H417" t="s">
@@ -20510,13 +20769,13 @@
       <c r="D418" s="1">
         <v>42</v>
       </c>
-      <c r="E418" t="s">
-        <v>48</v>
-      </c>
-      <c r="F418" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G418" s="5">
+      <c r="E418" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F418" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G418" s="2">
         <v>44545</v>
       </c>
       <c r="H418" t="s">
@@ -20545,11 +20804,11 @@
       <c r="D419" s="1">
         <v>-1</v>
       </c>
-      <c r="E419">
-        <v>4800</v>
-      </c>
-      <c r="F419">
-        <v>300</v>
+      <c r="E419" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F419" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G419" t="s">
         <v>1748</v>
@@ -20580,11 +20839,11 @@
       <c r="D420" s="1">
         <v>31</v>
       </c>
-      <c r="E420">
-        <v>8000</v>
-      </c>
-      <c r="F420" s="2">
-        <v>750</v>
+      <c r="E420" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F420" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G420" t="s">
         <v>1751</v>
@@ -20615,10 +20874,10 @@
       <c r="D421" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E421">
-        <v>5500</v>
-      </c>
-      <c r="F421" t="s">
+      <c r="E421" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F421" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G421" t="s">
@@ -20650,11 +20909,11 @@
       <c r="D422" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E422" t="s">
+      <c r="E422" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F422">
-        <v>300</v>
+      <c r="F422" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G422" t="s">
         <v>1137</v>
@@ -20663,7 +20922,6 @@
         <v>1756</v>
       </c>
       <c r="I422">
-        <f>974-3777-6084</f>
         <v>-8887</v>
       </c>
       <c r="J422" t="s">
@@ -20686,11 +20944,11 @@
       <c r="D423" s="1">
         <v>44</v>
       </c>
-      <c r="E423">
-        <v>7500</v>
-      </c>
-      <c r="F423">
-        <v>-200</v>
+      <c r="E423" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F423" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G423" t="s">
         <v>1757</v>
@@ -20721,11 +20979,11 @@
       <c r="D424" s="1">
         <v>33</v>
       </c>
-      <c r="E424">
-        <v>6200</v>
-      </c>
-      <c r="F424">
-        <v>500</v>
+      <c r="E424" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F424" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G424" t="s">
         <v>1759</v>
@@ -20756,10 +21014,10 @@
       <c r="D425" s="1">
         <v>20</v>
       </c>
-      <c r="E425" t="s">
-        <v>48</v>
-      </c>
-      <c r="F425" t="s">
+      <c r="E425" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F425" s="5" t="s">
         <v>1010</v>
       </c>
       <c r="G425" t="s">
@@ -20791,13 +21049,13 @@
       <c r="D426" s="1">
         <v>38</v>
       </c>
-      <c r="E426">
-        <v>5250</v>
-      </c>
-      <c r="F426" t="s">
+      <c r="E426" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F426" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G426" s="5">
+      <c r="G426" s="2">
         <v>44995</v>
       </c>
       <c r="H426" t="s">
@@ -20826,20 +21084,19 @@
       <c r="D427" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E427">
-        <v>7200</v>
-      </c>
-      <c r="F427">
-        <v>250</v>
-      </c>
-      <c r="G427" s="5">
+      <c r="E427" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F427" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G427" s="2">
         <v>44199</v>
       </c>
       <c r="H427" t="s">
         <v>1765</v>
       </c>
       <c r="I427">
-        <f>974-4343-4332</f>
         <v>-7701</v>
       </c>
       <c r="J427" t="s">
@@ -20862,11 +21119,11 @@
       <c r="D428" s="1">
         <v>26</v>
       </c>
-      <c r="E428">
-        <v>9000</v>
-      </c>
-      <c r="F428">
-        <v>-200</v>
+      <c r="E428" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F428" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G428" t="s">
         <v>1766</v>
@@ -20897,20 +21154,19 @@
       <c r="D429" s="1">
         <v>47</v>
       </c>
-      <c r="E429" t="s">
+      <c r="E429" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F429">
-        <v>300</v>
-      </c>
-      <c r="G429" s="5">
+      <c r="F429" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G429" s="2">
         <v>43952</v>
       </c>
       <c r="H429" t="s">
         <v>1769</v>
       </c>
       <c r="I429">
-        <f>974-3432-3162</f>
         <v>-5620</v>
       </c>
       <c r="J429" t="s">
@@ -20933,11 +21189,11 @@
       <c r="D430" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E430">
-        <v>6500</v>
-      </c>
-      <c r="F430">
-        <v>500</v>
+      <c r="E430" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F430" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G430" t="s">
         <v>1137</v>
@@ -20965,13 +21221,13 @@
       <c r="D431" s="1">
         <v>35</v>
       </c>
-      <c r="E431" t="s">
-        <v>48</v>
-      </c>
-      <c r="F431">
-        <v>250</v>
-      </c>
-      <c r="G431" s="5">
+      <c r="E431" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F431" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G431" s="2">
         <v>45583</v>
       </c>
       <c r="H431" t="s">
@@ -21000,13 +21256,13 @@
       <c r="D432" s="1">
         <v>150</v>
       </c>
-      <c r="E432">
-        <v>6800</v>
-      </c>
-      <c r="F432" t="s">
+      <c r="E432" s="5" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F432" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="G432" s="5">
+      <c r="G432" s="2">
         <v>43952</v>
       </c>
       <c r="H432" t="s">
@@ -21035,11 +21291,11 @@
       <c r="D433" s="1">
         <v>30</v>
       </c>
-      <c r="E433">
-        <v>4800</v>
-      </c>
-      <c r="F433">
-        <v>500</v>
+      <c r="E433" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F433" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G433" t="s">
         <v>1003</v>
@@ -21070,11 +21326,11 @@
       <c r="D434" s="1">
         <v>23</v>
       </c>
-      <c r="E434">
-        <v>8250</v>
-      </c>
-      <c r="F434">
-        <v>750</v>
+      <c r="E434" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F434" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G434" t="s">
         <v>1775</v>
@@ -21105,13 +21361,13 @@
       <c r="D435" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E435">
-        <v>-1500</v>
-      </c>
-      <c r="F435">
-        <v>300</v>
-      </c>
-      <c r="G435" s="5">
+      <c r="E435" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F435" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G435" s="2">
         <v>45264</v>
       </c>
       <c r="H435" t="s">
@@ -21140,13 +21396,13 @@
       <c r="D436" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="E436" t="s">
+      <c r="E436" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F436" t="s">
+      <c r="F436" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="G436" s="5">
+      <c r="G436" s="2">
         <v>44000</v>
       </c>
       <c r="I436" t="s">
@@ -21172,10 +21428,10 @@
       <c r="D437" s="1">
         <v>40</v>
       </c>
-      <c r="E437">
-        <v>5500</v>
-      </c>
-      <c r="F437" t="s">
+      <c r="E437" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F437" s="5" t="s">
         <v>1014</v>
       </c>
       <c r="G437" t="s">
@@ -21207,20 +21463,19 @@
       <c r="D438" s="1">
         <v>32</v>
       </c>
-      <c r="E438">
-        <v>7000</v>
-      </c>
-      <c r="F438" t="s">
+      <c r="E438" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F438" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G438" s="5">
+      <c r="G438" s="2">
         <v>43520</v>
       </c>
       <c r="H438" t="s">
         <v>1781</v>
       </c>
       <c r="I438">
-        <f>974-6629-9664</f>
         <v>-15319</v>
       </c>
       <c r="J438" t="s">
@@ -21243,20 +21498,19 @@
       <c r="D439" s="1">
         <v>28</v>
       </c>
-      <c r="E439" t="s">
-        <v>48</v>
-      </c>
-      <c r="F439" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G439" s="5">
+      <c r="E439" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F439" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G439" s="2">
         <v>45551</v>
       </c>
       <c r="H439" t="s">
         <v>1782</v>
       </c>
       <c r="I439">
-        <f>974-5756-8104</f>
         <v>-12886</v>
       </c>
       <c r="J439" t="s">
@@ -21279,11 +21533,11 @@
       <c r="D440" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E440">
-        <v>9250</v>
-      </c>
-      <c r="F440">
-        <v>-50</v>
+      <c r="E440" s="5" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F440" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G440" t="s">
         <v>1783</v>
@@ -21314,13 +21568,13 @@
       <c r="D441" s="1">
         <v>19</v>
       </c>
-      <c r="E441">
-        <v>5200</v>
-      </c>
-      <c r="F441">
-        <v>500</v>
-      </c>
-      <c r="G441" s="5">
+      <c r="E441" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F441" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G441" s="2">
         <v>45650</v>
       </c>
       <c r="H441" t="s">
@@ -21346,10 +21600,10 @@
       <c r="D442" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E442">
-        <v>6500</v>
-      </c>
-      <c r="F442" t="s">
+      <c r="E442" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F442" s="5" t="s">
         <v>958</v>
       </c>
       <c r="G442" t="s">
@@ -21359,7 +21613,6 @@
         <v>1789</v>
       </c>
       <c r="I442">
-        <f>974-6768-7821</f>
         <v>-13615</v>
       </c>
       <c r="J442" t="s">
@@ -21382,13 +21635,13 @@
       <c r="D443" s="1">
         <v>41</v>
       </c>
-      <c r="E443" t="s">
+      <c r="E443" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F443" t="s">
+      <c r="F443" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="G443" s="5">
+      <c r="G443" s="2">
         <v>44291</v>
       </c>
       <c r="H443" t="s">
@@ -21417,11 +21670,11 @@
       <c r="D444" s="1">
         <v>36</v>
       </c>
-      <c r="E444">
-        <v>8000</v>
-      </c>
-      <c r="F444">
-        <v>250</v>
+      <c r="E444" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F444" s="5" t="s">
+        <v>1922</v>
       </c>
       <c r="G444" t="s">
         <v>1792</v>
@@ -21452,13 +21705,13 @@
       <c r="D445" s="1">
         <v>25</v>
       </c>
-      <c r="E445">
-        <v>4750</v>
-      </c>
-      <c r="F445">
-        <v>1000</v>
-      </c>
-      <c r="G445" s="5">
+      <c r="E445" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F445" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G445" s="2">
         <v>43533</v>
       </c>
       <c r="H445" t="s">
@@ -21487,10 +21740,10 @@
       <c r="D446" s="1">
         <v>-6</v>
       </c>
-      <c r="E446" t="s">
-        <v>48</v>
-      </c>
-      <c r="F446" t="s">
+      <c r="E446" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F446" s="5" t="s">
         <v>970</v>
       </c>
       <c r="G446" t="s">
@@ -21500,7 +21753,6 @@
         <v>1797</v>
       </c>
       <c r="I446">
-        <f>974-4863-2991</f>
         <v>-6880</v>
       </c>
       <c r="J446" t="s">
@@ -21523,10 +21775,10 @@
       <c r="D447" s="1">
         <v>43</v>
       </c>
-      <c r="E447">
-        <v>7000</v>
-      </c>
-      <c r="F447" t="s">
+      <c r="E447" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F447" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G447" t="s">
@@ -21558,10 +21810,13 @@
       <c r="D448" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E448">
-        <v>6200</v>
-      </c>
-      <c r="G448" s="5">
+      <c r="E448" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F448" s="5">
+        <v>0</v>
+      </c>
+      <c r="G448" s="2">
         <v>44697</v>
       </c>
       <c r="H448" t="s">
@@ -21587,11 +21842,11 @@
       <c r="D449" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E449">
-        <v>5750</v>
-      </c>
-      <c r="F449">
-        <v>-200</v>
+      <c r="E449" s="5" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F449" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G449" t="s">
         <v>1802</v>
@@ -21622,17 +21877,16 @@
       <c r="D450" s="1">
         <v>29</v>
       </c>
-      <c r="E450" t="s">
+      <c r="E450" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F450">
-        <v>1000</v>
-      </c>
-      <c r="G450" s="5">
+      <c r="F450" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G450" s="2">
         <v>44471</v>
       </c>
       <c r="I450">
-        <f>974-4106-7589</f>
         <v>-10721</v>
       </c>
       <c r="J450" t="s">
@@ -21655,10 +21909,10 @@
       <c r="D451" s="1">
         <v>34</v>
       </c>
-      <c r="E451">
-        <v>8500</v>
-      </c>
-      <c r="F451" t="s">
+      <c r="E451" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F451" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G451" t="s">
@@ -21690,10 +21944,10 @@
       <c r="D452" s="1">
         <v>21</v>
       </c>
-      <c r="E452">
-        <v>4500</v>
-      </c>
-      <c r="F452" t="s">
+      <c r="E452" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F452" s="5" t="s">
         <v>1157</v>
       </c>
       <c r="G452" t="s">
@@ -21725,20 +21979,19 @@
       <c r="D453" s="1">
         <v>45</v>
       </c>
-      <c r="E453" t="s">
-        <v>48</v>
-      </c>
-      <c r="F453">
-        <v>1250</v>
-      </c>
-      <c r="G453" s="5">
+      <c r="E453" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F453" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G453" s="2">
         <v>44623</v>
       </c>
       <c r="H453" t="s">
         <v>1807</v>
       </c>
       <c r="I453">
-        <f>974-6184-8013</f>
         <v>-13223</v>
       </c>
       <c r="J453" t="s">
@@ -21761,11 +22014,11 @@
       <c r="D454" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E454">
-        <v>6250</v>
-      </c>
-      <c r="F454">
-        <v>500</v>
+      <c r="E454" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F454" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G454" t="s">
         <v>1808</v>
@@ -21796,13 +22049,13 @@
       <c r="D455" s="1">
         <v>38</v>
       </c>
-      <c r="E455">
-        <v>9000</v>
-      </c>
-      <c r="F455" t="s">
+      <c r="E455" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F455" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="G455" s="5">
+      <c r="G455" s="2">
         <v>44310</v>
       </c>
       <c r="H455" t="s">
@@ -21828,13 +22081,13 @@
       <c r="D456" s="1">
         <v>27</v>
       </c>
-      <c r="E456">
-        <v>-2500</v>
-      </c>
-      <c r="F456">
-        <v>750</v>
-      </c>
-      <c r="G456" s="5">
+      <c r="E456" s="5" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F456" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G456" s="2">
         <v>45482</v>
       </c>
       <c r="H456" t="s">
@@ -21863,11 +22116,11 @@
       <c r="D457" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E457" t="s">
+      <c r="E457" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F457">
-        <v>300</v>
+      <c r="F457" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G457" t="s">
         <v>1813</v>
@@ -21898,10 +22151,10 @@
       <c r="D458" s="1">
         <v>31</v>
       </c>
-      <c r="E458">
-        <v>5000</v>
-      </c>
-      <c r="F458" t="s">
+      <c r="E458" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F458" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G458" t="s">
@@ -21911,7 +22164,6 @@
         <v>1817</v>
       </c>
       <c r="I458">
-        <f>974-5701-6106</f>
         <v>-10833</v>
       </c>
       <c r="J458" t="s">
@@ -21934,13 +22186,13 @@
       <c r="D459" s="1">
         <v>175</v>
       </c>
-      <c r="E459">
-        <v>7200</v>
-      </c>
-      <c r="F459">
-        <v>250</v>
-      </c>
-      <c r="G459" s="5">
+      <c r="E459" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F459" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G459" s="2">
         <v>44361</v>
       </c>
       <c r="H459" t="s">
@@ -21969,11 +22221,11 @@
       <c r="D460" s="1">
         <v>42</v>
       </c>
-      <c r="E460" t="s">
-        <v>48</v>
-      </c>
-      <c r="F460">
-        <v>0</v>
+      <c r="E460" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F460" s="5" t="s">
+        <v>1938</v>
       </c>
       <c r="G460" t="s">
         <v>1820</v>
@@ -22004,10 +22256,10 @@
       <c r="D461" s="1">
         <v>24</v>
       </c>
-      <c r="E461">
-        <v>7500</v>
-      </c>
-      <c r="F461" t="s">
+      <c r="E461" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F461" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G461" t="s">
@@ -22017,7 +22269,6 @@
         <v>1824</v>
       </c>
       <c r="I461">
-        <f>974-6523-9980</f>
         <v>-15529</v>
       </c>
       <c r="J461" t="s">
@@ -22040,11 +22291,11 @@
       <c r="D462" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E462">
-        <v>5500</v>
-      </c>
-      <c r="F462">
-        <v>750</v>
+      <c r="E462" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F462" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G462" t="s">
         <v>1825</v>
@@ -22075,11 +22326,11 @@
       <c r="D463" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="E463">
-        <v>8000</v>
-      </c>
-      <c r="F463">
-        <v>500</v>
+      <c r="E463" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F463" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G463" t="s">
         <v>1828</v>
@@ -22110,13 +22361,13 @@
       <c r="D464" s="1">
         <v>39</v>
       </c>
-      <c r="E464" t="s">
+      <c r="E464" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F464">
-        <v>750</v>
-      </c>
-      <c r="G464" s="5">
+      <c r="F464" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G464" s="2">
         <v>43931</v>
       </c>
       <c r="H464" t="s">
@@ -22145,11 +22396,11 @@
       <c r="D465" s="1">
         <v>33</v>
       </c>
-      <c r="E465">
-        <v>6500</v>
-      </c>
-      <c r="F465">
-        <v>1000</v>
+      <c r="E465" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F465" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G465" t="s">
         <v>1003</v>
@@ -22158,7 +22409,6 @@
         <v>1832</v>
       </c>
       <c r="I465">
-        <f>974-7977-1000</f>
         <v>-8003</v>
       </c>
       <c r="J465" t="s">
@@ -22181,13 +22431,13 @@
       <c r="D466" s="1">
         <v>30</v>
       </c>
-      <c r="E466" t="s">
-        <v>48</v>
-      </c>
-      <c r="F466">
-        <v>500</v>
-      </c>
-      <c r="G466" s="5">
+      <c r="E466" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F466" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G466" s="2">
         <v>43471</v>
       </c>
       <c r="H466" t="s">
@@ -22216,20 +22466,19 @@
       <c r="D467" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E467">
-        <v>4800</v>
-      </c>
-      <c r="F467">
-        <v>1000</v>
-      </c>
-      <c r="G467" s="5">
+      <c r="E467" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F467" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G467" s="2">
         <v>45066</v>
       </c>
       <c r="H467" t="s">
         <v>1556</v>
       </c>
       <c r="I467">
-        <f>974-4032-1792</f>
         <v>-4850</v>
       </c>
       <c r="J467" t="s">
@@ -22252,11 +22501,11 @@
       <c r="D468" s="1">
         <v>22</v>
       </c>
-      <c r="E468">
-        <v>9500</v>
-      </c>
-      <c r="F468">
-        <v>1250</v>
+      <c r="E468" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F468" s="5" t="s">
+        <v>1913</v>
       </c>
       <c r="G468" t="s">
         <v>1137</v>
@@ -22287,13 +22536,13 @@
       <c r="D469" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E469">
-        <v>6200</v>
-      </c>
-      <c r="F469">
-        <v>500</v>
-      </c>
-      <c r="G469" s="5">
+      <c r="E469" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F469" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G469" s="2">
         <v>45472</v>
       </c>
       <c r="H469" t="s">
@@ -22322,20 +22571,19 @@
       <c r="D470" s="1">
         <v>46</v>
       </c>
-      <c r="E470" t="s">
+      <c r="E470" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F470">
-        <v>750</v>
-      </c>
-      <c r="G470" s="5">
+      <c r="F470" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G470" s="2">
         <v>45613</v>
       </c>
       <c r="H470" t="s">
         <v>1836</v>
       </c>
       <c r="I470">
-        <f>974-6307-8049</f>
         <v>-13382</v>
       </c>
       <c r="J470" t="s">
@@ -22358,13 +22606,13 @@
       <c r="D471" s="1">
         <v>35</v>
       </c>
-      <c r="E471">
-        <v>6500</v>
-      </c>
-      <c r="F471" t="s">
+      <c r="E471" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F471" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="G471" s="5">
+      <c r="G471" s="2">
         <v>44433</v>
       </c>
       <c r="H471" t="s">
@@ -22393,13 +22641,13 @@
       <c r="D472" s="1">
         <v>28</v>
       </c>
-      <c r="E472">
-        <v>4800</v>
-      </c>
-      <c r="F472">
-        <v>500</v>
-      </c>
-      <c r="G472" s="5">
+      <c r="E472" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F472" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G472" s="2">
         <v>45607</v>
       </c>
       <c r="H472" t="s">
@@ -22428,11 +22676,11 @@
       <c r="D473" s="1">
         <v>-3</v>
       </c>
-      <c r="E473" t="s">
-        <v>48</v>
-      </c>
-      <c r="F473">
-        <v>750</v>
+      <c r="E473" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F473" s="5" t="s">
+        <v>1925</v>
       </c>
       <c r="G473" t="s">
         <v>48</v>
@@ -22463,13 +22711,13 @@
       <c r="D474" s="1">
         <v>41</v>
       </c>
-      <c r="E474">
-        <v>7200</v>
-      </c>
-      <c r="F474" s="2">
-        <v>500</v>
-      </c>
-      <c r="G474" s="5">
+      <c r="E474" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F474" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G474" s="2">
         <v>44677</v>
       </c>
       <c r="H474" t="s">
@@ -22498,13 +22746,13 @@
       <c r="D475" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E475">
-        <v>5500</v>
-      </c>
-      <c r="F475">
-        <v>1000</v>
-      </c>
-      <c r="G475" s="5">
+      <c r="E475" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F475" s="5" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G475" s="2">
         <v>44929</v>
       </c>
       <c r="H475" t="s">
@@ -22533,13 +22781,13 @@
       <c r="D476" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E476">
-        <v>-1000</v>
-      </c>
-      <c r="F476" t="s">
+      <c r="E476" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F476" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="G476" s="5">
+      <c r="G476" s="2">
         <v>43474</v>
       </c>
       <c r="H476" t="s">
@@ -22568,10 +22816,10 @@
       <c r="D477" s="1">
         <v>25</v>
       </c>
-      <c r="E477" t="s">
+      <c r="E477" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F477" t="s">
+      <c r="F477" s="5" t="s">
         <v>1055</v>
       </c>
       <c r="G477" t="s">
@@ -22603,13 +22851,13 @@
       <c r="D478" s="1">
         <v>37</v>
       </c>
-      <c r="E478">
-        <v>8250</v>
-      </c>
-      <c r="F478">
-        <v>300</v>
-      </c>
-      <c r="G478" s="5">
+      <c r="E478" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F478" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G478" s="2">
         <v>44970</v>
       </c>
       <c r="H478" t="s">
@@ -22638,11 +22886,11 @@
       <c r="D479" s="1">
         <v>19</v>
       </c>
-      <c r="E479">
-        <v>6500</v>
-      </c>
-      <c r="F479">
-        <v>300</v>
+      <c r="E479" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F479" s="5" t="s">
+        <v>1909</v>
       </c>
       <c r="G479" t="s">
         <v>1853</v>
@@ -22673,11 +22921,11 @@
       <c r="D480" s="1">
         <v>44</v>
       </c>
-      <c r="E480" t="s">
-        <v>48</v>
-      </c>
-      <c r="F480" s="2">
-        <v>750</v>
+      <c r="E480" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F480" s="5" t="s">
+        <v>1944</v>
       </c>
       <c r="G480" t="s">
         <v>1856</v>
@@ -22686,7 +22934,6 @@
         <v>1857</v>
       </c>
       <c r="I480">
-        <f>974-3923-9757</f>
         <v>-12706</v>
       </c>
       <c r="J480" t="s">
@@ -22709,11 +22956,11 @@
       <c r="D481" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E481">
-        <v>5250</v>
-      </c>
-      <c r="F481">
-        <v>-50</v>
+      <c r="E481" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F481" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G481" t="s">
         <v>1858</v>
@@ -22744,10 +22991,10 @@
       <c r="D482" s="1">
         <v>31</v>
       </c>
-      <c r="E482">
-        <v>9000</v>
-      </c>
-      <c r="F482" t="s">
+      <c r="E482" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F482" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G482" t="s">
@@ -22779,17 +23026,16 @@
       <c r="D483" s="1">
         <v>26</v>
       </c>
-      <c r="E483">
-        <v>6000</v>
-      </c>
-      <c r="F483">
-        <v>-50</v>
-      </c>
-      <c r="G483" s="5">
+      <c r="E483" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F483" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G483" s="2">
         <v>44082</v>
       </c>
       <c r="I483">
-        <f>974-4460-9570</f>
         <v>-13056</v>
       </c>
       <c r="J483" t="s">
@@ -22812,20 +23058,19 @@
       <c r="D484" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E484" t="s">
+      <c r="E484" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F484">
-        <v>0</v>
-      </c>
-      <c r="G484" s="5">
+      <c r="F484" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G484" s="2">
         <v>44512</v>
       </c>
       <c r="H484" t="s">
         <v>1863</v>
       </c>
       <c r="I484">
-        <f>974-4801-3564</f>
         <v>-7391</v>
       </c>
       <c r="K484" t="s">
@@ -22845,13 +23090,13 @@
       <c r="D485" s="1">
         <v>40</v>
       </c>
-      <c r="E485">
-        <v>7200</v>
-      </c>
-      <c r="F485" s="2">
-        <v>500</v>
-      </c>
-      <c r="G485" s="5">
+      <c r="E485" s="5" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F485" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G485" s="2">
         <v>44965</v>
       </c>
       <c r="H485" t="s">
@@ -22880,8 +23125,11 @@
       <c r="D486" s="1">
         <v>160</v>
       </c>
-      <c r="E486" t="s">
-        <v>48</v>
+      <c r="E486" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F486" s="5">
+        <v>0</v>
       </c>
       <c r="G486" t="s">
         <v>1866</v>
@@ -22909,10 +23157,10 @@
       <c r="D487" s="1">
         <v>34</v>
       </c>
-      <c r="E487">
-        <v>4500</v>
-      </c>
-      <c r="F487" t="s">
+      <c r="E487" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F487" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="G487" t="s">
@@ -22944,11 +23192,11 @@
       <c r="D488" s="1">
         <v>23</v>
       </c>
-      <c r="E488">
-        <v>7750</v>
-      </c>
-      <c r="F488">
-        <v>-200</v>
+      <c r="E488" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F488" s="5" t="s">
+        <v>1923</v>
       </c>
       <c r="G488" t="s">
         <v>1871</v>
@@ -22979,11 +23227,11 @@
       <c r="D489" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E489">
-        <v>5200</v>
-      </c>
-      <c r="F489">
-        <v>-50</v>
+      <c r="E489" s="5" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F489" s="5" t="s">
+        <v>1902</v>
       </c>
       <c r="G489" t="s">
         <v>1874</v>
@@ -23014,11 +23262,11 @@
       <c r="D490" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="E490" t="s">
+      <c r="E490" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F490">
-        <v>500</v>
+      <c r="F490" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G490" t="s">
         <v>1876</v>
@@ -23049,13 +23297,13 @@
       <c r="D491" s="1">
         <v>42</v>
       </c>
-      <c r="E491">
-        <v>8500</v>
-      </c>
-      <c r="F491">
-        <v>250</v>
-      </c>
-      <c r="G491" s="5">
+      <c r="E491" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F491" s="5" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G491" s="2">
         <v>45010</v>
       </c>
       <c r="H491" t="s">
@@ -23084,11 +23332,11 @@
       <c r="D492" s="1">
         <v>29</v>
       </c>
-      <c r="E492">
-        <v>6500</v>
-      </c>
-      <c r="F492">
-        <v>500</v>
+      <c r="E492" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F492" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G492" t="s">
         <v>1221</v>
@@ -23116,10 +23364,10 @@
       <c r="D493" s="1">
         <v>36</v>
       </c>
-      <c r="E493" t="s">
-        <v>48</v>
-      </c>
-      <c r="F493" t="s">
+      <c r="E493" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F493" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G493" t="s">
@@ -23151,13 +23399,13 @@
       <c r="D494" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E494">
-        <v>5500</v>
-      </c>
-      <c r="F494">
-        <v>500</v>
-      </c>
-      <c r="G494" s="5">
+      <c r="E494" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="F494" s="5" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G494" s="2">
         <v>45294</v>
       </c>
       <c r="H494" t="s">
@@ -23186,13 +23434,13 @@
       <c r="D495" s="1">
         <v>18</v>
       </c>
-      <c r="E495">
-        <v>9000</v>
-      </c>
-      <c r="F495" t="s">
+      <c r="E495" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F495" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G495" s="5">
+      <c r="G495" s="2">
         <v>44341</v>
       </c>
       <c r="I495" t="s">
@@ -23218,11 +23466,11 @@
       <c r="D496" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E496">
-        <v>6250</v>
-      </c>
-      <c r="F496">
-        <v>500</v>
+      <c r="E496" s="5" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F496" s="5" t="s">
+        <v>1899</v>
       </c>
       <c r="G496" t="s">
         <v>978</v>
@@ -23253,13 +23501,13 @@
       <c r="D497" s="1">
         <v>45</v>
       </c>
-      <c r="E497" t="s">
+      <c r="E497" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F497">
-        <v>-50</v>
-      </c>
-      <c r="G497" s="5">
+      <c r="F497" s="5" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G497" s="2">
         <v>43505</v>
       </c>
       <c r="H497" t="s">
@@ -23288,11 +23536,11 @@
       <c r="D498" s="1">
         <v>32</v>
       </c>
-      <c r="E498">
-        <v>4800</v>
-      </c>
-      <c r="F498">
-        <v>1000</v>
+      <c r="E498" s="5" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F498" s="5" t="s">
+        <v>1907</v>
       </c>
       <c r="G498" t="s">
         <v>1885</v>
@@ -23323,13 +23571,13 @@
       <c r="D499" s="1">
         <v>27</v>
       </c>
-      <c r="E499" t="s">
-        <v>48</v>
-      </c>
-      <c r="F499">
-        <v>300</v>
-      </c>
-      <c r="G499" s="5">
+      <c r="E499" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F499" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G499" s="2">
         <v>44180</v>
       </c>
       <c r="H499" t="s">
@@ -23358,8 +23606,11 @@
       <c r="D500" s="1">
         <v>38</v>
       </c>
-      <c r="E500">
-        <v>6200</v>
+      <c r="E500" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F500" s="5">
+        <v>0</v>
       </c>
       <c r="G500" t="s">
         <v>1890</v>
@@ -23390,8 +23641,11 @@
       <c r="D501" s="1">
         <v>38</v>
       </c>
-      <c r="E501">
-        <v>6200</v>
+      <c r="E501" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F501" s="5">
+        <v>0</v>
       </c>
       <c r="G501" t="s">
         <v>1890</v>

--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC79B16-0647-4D7D-8398-01D85ABF6CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B097A57F-8B32-4FA9-8DB6-6429E7B5A201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1978">
   <si>
     <t xml:space="preserve"> Employee ID </t>
   </si>
@@ -5730,9 +5730,6 @@
   </si>
   <si>
     <t>$500</t>
-  </si>
-  <si>
-    <t>7,501</t>
   </si>
   <si>
     <t>500</t>
@@ -6469,7 +6466,7 @@
         <v>35</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1898</v>
+        <v>1935</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>962</v>
@@ -6507,7 +6504,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>52</v>
@@ -6539,7 +6536,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -6574,10 +6571,10 @@
         <v>49</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>1901</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>1902</v>
       </c>
       <c r="G7" s="2">
         <v>44127</v>
@@ -6609,10 +6606,10 @@
         <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>51</v>
@@ -6673,7 +6670,7 @@
         <v>150</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -6702,10 +6699,10 @@
         <v>-5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G11" t="s">
         <v>975</v>
@@ -6737,7 +6734,7 @@
         <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>1897</v>
@@ -6775,7 +6772,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H13" t="s">
         <v>981</v>
@@ -6804,10 +6801,10 @@
         <v>27</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G14" t="s">
         <v>982</v>
@@ -6839,10 +6836,10 @@
         <v>33</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G15" s="2">
         <v>44197</v>
@@ -6874,10 +6871,10 @@
         <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G16" t="s">
         <v>985</v>
@@ -6909,7 +6906,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>1003</v>
@@ -6944,7 +6941,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>970</v>
@@ -6979,10 +6976,10 @@
         <v>48</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>1912</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>1913</v>
       </c>
       <c r="G19" s="2">
         <v>45639</v>
@@ -7014,10 +7011,10 @@
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G20" s="2">
         <v>44493</v>
@@ -7052,7 +7049,7 @@
         <v>48</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G21" t="s">
         <v>997</v>
@@ -7084,7 +7081,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -7119,7 +7116,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>1003</v>
@@ -7154,7 +7151,7 @@
         <v>33</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -7224,7 +7221,7 @@
         <v>-2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>1010</v>
@@ -7259,7 +7256,7 @@
         <v>34</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>1014</v>
@@ -7294,7 +7291,7 @@
         <v>41</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>50</v>
@@ -7326,10 +7323,10 @@
         <v>944</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>1921</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>1922</v>
       </c>
       <c r="G29" s="2">
         <v>45352</v>
@@ -7361,10 +7358,10 @@
         <v>26</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G30" s="2">
         <v>44116</v>
@@ -7399,7 +7396,7 @@
         <v>945</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G31" t="s">
         <v>1021</v>
@@ -7431,10 +7428,10 @@
         <v>48</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G32" t="s">
         <v>1024</v>
@@ -7466,10 +7463,10 @@
         <v>23</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G33" s="2">
         <v>45512</v>
@@ -7501,10 +7498,10 @@
         <v>44</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G34" t="s">
         <v>1028</v>
@@ -7536,10 +7533,10 @@
         <v>32</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G35" s="2">
         <v>45102</v>
@@ -7574,7 +7571,7 @@
         <v>48</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G36" t="s">
         <v>1031</v>
@@ -7606,10 +7603,10 @@
         <v>29</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G37" t="s">
         <v>1033</v>
@@ -7641,10 +7638,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G38" s="2">
         <v>45083</v>
@@ -7676,7 +7673,7 @@
         <v>55</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
@@ -7746,7 +7743,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>50</v>
@@ -7781,10 +7778,10 @@
         <v>39</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G42" s="2">
         <v>43860</v>
@@ -7813,10 +7810,10 @@
         <v>48</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G43" t="s">
         <v>1045</v>
@@ -7848,10 +7845,10 @@
         <v>31</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G44" s="2">
         <v>44652</v>
@@ -7883,7 +7880,7 @@
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
@@ -7918,7 +7915,7 @@
         <v>28</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -7956,7 +7953,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G47" s="2">
         <v>45384</v>
@@ -7988,7 +7985,7 @@
         <v>33</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>1055</v>
@@ -8023,7 +8020,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>962</v>
@@ -8058,10 +8055,10 @@
         <v>37</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G50" s="2">
         <v>44270</v>
@@ -8096,7 +8093,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G51" t="s">
         <v>1060</v>
@@ -8128,7 +8125,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
@@ -8163,10 +8160,10 @@
         <v>27</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G53" s="2">
         <v>44567</v>
@@ -8198,10 +8195,10 @@
         <v>48</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G54" t="s">
         <v>50</v>
@@ -8236,7 +8233,7 @@
         <v>48</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G55" s="2">
         <v>45549</v>
@@ -8268,10 +8265,10 @@
         <v>30</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>1937</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>1938</v>
       </c>
       <c r="G56" t="s">
         <v>1068</v>
@@ -8300,10 +8297,10 @@
         <v>49</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>1939</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>1940</v>
       </c>
       <c r="G57" t="s">
         <v>50</v>
@@ -8335,7 +8332,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
@@ -8370,7 +8367,7 @@
         <v>140</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>33</v>
@@ -8408,7 +8405,7 @@
         <v>50</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G60" t="s">
         <v>1078</v>
@@ -8437,7 +8434,7 @@
         <v>26</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>33</v>
@@ -8469,10 +8466,10 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G62" s="2">
         <v>45140</v>
@@ -8504,10 +8501,10 @@
         <v>40</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G63" t="s">
         <v>1084</v>
@@ -8539,7 +8536,7 @@
         <v>22</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>1014</v>
@@ -8606,7 +8603,7 @@
         <v>34</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>958</v>
@@ -8641,10 +8638,10 @@
         <v>29</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G67" t="s">
         <v>1092</v>
@@ -8676,7 +8673,7 @@
         <v>41</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>1897</v>
@@ -8714,7 +8711,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G69" t="s">
         <v>1097</v>
@@ -8746,10 +8743,10 @@
         <v>31</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G70" s="2">
         <v>44270</v>
@@ -8781,10 +8778,10 @@
         <v>947</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G71" s="2">
         <v>43599</v>
@@ -8816,10 +8813,10 @@
         <v>37</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G72" t="s">
         <v>48</v>
@@ -8883,7 +8880,7 @@
         <v>48</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -8918,10 +8915,10 @@
         <v>32</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G75" s="2">
         <v>45376</v>
@@ -8953,7 +8950,7 @@
         <v>44</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>1014</v>
@@ -8988,10 +8985,10 @@
         <v>28</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G77" s="2">
         <v>45601</v>
@@ -9055,7 +9052,7 @@
         <v>39</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>1014</v>
@@ -9090,10 +9087,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G80" s="2">
         <v>45481</v>
@@ -9128,7 +9125,7 @@
         <v>48</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G81" s="2">
         <v>44748</v>
@@ -9160,10 +9157,10 @@
         <v>36</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G82" s="2">
         <v>45575</v>
@@ -9195,7 +9192,7 @@
         <v>45</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>970</v>
@@ -9224,10 +9221,10 @@
         <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G84" s="2">
         <v>44353</v>
@@ -9259,10 +9256,10 @@
         <v>48</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G85" s="2">
         <v>45208</v>
@@ -9297,7 +9294,7 @@
         <v>50</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G86" s="2">
         <v>44073</v>
@@ -9329,10 +9326,10 @@
         <v>33</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G87" s="2">
         <v>45401</v>
@@ -9364,7 +9361,7 @@
         <v>160</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>1055</v>
@@ -9402,7 +9399,7 @@
         <v>48</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G89" t="s">
         <v>1125</v>
@@ -9434,10 +9431,10 @@
         <v>30</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G90" s="2">
         <v>43600</v>
@@ -9469,7 +9466,7 @@
         <v>42</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>48</v>
@@ -9504,7 +9501,7 @@
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>48</v>
@@ -9539,10 +9536,10 @@
         <v>24</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G93" t="s">
         <v>1133</v>
@@ -9577,7 +9574,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G94" s="2">
         <v>44414</v>
@@ -9609,7 +9606,7 @@
         <v>48</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>1897</v>
@@ -9644,10 +9641,10 @@
         <v>35</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G96" s="2">
         <v>44113</v>
@@ -9682,7 +9679,7 @@
         <v>48</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G97" s="2">
         <v>43761</v>
@@ -9714,7 +9711,7 @@
         <v>1896</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G98" s="2">
         <v>43466</v>
@@ -9746,10 +9743,10 @@
         <v>21</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G99" t="s">
         <v>1144</v>
@@ -9781,10 +9778,10 @@
         <v>-8</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G100" t="s">
         <v>1137</v>
@@ -9816,10 +9813,10 @@
         <v>31</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G101" t="s">
         <v>1148</v>
@@ -9886,10 +9883,10 @@
         <v>48</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G103" t="s">
         <v>1152</v>
@@ -9918,10 +9915,10 @@
         <v>948</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G104" t="s">
         <v>1154</v>
@@ -9953,7 +9950,7 @@
         <v>34</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>1157</v>
@@ -10020,10 +10017,10 @@
         <v>26</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G107" t="s">
         <v>1163</v>
@@ -10055,7 +10052,7 @@
         <v>18</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>1897</v>
@@ -10087,7 +10084,7 @@
         <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>1014</v>
@@ -10125,7 +10122,7 @@
         <v>50</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G110" t="s">
         <v>1168</v>
@@ -10157,7 +10154,7 @@
         <v>32</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>970</v>
@@ -10192,10 +10189,10 @@
         <v>145</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G112" s="2">
         <v>44633</v>
@@ -10227,10 +10224,10 @@
         <v>25</v>
       </c>
       <c r="E113" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F113" s="5" t="s">
         <v>1937</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>1938</v>
       </c>
       <c r="G113" s="2">
         <v>44060</v>
@@ -10297,10 +10294,10 @@
         <v>48</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G115" s="2">
         <v>44646</v>
@@ -10332,7 +10329,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>1157</v>
@@ -10367,10 +10364,10 @@
         <v>48</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G117" t="s">
         <v>1182</v>
@@ -10402,10 +10399,10 @@
         <v>22</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G118" t="s">
         <v>1185</v>
@@ -10440,7 +10437,7 @@
         <v>50</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G119" s="2">
         <v>44427</v>
@@ -10472,10 +10469,10 @@
         <v>37</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G120" s="2">
         <v>45601</v>
@@ -10507,7 +10504,7 @@
         <v>28</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>1055</v>
@@ -10542,7 +10539,7 @@
         <v>41</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>1003</v>
@@ -10612,7 +10609,7 @@
         <v>19</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>1014</v>
@@ -10647,10 +10644,10 @@
         <v>35</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G125" s="2">
         <v>44502</v>
@@ -10682,10 +10679,10 @@
         <v>48</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G126" s="2">
         <v>44508</v>
@@ -10717,7 +10714,7 @@
         <v>50</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G127" t="s">
         <v>1202</v>
@@ -10749,10 +10746,10 @@
         <v>-3</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G128" t="s">
         <v>1203</v>
@@ -10784,7 +10781,7 @@
         <v>46</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>962</v>
@@ -10819,7 +10816,7 @@
         <v>24</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>970</v>
@@ -10889,10 +10886,10 @@
         <v>40</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G132" s="2">
         <v>45611</v>
@@ -10924,10 +10921,10 @@
         <v>29</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G133" t="s">
         <v>1212</v>
@@ -10959,7 +10956,7 @@
         <v>48</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>1010</v>
@@ -11029,7 +11026,7 @@
         <v>36</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>1897</v>
@@ -11064,10 +11061,10 @@
         <v>950</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G137" t="s">
         <v>1221</v>
@@ -11099,10 +11096,10 @@
         <v>27</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G138" s="2">
         <v>43608</v>
@@ -11137,7 +11134,7 @@
         <v>48</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G139" t="s">
         <v>1225</v>
@@ -11169,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>1157</v>
@@ -11204,7 +11201,7 @@
         <v>50</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>1897</v>
@@ -11239,7 +11236,7 @@
         <v>38</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>1003</v>
@@ -11309,7 +11306,7 @@
         <v>48</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>48</v>
@@ -11344,7 +11341,7 @@
         <v>25</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>1055</v>
@@ -11376,10 +11373,10 @@
         <v>43</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G146" s="2">
         <v>43656</v>
@@ -11446,7 +11443,7 @@
         <v>15</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>970</v>
@@ -11481,10 +11478,10 @@
         <v>49</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G149" s="2">
         <v>45564</v>
@@ -11516,10 +11513,10 @@
         <v>34</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G150" t="s">
         <v>1248</v>
@@ -11548,10 +11545,10 @@
         <v>48</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G151" s="2">
         <v>45354</v>
@@ -11618,7 +11615,7 @@
         <v>28</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>970</v>
@@ -11653,10 +11650,10 @@
         <v>50</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G154" t="s">
         <v>48</v>
@@ -11688,10 +11685,10 @@
         <v>41</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G155" t="s">
         <v>1257</v>
@@ -11726,7 +11723,7 @@
         <v>48</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G156" t="s">
         <v>1260</v>
@@ -11758,7 +11755,7 @@
         <v>135</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>970</v>
@@ -11790,7 +11787,7 @@
         <v>31</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>1055</v>
@@ -11825,7 +11822,7 @@
         <v>45</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>1157</v>
@@ -11863,7 +11860,7 @@
         <v>50</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G160" t="s">
         <v>1270</v>
@@ -11895,7 +11892,7 @@
         <v>39</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>50</v>
@@ -11930,10 +11927,10 @@
         <v>48</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G162" s="2">
         <v>45632</v>
@@ -12000,7 +11997,7 @@
         <v>33</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>1010</v>
@@ -12035,7 +12032,7 @@
         <v>20</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
@@ -12070,7 +12067,7 @@
         <v>42</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>1003</v>
@@ -12102,7 +12099,7 @@
         <v>50</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>970</v>
@@ -12140,7 +12137,7 @@
         <v>50</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G168" s="2">
         <v>45100</v>
@@ -12172,7 +12169,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>1055</v>
@@ -12210,7 +12207,7 @@
         <v>48</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G170" t="s">
         <v>1286</v>
@@ -12242,10 +12239,10 @@
         <v>-6</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G171" t="s">
         <v>1288</v>
@@ -12277,7 +12274,7 @@
         <v>47</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>962</v>
@@ -12312,7 +12309,7 @@
         <v>25</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>48</v>
@@ -12347,10 +12344,10 @@
         <v>30</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G174" t="s">
         <v>51</v>
@@ -12417,7 +12414,7 @@
         <v>50</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>958</v>
@@ -12452,10 +12449,10 @@
         <v>22</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G177" s="2">
         <v>44842</v>
@@ -12487,7 +12484,7 @@
         <v>34</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>48</v>
@@ -12557,10 +12554,10 @@
         <v>180</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G180" s="2">
         <v>44141</v>
@@ -12592,10 +12589,10 @@
         <v>27</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G181" t="s">
         <v>1307</v>
@@ -12627,10 +12624,10 @@
         <v>38</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G182" s="2">
         <v>45169</v>
@@ -12665,7 +12662,7 @@
         <v>50</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G183" s="2">
         <v>43648</v>
@@ -12697,10 +12694,10 @@
         <v>952</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G184" s="2">
         <v>45171</v>
@@ -12729,7 +12726,7 @@
         <v>44</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>1157</v>
@@ -12799,7 +12796,7 @@
         <v>48</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>970</v>
@@ -12834,10 +12831,10 @@
         <v>35</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G188" s="2">
         <v>43575</v>
@@ -12869,10 +12866,10 @@
         <v>29</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G189" t="s">
         <v>1318</v>
@@ -12907,7 +12904,7 @@
         <v>50</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G190" t="s">
         <v>1320</v>
@@ -12939,10 +12936,10 @@
         <v>50</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G191" t="s">
         <v>1323</v>
@@ -12974,7 +12971,7 @@
         <v>24</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>962</v>
@@ -13006,7 +13003,7 @@
         <v>37</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -13044,7 +13041,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G194" s="2">
         <v>44758</v>
@@ -13076,7 +13073,7 @@
         <v>48</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>1157</v>
@@ -13111,10 +13108,10 @@
         <v>33</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G196" t="s">
         <v>1333</v>
@@ -13146,10 +13143,10 @@
         <v>41</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G197" t="s">
         <v>1335</v>
@@ -13184,7 +13181,7 @@
         <v>50</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G198" s="2">
         <v>44657</v>
@@ -13216,10 +13213,10 @@
         <v>-4</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G199" t="s">
         <v>1338</v>
@@ -13251,10 +13248,10 @@
         <v>46</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G200" s="2">
         <v>44442</v>
@@ -13321,7 +13318,7 @@
         <v>50</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>1055</v>
@@ -13356,7 +13353,7 @@
         <v>39</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F203" s="5">
         <v>0</v>
@@ -13391,7 +13388,7 @@
         <v>21</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>1003</v>
@@ -13426,7 +13423,7 @@
         <v>48</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>1897</v>
@@ -13496,7 +13493,7 @@
         <v>25</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>48</v>
@@ -13531,10 +13528,10 @@
         <v>43</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G208" t="s">
         <v>1353</v>
@@ -13569,7 +13566,7 @@
         <v>48</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G209" t="s">
         <v>1356</v>
@@ -13598,10 +13595,10 @@
         <v>155</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G210" t="s">
         <v>1359</v>
@@ -13633,10 +13630,10 @@
         <v>27</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G211" s="2">
         <v>45543</v>
@@ -13668,10 +13665,10 @@
         <v>50</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G212" t="s">
         <v>51</v>
@@ -13706,7 +13703,7 @@
         <v>50</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G213" s="2">
         <v>43851</v>
@@ -13738,7 +13735,7 @@
         <v>48</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>1014</v>
@@ -13773,10 +13770,10 @@
         <v>49</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G215" s="2">
         <v>44595</v>
@@ -13811,7 +13808,7 @@
         <v>48</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G216" t="s">
         <v>1370</v>
@@ -13840,10 +13837,10 @@
         <v>23</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G217" s="2">
         <v>44213</v>
@@ -13872,10 +13869,10 @@
         <v>31</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G218" s="2">
         <v>44597</v>
@@ -13907,10 +13904,10 @@
         <v>48</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G219" s="2">
         <v>45265</v>
@@ -13942,10 +13939,10 @@
         <v>29</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G220" t="s">
         <v>50</v>
@@ -13974,10 +13971,10 @@
         <v>48</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G221" t="s">
         <v>1377</v>
@@ -14012,7 +14009,7 @@
         <v>50</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G222" s="2">
         <v>44908</v>
@@ -14044,7 +14041,7 @@
         <v>44</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>48</v>
@@ -14079,7 +14076,7 @@
         <v>18</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>1157</v>
@@ -14149,7 +14146,7 @@
         <v>37</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>1897</v>
@@ -14184,10 +14181,10 @@
         <v>26</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G227" t="s">
         <v>1386</v>
@@ -14219,10 +14216,10 @@
         <v>-9</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G228" s="2">
         <v>44473</v>
@@ -14257,7 +14254,7 @@
         <v>50</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G229" s="2">
         <v>44476</v>
@@ -14289,10 +14286,10 @@
         <v>48</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G230" s="2">
         <v>44217</v>
@@ -14324,7 +14321,7 @@
         <v>30</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>958</v>
@@ -14394,7 +14391,7 @@
         <v>22</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>50</v>
@@ -14429,10 +14426,10 @@
         <v>50</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G234" s="2">
         <v>44933</v>
@@ -14464,10 +14461,10 @@
         <v>953</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G235" t="s">
         <v>1400</v>
@@ -14531,10 +14528,10 @@
         <v>50</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G237" s="2">
         <v>45646</v>
@@ -14566,10 +14563,10 @@
         <v>27</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G238" s="2">
         <v>44998</v>
@@ -14601,7 +14598,7 @@
         <v>48</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>970</v>
@@ -14639,7 +14636,7 @@
         <v>48</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G240" t="s">
         <v>1409</v>
@@ -14671,7 +14668,7 @@
         <v>32</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>1157</v>
@@ -14706,7 +14703,7 @@
         <v>24</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>50</v>
@@ -14741,7 +14738,7 @@
         <v>145</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>33</v>
@@ -14779,7 +14776,7 @@
         <v>50</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G244" t="s">
         <v>1419</v>
@@ -14811,7 +14808,7 @@
         <v>28</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>50</v>
@@ -14846,10 +14843,10 @@
         <v>43</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G246" t="s">
         <v>1137</v>
@@ -14884,7 +14881,7 @@
         <v>48</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G247" s="2">
         <v>45082</v>
@@ -14916,10 +14913,10 @@
         <v>19</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G248" t="s">
         <v>1424</v>
@@ -14951,10 +14948,10 @@
         <v>48</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G249" t="s">
         <v>1427</v>
@@ -14986,10 +14983,10 @@
         <v>33</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G250" s="2">
         <v>44303</v>
@@ -15018,7 +15015,7 @@
         <v>50</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G251" s="2">
         <v>45270</v>
@@ -15050,10 +15047,10 @@
         <v>25</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G252" t="s">
         <v>1431</v>
@@ -15085,10 +15082,10 @@
         <v>-7</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G253" t="s">
         <v>1434</v>
@@ -15123,7 +15120,7 @@
         <v>48</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G254" s="2">
         <v>43784</v>
@@ -15155,10 +15152,10 @@
         <v>30</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G255" t="s">
         <v>1137</v>
@@ -15187,10 +15184,10 @@
         <v>48</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G256" s="2">
         <v>45360</v>
@@ -15222,10 +15219,10 @@
         <v>954</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G257" s="2">
         <v>44737</v>
@@ -15257,10 +15254,10 @@
         <v>41</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G258" t="s">
         <v>1440</v>
@@ -15295,7 +15292,7 @@
         <v>50</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G259" t="s">
         <v>1442</v>
@@ -15327,7 +15324,7 @@
         <v>34</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>1157</v>
@@ -15362,10 +15359,10 @@
         <v>50</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G261" s="2">
         <v>44262</v>
@@ -15400,7 +15397,7 @@
         <v>48</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G262" s="2">
         <v>43521</v>
@@ -15432,7 +15429,7 @@
         <v>36</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>970</v>
@@ -15467,10 +15464,10 @@
         <v>48</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G264" s="2">
         <v>44601</v>
@@ -15502,7 +15499,7 @@
         <v>160</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>962</v>
@@ -15540,7 +15537,7 @@
         <v>50</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G266" s="2">
         <v>44638</v>
@@ -15572,10 +15569,10 @@
         <v>45</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G267" s="2">
         <v>43857</v>
@@ -15607,10 +15604,10 @@
         <v>31</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G268" s="2">
         <v>45657</v>
@@ -15677,7 +15674,7 @@
         <v>50</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>1003</v>
@@ -15709,10 +15706,10 @@
         <v>39</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G271" s="2">
         <v>43877</v>
@@ -15744,10 +15741,10 @@
         <v>48</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G272" s="2">
         <v>44169</v>
@@ -15811,10 +15808,10 @@
         <v>42</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G274" t="s">
         <v>1468</v>
@@ -15846,10 +15843,10 @@
         <v>28</v>
       </c>
       <c r="E275" s="5" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F275" s="5" t="s">
         <v>1901</v>
-      </c>
-      <c r="F275" s="5" t="s">
-        <v>1902</v>
       </c>
       <c r="G275" s="2">
         <v>44661</v>
@@ -15881,7 +15878,7 @@
         <v>17</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="F276" s="5" t="s">
         <v>1897</v>
@@ -15919,7 +15916,7 @@
         <v>48</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G277" s="2">
         <v>43818</v>
@@ -15951,10 +15948,10 @@
         <v>40</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G278" t="s">
         <v>48</v>
@@ -15986,10 +15983,10 @@
         <v>50</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G279" t="s">
         <v>1478</v>
@@ -16021,7 +16018,7 @@
         <v>26</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>48</v>
@@ -16059,7 +16056,7 @@
         <v>50</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G281" t="s">
         <v>1480</v>
@@ -16091,10 +16088,10 @@
         <v>44</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G282" s="2">
         <v>44907</v>
@@ -16129,7 +16126,7 @@
         <v>48</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G283" s="2">
         <v>44930</v>
@@ -16161,10 +16158,10 @@
         <v>30</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G284" t="s">
         <v>1486</v>
@@ -16196,10 +16193,10 @@
         <v>37</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G285" s="2">
         <v>45146</v>
@@ -16231,7 +16228,7 @@
         <v>23</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>970</v>
@@ -16266,10 +16263,10 @@
         <v>48</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G287" t="s">
         <v>1491</v>
@@ -16304,7 +16301,7 @@
         <v>50</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G288" s="2">
         <v>43500</v>
@@ -16333,7 +16330,7 @@
         <v>950</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F289" s="5">
         <v>0</v>
@@ -16371,7 +16368,7 @@
         <v>48</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G290" t="s">
         <v>1497</v>
@@ -16403,7 +16400,7 @@
         <v>31</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>1003</v>
@@ -16435,7 +16432,7 @@
         <v>41</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>48</v>
@@ -16467,10 +16464,10 @@
         <v>50</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G293" t="s">
         <v>1501</v>
@@ -16502,10 +16499,10 @@
         <v>20</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F294" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G294" s="2">
         <v>44249</v>
@@ -16540,7 +16537,7 @@
         <v>50</v>
       </c>
       <c r="F295" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G295" s="2">
         <v>44463</v>
@@ -16572,7 +16569,7 @@
         <v>43</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>962</v>
@@ -16607,7 +16604,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>958</v>
@@ -16677,7 +16674,7 @@
         <v>150</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>50</v>
@@ -16712,10 +16709,10 @@
         <v>32</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F300" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G300" t="s">
         <v>1515</v>
@@ -16747,7 +16744,7 @@
         <v>50</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F301" s="5">
         <v>0</v>
@@ -16782,7 +16779,7 @@
         <v>50</v>
       </c>
       <c r="F302" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G302" s="2">
         <v>44630</v>
@@ -16811,7 +16808,7 @@
         <v>48</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>970</v>
@@ -16846,10 +16843,10 @@
         <v>39</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G304" t="s">
         <v>1523</v>
@@ -16913,7 +16910,7 @@
         <v>29</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>1055</v>
@@ -16948,10 +16945,10 @@
         <v>-5</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G307" t="s">
         <v>1530</v>
@@ -16983,10 +16980,10 @@
         <v>35</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G308" t="s">
         <v>1533</v>
@@ -17021,7 +17018,7 @@
         <v>50</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G309" t="s">
         <v>1536</v>
@@ -17053,10 +17050,10 @@
         <v>40</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G310" t="s">
         <v>1539</v>
@@ -17088,10 +17085,10 @@
         <v>48</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G311" s="2">
         <v>45018</v>
@@ -17126,7 +17123,7 @@
         <v>48</v>
       </c>
       <c r="F312" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G312" s="2">
         <v>43600</v>
@@ -17158,7 +17155,7 @@
         <v>31</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>33</v>
@@ -17193,10 +17190,10 @@
         <v>50</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F314" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G314" t="s">
         <v>48</v>
@@ -17228,7 +17225,7 @@
         <v>24</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F315" s="5" t="s">
         <v>962</v>
@@ -17263,7 +17260,7 @@
         <v>42</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F316" s="5" t="s">
         <v>48</v>
@@ -17301,7 +17298,7 @@
         <v>50</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G317" t="s">
         <v>1553</v>
@@ -17333,7 +17330,7 @@
         <v>48</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F318" s="5" t="s">
         <v>1003</v>
@@ -17368,10 +17365,10 @@
         <v>18</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G319" s="2">
         <v>43613</v>
@@ -17435,10 +17432,10 @@
         <v>45</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G321" s="2">
         <v>43984</v>
@@ -17467,7 +17464,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F322" s="5" t="s">
         <v>962</v>
@@ -17502,10 +17499,10 @@
         <v>50</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F323" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G323" t="s">
         <v>1565</v>
@@ -17572,10 +17569,10 @@
         <v>48</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F325" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G325" s="2">
         <v>44364</v>
@@ -17639,10 +17636,10 @@
         <v>26</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F327" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G327" s="2">
         <v>44502</v>
@@ -17674,7 +17671,7 @@
         <v>41</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F328" s="5" t="s">
         <v>48</v>
@@ -17709,7 +17706,7 @@
         <v>22</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F329" s="5" t="s">
         <v>33</v>
@@ -17741,10 +17738,10 @@
         <v>948</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F330" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G330" s="2">
         <v>44318</v>
@@ -17776,7 +17773,7 @@
         <v>50</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G331" s="2">
         <v>44806</v>
@@ -17808,10 +17805,10 @@
         <v>48</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F332" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G332" t="s">
         <v>1581</v>
@@ -17843,10 +17840,10 @@
         <v>33</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G333" s="2">
         <v>43482</v>
@@ -17881,7 +17878,7 @@
         <v>48</v>
       </c>
       <c r="F334" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G334" t="s">
         <v>1584</v>
@@ -17913,7 +17910,7 @@
         <v>50</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F335" s="5">
         <v>0</v>
@@ -17945,10 +17942,10 @@
         <v>44</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G336" t="s">
         <v>1589</v>
@@ -17980,10 +17977,10 @@
         <v>19</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F337" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G337" t="s">
         <v>1592</v>
@@ -18018,7 +18015,7 @@
         <v>50</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G338" t="s">
         <v>1595</v>
@@ -18047,10 +18044,10 @@
         <v>36</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G339" s="2">
         <v>44532</v>
@@ -18079,7 +18076,7 @@
         <v>31</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F340" s="5">
         <v>0</v>
@@ -18114,7 +18111,7 @@
         <v>48</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G341" t="s">
         <v>1601</v>
@@ -18146,7 +18143,7 @@
         <v>40</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F342" s="5">
         <v>0</v>
@@ -18181,10 +18178,10 @@
         <v>25</v>
       </c>
       <c r="E343" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F343" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G343" s="2">
         <v>44848</v>
@@ -18213,7 +18210,7 @@
         <v>50</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F344" s="5" t="s">
         <v>1157</v>
@@ -18251,7 +18248,7 @@
         <v>50</v>
       </c>
       <c r="F345" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G345" t="s">
         <v>1608</v>
@@ -18283,7 +18280,7 @@
         <v>43</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F346" s="5">
         <v>0</v>
@@ -18318,10 +18315,10 @@
         <v>28</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F347" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G347" s="2">
         <v>44192</v>
@@ -18353,10 +18350,10 @@
         <v>35</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="F348" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G348" s="2">
         <v>44323</v>
@@ -18391,7 +18388,7 @@
         <v>48</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G349" s="2">
         <v>45390</v>
@@ -18423,7 +18420,7 @@
         <v>24</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F350" s="5" t="s">
         <v>48</v>
@@ -18455,7 +18452,7 @@
         <v>42</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F351" s="5" t="s">
         <v>958</v>
@@ -18490,7 +18487,7 @@
         <v>50</v>
       </c>
       <c r="E352" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F352" s="5" t="s">
         <v>1157</v>
@@ -18528,7 +18525,7 @@
         <v>50</v>
       </c>
       <c r="F353" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G353" t="s">
         <v>51</v>
@@ -18557,10 +18554,10 @@
         <v>48</v>
       </c>
       <c r="E354" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F354" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G354" t="s">
         <v>1623</v>
@@ -18592,7 +18589,7 @@
         <v>956</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F355" s="5">
         <v>0</v>
@@ -18630,7 +18627,7 @@
         <v>48</v>
       </c>
       <c r="F356" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G356" s="2">
         <v>43862</v>
@@ -18662,7 +18659,7 @@
         <v>27</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F357" s="5" t="s">
         <v>48</v>
@@ -18697,7 +18694,7 @@
         <v>46</v>
       </c>
       <c r="E358" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F358" s="5" t="s">
         <v>33</v>
@@ -18729,7 +18726,7 @@
         <v>32</v>
       </c>
       <c r="E359" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F359" s="5" t="s">
         <v>958</v>
@@ -18793,7 +18790,7 @@
         <v>41</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F361" s="5">
         <v>0</v>
@@ -18831,7 +18828,7 @@
         <v>48</v>
       </c>
       <c r="F362" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G362" t="s">
         <v>1137</v>
@@ -18863,7 +18860,7 @@
         <v>50</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F363" s="5">
         <v>0</v>
@@ -18898,10 +18895,10 @@
         <v>36</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F364" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G364" t="s">
         <v>1641</v>
@@ -18933,7 +18930,7 @@
         <v>18</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F365" s="5" t="s">
         <v>1157</v>
@@ -18971,7 +18968,7 @@
         <v>50</v>
       </c>
       <c r="F366" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G366" s="2">
         <v>44450</v>
@@ -19003,10 +19000,10 @@
         <v>34</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F367" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G367" t="s">
         <v>1646</v>
@@ -19038,10 +19035,10 @@
         <v>29</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F368" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G368" s="2">
         <v>43681</v>
@@ -19105,7 +19102,7 @@
         <v>47</v>
       </c>
       <c r="E370" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F370" s="5" t="s">
         <v>970</v>
@@ -19137,7 +19134,7 @@
         <v>25</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F371" s="5" t="s">
         <v>33</v>
@@ -19172,10 +19169,10 @@
         <v>40</v>
       </c>
       <c r="E372" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G372" s="2">
         <v>45339</v>
@@ -19210,7 +19207,7 @@
         <v>50</v>
       </c>
       <c r="F373" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G373" t="s">
         <v>1657</v>
@@ -19242,10 +19239,10 @@
         <v>33</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F374" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G374" t="s">
         <v>48</v>
@@ -19277,10 +19274,10 @@
         <v>48</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F375" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G375" t="s">
         <v>1661</v>
@@ -19315,7 +19312,7 @@
         <v>48</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G376" t="s">
         <v>1663</v>
@@ -19347,10 +19344,10 @@
         <v>21</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F377" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G377" t="s">
         <v>1665</v>
@@ -19382,7 +19379,7 @@
         <v>145</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F378" s="5" t="s">
         <v>48</v>
@@ -19414,10 +19411,10 @@
         <v>31</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G379" s="2">
         <v>45159</v>
@@ -19484,7 +19481,7 @@
         <v>44</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F381" s="5" t="s">
         <v>48</v>
@@ -19519,10 +19516,10 @@
         <v>48</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G382" t="s">
         <v>1049</v>
@@ -19557,7 +19554,7 @@
         <v>48</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G383" s="2">
         <v>44114</v>
@@ -19589,10 +19586,10 @@
         <v>26</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G384" s="2">
         <v>44904</v>
@@ -19624,7 +19621,7 @@
         <v>50</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F385" s="5" t="s">
         <v>1897</v>
@@ -19659,7 +19656,7 @@
         <v>37</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F386" s="5" t="s">
         <v>1010</v>
@@ -19729,7 +19726,7 @@
         <v>48</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F388" s="5" t="s">
         <v>962</v>
@@ -19764,10 +19761,10 @@
         <v>42</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G389" s="2">
         <v>44159</v>
@@ -19834,10 +19831,10 @@
         <v>28</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G391" s="2">
         <v>44810</v>
@@ -19869,10 +19866,10 @@
         <v>-4</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G392" t="s">
         <v>1696</v>
@@ -19904,7 +19901,7 @@
         <v>49</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F393" s="5" t="s">
         <v>48</v>
@@ -19974,10 +19971,10 @@
         <v>48</v>
       </c>
       <c r="E395" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G395" s="2">
         <v>45601</v>
@@ -20009,10 +20006,10 @@
         <v>32</v>
       </c>
       <c r="E396" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G396" s="2">
         <v>45385</v>
@@ -20044,7 +20041,7 @@
         <v>48</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G397" t="s">
         <v>1706</v>
@@ -20076,7 +20073,7 @@
         <v>24</v>
       </c>
       <c r="E398" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F398" s="5" t="s">
         <v>48</v>
@@ -20111,7 +20108,7 @@
         <v>36</v>
       </c>
       <c r="E399" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F399" s="5" t="s">
         <v>1897</v>
@@ -20146,10 +20143,10 @@
         <v>48</v>
       </c>
       <c r="E400" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G400" s="2">
         <v>44660</v>
@@ -20216,10 +20213,10 @@
         <v>43</v>
       </c>
       <c r="E402" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G402" t="s">
         <v>51</v>
@@ -20251,7 +20248,7 @@
         <v>50</v>
       </c>
       <c r="E403" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F403" s="5" t="s">
         <v>33</v>
@@ -20289,7 +20286,7 @@
         <v>48</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G404" s="2">
         <v>45408</v>
@@ -20318,10 +20315,10 @@
         <v>160</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G405" t="s">
         <v>1719</v>
@@ -20353,10 +20350,10 @@
         <v>39</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G406" t="s">
         <v>1722</v>
@@ -20388,10 +20385,10 @@
         <v>22</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G407" t="s">
         <v>1724</v>
@@ -20458,10 +20455,10 @@
         <v>49</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G409" s="2">
         <v>43930</v>
@@ -20493,10 +20490,10 @@
         <v>34</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G410" t="s">
         <v>1730</v>
@@ -20531,7 +20528,7 @@
         <v>48</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G411" t="s">
         <v>1733</v>
@@ -20563,10 +20560,10 @@
         <v>29</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G412" s="2">
         <v>45574</v>
@@ -20598,10 +20595,10 @@
         <v>50</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G413" t="s">
         <v>51</v>
@@ -20633,7 +20630,7 @@
         <v>18</v>
       </c>
       <c r="E414" s="5" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F414" s="5" t="s">
         <v>50</v>
@@ -20668,7 +20665,7 @@
         <v>50</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G415" s="2">
         <v>43792</v>
@@ -20700,10 +20697,10 @@
         <v>37</v>
       </c>
       <c r="E416" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G416" t="s">
         <v>1742</v>
@@ -20735,10 +20732,10 @@
         <v>25</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G417" s="2">
         <v>45383</v>
@@ -20773,7 +20770,7 @@
         <v>48</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G418" s="2">
         <v>44545</v>
@@ -20805,10 +20802,10 @@
         <v>-1</v>
       </c>
       <c r="E419" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G419" t="s">
         <v>1748</v>
@@ -20840,10 +20837,10 @@
         <v>31</v>
       </c>
       <c r="E420" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G420" t="s">
         <v>1751</v>
@@ -20875,7 +20872,7 @@
         <v>50</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F421" s="5" t="s">
         <v>48</v>
@@ -20913,7 +20910,7 @@
         <v>50</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G422" t="s">
         <v>1137</v>
@@ -20945,10 +20942,10 @@
         <v>44</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G423" t="s">
         <v>1757</v>
@@ -20980,10 +20977,10 @@
         <v>33</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G424" t="s">
         <v>1759</v>
@@ -21050,7 +21047,7 @@
         <v>38</v>
       </c>
       <c r="E426" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F426" s="5" t="s">
         <v>1014</v>
@@ -21085,10 +21082,10 @@
         <v>48</v>
       </c>
       <c r="E427" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G427" s="2">
         <v>44199</v>
@@ -21120,10 +21117,10 @@
         <v>26</v>
       </c>
       <c r="E428" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G428" t="s">
         <v>1766</v>
@@ -21158,7 +21155,7 @@
         <v>50</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G429" s="2">
         <v>43952</v>
@@ -21190,10 +21187,10 @@
         <v>50</v>
       </c>
       <c r="E430" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G430" t="s">
         <v>1137</v>
@@ -21225,7 +21222,7 @@
         <v>48</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G431" s="2">
         <v>45583</v>
@@ -21257,7 +21254,7 @@
         <v>150</v>
       </c>
       <c r="E432" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="F432" s="5" t="s">
         <v>970</v>
@@ -21292,10 +21289,10 @@
         <v>30</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G433" t="s">
         <v>1003</v>
@@ -21327,10 +21324,10 @@
         <v>23</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G434" t="s">
         <v>1775</v>
@@ -21362,10 +21359,10 @@
         <v>48</v>
       </c>
       <c r="E435" s="5" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G435" s="2">
         <v>45264</v>
@@ -21429,7 +21426,7 @@
         <v>40</v>
       </c>
       <c r="E437" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F437" s="5" t="s">
         <v>1014</v>
@@ -21464,7 +21461,7 @@
         <v>32</v>
       </c>
       <c r="E438" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F438" s="5" t="s">
         <v>1014</v>
@@ -21502,7 +21499,7 @@
         <v>48</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G439" s="2">
         <v>45551</v>
@@ -21534,10 +21531,10 @@
         <v>50</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G440" t="s">
         <v>1783</v>
@@ -21569,10 +21566,10 @@
         <v>19</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G441" s="2">
         <v>45650</v>
@@ -21601,7 +21598,7 @@
         <v>48</v>
       </c>
       <c r="E442" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F442" s="5" t="s">
         <v>958</v>
@@ -21671,10 +21668,10 @@
         <v>36</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G444" t="s">
         <v>1792</v>
@@ -21706,10 +21703,10 @@
         <v>25</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G445" s="2">
         <v>43533</v>
@@ -21776,7 +21773,7 @@
         <v>43</v>
       </c>
       <c r="E447" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F447" s="5" t="s">
         <v>50</v>
@@ -21811,7 +21808,7 @@
         <v>50</v>
       </c>
       <c r="E448" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F448" s="5">
         <v>0</v>
@@ -21843,10 +21840,10 @@
         <v>48</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G449" t="s">
         <v>1802</v>
@@ -21881,7 +21878,7 @@
         <v>50</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G450" s="2">
         <v>44471</v>
@@ -21910,7 +21907,7 @@
         <v>34</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F451" s="5" t="s">
         <v>1157</v>
@@ -21945,7 +21942,7 @@
         <v>21</v>
       </c>
       <c r="E452" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F452" s="5" t="s">
         <v>1157</v>
@@ -21983,7 +21980,7 @@
         <v>48</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G453" s="2">
         <v>44623</v>
@@ -22015,10 +22012,10 @@
         <v>48</v>
       </c>
       <c r="E454" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G454" t="s">
         <v>1808</v>
@@ -22050,7 +22047,7 @@
         <v>38</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F455" s="5" t="s">
         <v>1157</v>
@@ -22082,10 +22079,10 @@
         <v>27</v>
       </c>
       <c r="E456" s="5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G456" s="2">
         <v>45482</v>
@@ -22120,7 +22117,7 @@
         <v>50</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G457" t="s">
         <v>1813</v>
@@ -22152,7 +22149,7 @@
         <v>31</v>
       </c>
       <c r="E458" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F458" s="5" t="s">
         <v>50</v>
@@ -22187,10 +22184,10 @@
         <v>175</v>
       </c>
       <c r="E459" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F459" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G459" s="2">
         <v>44361</v>
@@ -22225,7 +22222,7 @@
         <v>48</v>
       </c>
       <c r="F460" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G460" t="s">
         <v>1820</v>
@@ -22257,7 +22254,7 @@
         <v>24</v>
       </c>
       <c r="E461" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F461" s="5" t="s">
         <v>50</v>
@@ -22292,10 +22289,10 @@
         <v>48</v>
       </c>
       <c r="E462" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F462" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G462" t="s">
         <v>1825</v>
@@ -22327,10 +22324,10 @@
         <v>952</v>
       </c>
       <c r="E463" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G463" t="s">
         <v>1828</v>
@@ -22365,7 +22362,7 @@
         <v>50</v>
       </c>
       <c r="F464" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G464" s="2">
         <v>43931</v>
@@ -22397,10 +22394,10 @@
         <v>33</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G465" t="s">
         <v>1003</v>
@@ -22435,7 +22432,7 @@
         <v>48</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G466" s="2">
         <v>43471</v>
@@ -22467,10 +22464,10 @@
         <v>50</v>
       </c>
       <c r="E467" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G467" s="2">
         <v>45066</v>
@@ -22502,10 +22499,10 @@
         <v>22</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="G468" t="s">
         <v>1137</v>
@@ -22537,10 +22534,10 @@
         <v>48</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G469" s="2">
         <v>45472</v>
@@ -22575,7 +22572,7 @@
         <v>50</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G470" s="2">
         <v>45613</v>
@@ -22607,7 +22604,7 @@
         <v>35</v>
       </c>
       <c r="E471" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F471" s="5" t="s">
         <v>958</v>
@@ -22642,10 +22639,10 @@
         <v>28</v>
       </c>
       <c r="E472" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G472" s="2">
         <v>45607</v>
@@ -22680,7 +22677,7 @@
         <v>48</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="G473" t="s">
         <v>48</v>
@@ -22712,7 +22709,7 @@
         <v>41</v>
       </c>
       <c r="E474" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F474" s="5" t="s">
         <v>1897</v>
@@ -22747,10 +22744,10 @@
         <v>50</v>
       </c>
       <c r="E475" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G475" s="2">
         <v>44929</v>
@@ -22782,7 +22779,7 @@
         <v>48</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F476" s="5" t="s">
         <v>1014</v>
@@ -22852,10 +22849,10 @@
         <v>37</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G478" s="2">
         <v>44970</v>
@@ -22887,10 +22884,10 @@
         <v>19</v>
       </c>
       <c r="E479" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G479" t="s">
         <v>1853</v>
@@ -22925,7 +22922,7 @@
         <v>48</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G480" t="s">
         <v>1856</v>
@@ -22957,10 +22954,10 @@
         <v>48</v>
       </c>
       <c r="E481" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G481" t="s">
         <v>1858</v>
@@ -22992,7 +22989,7 @@
         <v>31</v>
       </c>
       <c r="E482" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F482" s="5" t="s">
         <v>48</v>
@@ -23027,10 +23024,10 @@
         <v>26</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G483" s="2">
         <v>44082</v>
@@ -23062,7 +23059,7 @@
         <v>50</v>
       </c>
       <c r="F484" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="G484" s="2">
         <v>44512</v>
@@ -23091,7 +23088,7 @@
         <v>40</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F485" s="5" t="s">
         <v>1897</v>
@@ -23158,7 +23155,7 @@
         <v>34</v>
       </c>
       <c r="E487" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F487" s="5" t="s">
         <v>1003</v>
@@ -23193,10 +23190,10 @@
         <v>23</v>
       </c>
       <c r="E488" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="G488" t="s">
         <v>1871</v>
@@ -23228,10 +23225,10 @@
         <v>48</v>
       </c>
       <c r="E489" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G489" t="s">
         <v>1874</v>
@@ -23266,7 +23263,7 @@
         <v>50</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G490" t="s">
         <v>1876</v>
@@ -23298,10 +23295,10 @@
         <v>42</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="G491" s="2">
         <v>45010</v>
@@ -23333,10 +23330,10 @@
         <v>29</v>
       </c>
       <c r="E492" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G492" t="s">
         <v>1221</v>
@@ -23400,10 +23397,10 @@
         <v>50</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G494" s="2">
         <v>45294</v>
@@ -23435,7 +23432,7 @@
         <v>18</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F495" s="5" t="s">
         <v>33</v>
@@ -23467,10 +23464,10 @@
         <v>48</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="G496" t="s">
         <v>978</v>
@@ -23505,7 +23502,7 @@
         <v>50</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="G497" s="2">
         <v>43505</v>
@@ -23537,10 +23534,10 @@
         <v>32</v>
       </c>
       <c r="E498" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G498" t="s">
         <v>1885</v>
@@ -23575,7 +23572,7 @@
         <v>48</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G499" s="2">
         <v>44180</v>
@@ -23607,7 +23604,7 @@
         <v>38</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F500" s="5">
         <v>0</v>
@@ -23642,7 +23639,7 @@
         <v>38</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F501" s="5">
         <v>0</v>

--- a/data/raw_data.xlsx
+++ b/data/raw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private\555 sha\P\pandas-data-cleaning-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B097A57F-8B32-4FA9-8DB6-6429E7B5A201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB89AFE-AF16-47FA-8169-F3D49CCA4101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4615" uniqueCount="1978">
   <si>
     <t xml:space="preserve"> Employee ID </t>
   </si>
@@ -5717,12 +5717,6 @@
     <t xml:space="preserve">Robert     Brown </t>
   </si>
   <si>
-    <t>mary.brown@yahoo</t>
-  </si>
-  <si>
-    <t>john.davishotmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve"> +6028 1693 </t>
   </si>
   <si>
@@ -5970,6 +5964,12 @@
   </si>
   <si>
     <t>1,200</t>
+  </si>
+  <si>
+    <t>john.davismail.com</t>
+  </si>
+  <si>
+    <t>mary.brown@yahoo.com</t>
   </si>
 </sst>
 </file>
@@ -6399,10 +6399,10 @@
         <v>25</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G2" t="s">
         <v>50</v>
@@ -6439,8 +6439,8 @@
       <c r="F3" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="G3" s="2">
-        <v>51326</v>
+      <c r="G3" t="s">
+        <v>975</v>
       </c>
       <c r="H3" t="s">
         <v>959</v>
@@ -6466,7 +6466,7 @@
         <v>35</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>962</v>
@@ -6475,7 +6475,7 @@
         <v>43909</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1893</v>
+        <v>1977</v>
       </c>
       <c r="I4">
         <v>37773911</v>
@@ -6504,7 +6504,7 @@
         <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>52</v>
@@ -6536,7 +6536,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -6571,10 +6571,10 @@
         <v>49</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G7" s="2">
         <v>44127</v>
@@ -6583,7 +6583,7 @@
         <v>968</v>
       </c>
       <c r="I7" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="J7" t="s">
         <v>54</v>
@@ -6606,16 +6606,16 @@
         <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>1894</v>
+        <v>1976</v>
       </c>
       <c r="I8" t="s">
         <v>970</v>
@@ -6670,7 +6670,7 @@
         <v>150</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1903</v>
+        <v>1937</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -6699,10 +6699,10 @@
         <v>-5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G11" t="s">
         <v>975</v>
@@ -6734,10 +6734,10 @@
         <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G12" t="s">
         <v>978</v>
@@ -6772,7 +6772,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="H13" t="s">
         <v>981</v>
@@ -6801,10 +6801,10 @@
         <v>27</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G14" t="s">
         <v>982</v>
@@ -6836,10 +6836,10 @@
         <v>33</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G15" s="2">
         <v>44197</v>
@@ -6871,10 +6871,10 @@
         <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G16" t="s">
         <v>985</v>
@@ -6906,7 +6906,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>1003</v>
@@ -6941,7 +6941,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>970</v>
@@ -6976,10 +6976,10 @@
         <v>48</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G19" s="2">
         <v>45639</v>
@@ -7011,10 +7011,10 @@
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G20" s="2">
         <v>44493</v>
@@ -7049,7 +7049,7 @@
         <v>48</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G21" t="s">
         <v>997</v>
@@ -7081,7 +7081,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -7116,7 +7116,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>1003</v>
@@ -7151,7 +7151,7 @@
         <v>33</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>-2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>1010</v>
@@ -7256,7 +7256,7 @@
         <v>34</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>1014</v>
@@ -7291,7 +7291,7 @@
         <v>41</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>50</v>
@@ -7323,10 +7323,10 @@
         <v>944</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G29" s="2">
         <v>45352</v>
@@ -7358,10 +7358,10 @@
         <v>26</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G30" s="2">
         <v>44116</v>
@@ -7396,7 +7396,7 @@
         <v>945</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G31" t="s">
         <v>1021</v>
@@ -7428,10 +7428,10 @@
         <v>48</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G32" t="s">
         <v>1024</v>
@@ -7463,10 +7463,10 @@
         <v>23</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G33" s="2">
         <v>45512</v>
@@ -7498,10 +7498,10 @@
         <v>44</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G34" t="s">
         <v>1028</v>
@@ -7533,10 +7533,10 @@
         <v>32</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G35" s="2">
         <v>45102</v>
@@ -7571,7 +7571,7 @@
         <v>48</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G36" t="s">
         <v>1031</v>
@@ -7603,10 +7603,10 @@
         <v>29</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G37" t="s">
         <v>1033</v>
@@ -7638,10 +7638,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G38" s="2">
         <v>45083</v>
@@ -7673,7 +7673,7 @@
         <v>55</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
@@ -7743,7 +7743,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>50</v>
@@ -7778,10 +7778,10 @@
         <v>39</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G42" s="2">
         <v>43860</v>
@@ -7810,10 +7810,10 @@
         <v>48</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G43" t="s">
         <v>1045</v>
@@ -7845,10 +7845,10 @@
         <v>31</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G44" s="2">
         <v>44652</v>
@@ -7880,7 +7880,7 @@
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
@@ -7915,7 +7915,7 @@
         <v>28</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
@@ -7953,7 +7953,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G47" s="2">
         <v>45384</v>
@@ -7985,7 +7985,7 @@
         <v>33</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>1055</v>
@@ -8020,7 +8020,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>962</v>
@@ -8055,10 +8055,10 @@
         <v>37</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G50" s="2">
         <v>44270</v>
@@ -8093,7 +8093,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G51" t="s">
         <v>1060</v>
@@ -8125,7 +8125,7 @@
         <v>43</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>27</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G53" s="2">
         <v>44567</v>
@@ -8195,10 +8195,10 @@
         <v>48</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G54" t="s">
         <v>50</v>
@@ -8233,7 +8233,7 @@
         <v>48</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G55" s="2">
         <v>45549</v>
@@ -8265,10 +8265,10 @@
         <v>30</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G56" t="s">
         <v>1068</v>
@@ -8297,10 +8297,10 @@
         <v>49</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G57" t="s">
         <v>50</v>
@@ -8332,7 +8332,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
@@ -8367,7 +8367,7 @@
         <v>140</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>33</v>
@@ -8405,7 +8405,7 @@
         <v>50</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G60" t="s">
         <v>1078</v>
@@ -8434,7 +8434,7 @@
         <v>26</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>33</v>
@@ -8466,10 +8466,10 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G62" s="2">
         <v>45140</v>
@@ -8501,10 +8501,10 @@
         <v>40</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G63" t="s">
         <v>1084</v>
@@ -8536,7 +8536,7 @@
         <v>22</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>1014</v>
@@ -8603,7 +8603,7 @@
         <v>34</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>958</v>
@@ -8638,10 +8638,10 @@
         <v>29</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G67" t="s">
         <v>1092</v>
@@ -8673,10 +8673,10 @@
         <v>41</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G68" t="s">
         <v>1095</v>
@@ -8711,7 +8711,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G69" t="s">
         <v>1097</v>
@@ -8743,10 +8743,10 @@
         <v>31</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G70" s="2">
         <v>44270</v>
@@ -8778,10 +8778,10 @@
         <v>947</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G71" s="2">
         <v>43599</v>
@@ -8813,10 +8813,10 @@
         <v>37</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G72" t="s">
         <v>48</v>
@@ -8880,7 +8880,7 @@
         <v>48</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>32</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G75" s="2">
         <v>45376</v>
@@ -8950,7 +8950,7 @@
         <v>44</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>1014</v>
@@ -8985,10 +8985,10 @@
         <v>28</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G77" s="2">
         <v>45601</v>
@@ -9052,7 +9052,7 @@
         <v>39</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>1014</v>
@@ -9087,10 +9087,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G80" s="2">
         <v>45481</v>
@@ -9125,7 +9125,7 @@
         <v>48</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G81" s="2">
         <v>44748</v>
@@ -9157,10 +9157,10 @@
         <v>36</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G82" s="2">
         <v>45575</v>
@@ -9192,7 +9192,7 @@
         <v>45</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>970</v>
@@ -9221,10 +9221,10 @@
         <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G84" s="2">
         <v>44353</v>
@@ -9256,10 +9256,10 @@
         <v>48</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G85" s="2">
         <v>45208</v>
@@ -9294,7 +9294,7 @@
         <v>50</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G86" s="2">
         <v>44073</v>
@@ -9326,10 +9326,10 @@
         <v>33</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G87" s="2">
         <v>45401</v>
@@ -9361,7 +9361,7 @@
         <v>160</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>1055</v>
@@ -9399,7 +9399,7 @@
         <v>48</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G89" t="s">
         <v>1125</v>
@@ -9431,10 +9431,10 @@
         <v>30</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G90" s="2">
         <v>43600</v>
@@ -9466,7 +9466,7 @@
         <v>42</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>48</v>
@@ -9501,7 +9501,7 @@
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>48</v>
@@ -9536,10 +9536,10 @@
         <v>24</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G93" t="s">
         <v>1133</v>
@@ -9574,7 +9574,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G94" s="2">
         <v>44414</v>
@@ -9606,10 +9606,10 @@
         <v>48</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G95" t="s">
         <v>1137</v>
@@ -9641,10 +9641,10 @@
         <v>35</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G96" s="2">
         <v>44113</v>
@@ -9679,7 +9679,7 @@
         <v>48</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G97" s="2">
         <v>43761</v>
@@ -9708,10 +9708,10 @@
         <v>47</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G98" s="2">
         <v>43466</v>
@@ -9743,10 +9743,10 @@
         <v>21</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G99" t="s">
         <v>1144</v>
@@ -9778,10 +9778,10 @@
         <v>-8</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G100" t="s">
         <v>1137</v>
@@ -9813,10 +9813,10 @@
         <v>31</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G101" t="s">
         <v>1148</v>
@@ -9851,7 +9851,7 @@
         <v>50</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G102" s="2">
         <v>45471</v>
@@ -9883,10 +9883,10 @@
         <v>48</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G103" t="s">
         <v>1152</v>
@@ -9915,10 +9915,10 @@
         <v>948</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G104" t="s">
         <v>1154</v>
@@ -9950,7 +9950,7 @@
         <v>34</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>1157</v>
@@ -10017,10 +10017,10 @@
         <v>26</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G107" t="s">
         <v>1163</v>
@@ -10052,10 +10052,10 @@
         <v>18</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="H108" t="s">
         <v>1165</v>
@@ -10084,7 +10084,7 @@
         <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>1014</v>
@@ -10122,7 +10122,7 @@
         <v>50</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G110" t="s">
         <v>1168</v>
@@ -10154,7 +10154,7 @@
         <v>32</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>970</v>
@@ -10189,10 +10189,10 @@
         <v>145</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G112" s="2">
         <v>44633</v>
@@ -10224,10 +10224,10 @@
         <v>25</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G113" s="2">
         <v>44060</v>
@@ -10294,10 +10294,10 @@
         <v>48</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G115" s="2">
         <v>44646</v>
@@ -10329,7 +10329,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>1157</v>
@@ -10364,10 +10364,10 @@
         <v>48</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G117" t="s">
         <v>1182</v>
@@ -10399,10 +10399,10 @@
         <v>22</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G118" t="s">
         <v>1185</v>
@@ -10437,7 +10437,7 @@
         <v>50</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G119" s="2">
         <v>44427</v>
@@ -10469,10 +10469,10 @@
         <v>37</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G120" s="2">
         <v>45601</v>
@@ -10504,7 +10504,7 @@
         <v>28</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>1055</v>
@@ -10539,7 +10539,7 @@
         <v>41</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>1003</v>
@@ -10609,7 +10609,7 @@
         <v>19</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>1014</v>
@@ -10644,10 +10644,10 @@
         <v>35</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G125" s="2">
         <v>44502</v>
@@ -10679,10 +10679,10 @@
         <v>48</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G126" s="2">
         <v>44508</v>
@@ -10714,7 +10714,7 @@
         <v>50</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G127" t="s">
         <v>1202</v>
@@ -10746,10 +10746,10 @@
         <v>-3</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G128" t="s">
         <v>1203</v>
@@ -10781,7 +10781,7 @@
         <v>46</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>962</v>
@@ -10816,7 +10816,7 @@
         <v>24</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>970</v>
@@ -10886,10 +10886,10 @@
         <v>40</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G132" s="2">
         <v>45611</v>
@@ -10921,10 +10921,10 @@
         <v>29</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G133" t="s">
         <v>1212</v>
@@ -10956,7 +10956,7 @@
         <v>48</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>1010</v>
@@ -11026,10 +11026,10 @@
         <v>36</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G136" s="2">
         <v>44052</v>
@@ -11061,10 +11061,10 @@
         <v>950</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G137" t="s">
         <v>1221</v>
@@ -11096,10 +11096,10 @@
         <v>27</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G138" s="2">
         <v>43608</v>
@@ -11134,7 +11134,7 @@
         <v>48</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G139" t="s">
         <v>1225</v>
@@ -11166,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>1157</v>
@@ -11201,10 +11201,10 @@
         <v>50</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G141" t="s">
         <v>1229</v>
@@ -11236,7 +11236,7 @@
         <v>38</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>1003</v>
@@ -11306,7 +11306,7 @@
         <v>48</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>48</v>
@@ -11341,7 +11341,7 @@
         <v>25</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>1055</v>
@@ -11373,10 +11373,10 @@
         <v>43</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G146" s="2">
         <v>43656</v>
@@ -11443,7 +11443,7 @@
         <v>15</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>970</v>
@@ -11478,10 +11478,10 @@
         <v>49</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G149" s="2">
         <v>45564</v>
@@ -11513,10 +11513,10 @@
         <v>34</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G150" t="s">
         <v>1248</v>
@@ -11545,10 +11545,10 @@
         <v>48</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G151" s="2">
         <v>45354</v>
@@ -11615,7 +11615,7 @@
         <v>28</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>970</v>
@@ -11650,10 +11650,10 @@
         <v>50</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G154" t="s">
         <v>48</v>
@@ -11685,10 +11685,10 @@
         <v>41</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G155" t="s">
         <v>1257</v>
@@ -11723,7 +11723,7 @@
         <v>48</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G156" t="s">
         <v>1260</v>
@@ -11755,7 +11755,7 @@
         <v>135</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>970</v>
@@ -11787,7 +11787,7 @@
         <v>31</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>1055</v>
@@ -11822,7 +11822,7 @@
         <v>45</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>1157</v>
@@ -11860,7 +11860,7 @@
         <v>50</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G160" t="s">
         <v>1270</v>
@@ -11892,7 +11892,7 @@
         <v>39</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>50</v>
@@ -11927,10 +11927,10 @@
         <v>48</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G162" s="2">
         <v>45632</v>
@@ -11997,7 +11997,7 @@
         <v>33</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>1010</v>
@@ -12032,7 +12032,7 @@
         <v>20</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
@@ -12067,7 +12067,7 @@
         <v>42</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>1003</v>
@@ -12099,7 +12099,7 @@
         <v>50</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>970</v>
@@ -12137,7 +12137,7 @@
         <v>50</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G168" s="2">
         <v>45100</v>
@@ -12169,7 +12169,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>1055</v>
@@ -12207,7 +12207,7 @@
         <v>48</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G170" t="s">
         <v>1286</v>
@@ -12239,10 +12239,10 @@
         <v>-6</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G171" t="s">
         <v>1288</v>
@@ -12274,7 +12274,7 @@
         <v>47</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>962</v>
@@ -12309,7 +12309,7 @@
         <v>25</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>48</v>
@@ -12344,10 +12344,10 @@
         <v>30</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G174" t="s">
         <v>51</v>
@@ -12414,7 +12414,7 @@
         <v>50</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>958</v>
@@ -12449,10 +12449,10 @@
         <v>22</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G177" s="2">
         <v>44842</v>
@@ -12484,7 +12484,7 @@
         <v>34</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>48</v>
@@ -12554,10 +12554,10 @@
         <v>180</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G180" s="2">
         <v>44141</v>
@@ -12589,10 +12589,10 @@
         <v>27</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G181" t="s">
         <v>1307</v>
@@ -12624,10 +12624,10 @@
         <v>38</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G182" s="2">
         <v>45169</v>
@@ -12662,7 +12662,7 @@
         <v>50</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G183" s="2">
         <v>43648</v>
@@ -12694,10 +12694,10 @@
         <v>952</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G184" s="2">
         <v>45171</v>
@@ -12726,7 +12726,7 @@
         <v>44</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>1157</v>
@@ -12796,7 +12796,7 @@
         <v>48</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>970</v>
@@ -12831,10 +12831,10 @@
         <v>35</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G188" s="2">
         <v>43575</v>
@@ -12866,10 +12866,10 @@
         <v>29</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G189" t="s">
         <v>1318</v>
@@ -12904,7 +12904,7 @@
         <v>50</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G190" t="s">
         <v>1320</v>
@@ -12936,10 +12936,10 @@
         <v>50</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G191" t="s">
         <v>1323</v>
@@ -12971,7 +12971,7 @@
         <v>24</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>962</v>
@@ -13003,7 +13003,7 @@
         <v>37</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -13041,7 +13041,7 @@
         <v>48</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G194" s="2">
         <v>44758</v>
@@ -13073,7 +13073,7 @@
         <v>48</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>1157</v>
@@ -13108,10 +13108,10 @@
         <v>33</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G196" t="s">
         <v>1333</v>
@@ -13143,10 +13143,10 @@
         <v>41</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G197" t="s">
         <v>1335</v>
@@ -13181,7 +13181,7 @@
         <v>50</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G198" s="2">
         <v>44657</v>
@@ -13213,10 +13213,10 @@
         <v>-4</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G199" t="s">
         <v>1338</v>
@@ -13248,10 +13248,10 @@
         <v>46</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G200" s="2">
         <v>44442</v>
@@ -13318,7 +13318,7 @@
         <v>50</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>1055</v>
@@ -13353,7 +13353,7 @@
         <v>39</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F203" s="5">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>21</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>1003</v>
@@ -13423,10 +13423,10 @@
         <v>48</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G205" s="2">
         <v>43747</v>
@@ -13493,7 +13493,7 @@
         <v>25</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>48</v>
@@ -13528,10 +13528,10 @@
         <v>43</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G208" t="s">
         <v>1353</v>
@@ -13566,7 +13566,7 @@
         <v>48</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G209" t="s">
         <v>1356</v>
@@ -13595,10 +13595,10 @@
         <v>155</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G210" t="s">
         <v>1359</v>
@@ -13630,10 +13630,10 @@
         <v>27</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G211" s="2">
         <v>45543</v>
@@ -13665,10 +13665,10 @@
         <v>50</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G212" t="s">
         <v>51</v>
@@ -13703,7 +13703,7 @@
         <v>50</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G213" s="2">
         <v>43851</v>
@@ -13735,7 +13735,7 @@
         <v>48</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>1014</v>
@@ -13770,10 +13770,10 @@
         <v>49</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G215" s="2">
         <v>44595</v>
@@ -13808,7 +13808,7 @@
         <v>48</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G216" t="s">
         <v>1370</v>
@@ -13837,10 +13837,10 @@
         <v>23</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G217" s="2">
         <v>44213</v>
@@ -13869,10 +13869,10 @@
         <v>31</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G218" s="2">
         <v>44597</v>
@@ -13904,10 +13904,10 @@
         <v>48</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G219" s="2">
         <v>45265</v>
@@ -13939,10 +13939,10 @@
         <v>29</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G220" t="s">
         <v>50</v>
@@ -13971,10 +13971,10 @@
         <v>48</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G221" t="s">
         <v>1377</v>
@@ -14009,7 +14009,7 @@
         <v>50</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G222" s="2">
         <v>44908</v>
@@ -14041,7 +14041,7 @@
         <v>44</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>48</v>
@@ -14076,7 +14076,7 @@
         <v>18</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>1157</v>
@@ -14146,10 +14146,10 @@
         <v>37</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G226" s="2">
         <v>44169</v>
@@ -14181,10 +14181,10 @@
         <v>26</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G227" t="s">
         <v>1386</v>
@@ -14216,10 +14216,10 @@
         <v>-9</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G228" s="2">
         <v>44473</v>
@@ -14254,7 +14254,7 @@
         <v>50</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G229" s="2">
         <v>44476</v>
@@ -14286,10 +14286,10 @@
         <v>48</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G230" s="2">
         <v>44217</v>
@@ -14321,7 +14321,7 @@
         <v>30</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>958</v>
@@ -14391,7 +14391,7 @@
         <v>22</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>50</v>
@@ -14426,10 +14426,10 @@
         <v>50</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G234" s="2">
         <v>44933</v>
@@ -14461,10 +14461,10 @@
         <v>953</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G235" t="s">
         <v>1400</v>
@@ -14528,10 +14528,10 @@
         <v>50</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G237" s="2">
         <v>45646</v>
@@ -14563,10 +14563,10 @@
         <v>27</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G238" s="2">
         <v>44998</v>
@@ -14598,7 +14598,7 @@
         <v>48</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>970</v>
@@ -14636,7 +14636,7 @@
         <v>48</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G240" t="s">
         <v>1409</v>
@@ -14668,7 +14668,7 @@
         <v>32</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>1157</v>
@@ -14703,7 +14703,7 @@
         <v>24</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>50</v>
@@ -14738,7 +14738,7 @@
         <v>145</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>33</v>
@@ -14776,7 +14776,7 @@
         <v>50</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G244" t="s">
         <v>1419</v>
@@ -14808,7 +14808,7 @@
         <v>28</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>50</v>
@@ -14843,10 +14843,10 @@
         <v>43</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G246" t="s">
         <v>1137</v>
@@ -14881,7 +14881,7 @@
         <v>48</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G247" s="2">
         <v>45082</v>
@@ -14913,10 +14913,10 @@
         <v>19</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G248" t="s">
         <v>1424</v>
@@ -14948,10 +14948,10 @@
         <v>48</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G249" t="s">
         <v>1427</v>
@@ -14983,10 +14983,10 @@
         <v>33</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G250" s="2">
         <v>44303</v>
@@ -15015,7 +15015,7 @@
         <v>50</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G251" s="2">
         <v>45270</v>
@@ -15047,10 +15047,10 @@
         <v>25</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G252" t="s">
         <v>1431</v>
@@ -15082,10 +15082,10 @@
         <v>-7</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G253" t="s">
         <v>1434</v>
@@ -15120,7 +15120,7 @@
         <v>48</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G254" s="2">
         <v>43784</v>
@@ -15152,10 +15152,10 @@
         <v>30</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G255" t="s">
         <v>1137</v>
@@ -15184,10 +15184,10 @@
         <v>48</v>
       </c>
       <c r="E256" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F256" s="5" t="s">
         <v>1899</v>
-      </c>
-      <c r="F256" s="5" t="s">
-        <v>1901</v>
       </c>
       <c r="G256" s="2">
         <v>45360</v>
@@ -15219,10 +15219,10 @@
         <v>954</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G257" s="2">
         <v>44737</v>
@@ -15254,10 +15254,10 @@
         <v>41</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G258" t="s">
         <v>1440</v>
@@ -15292,7 +15292,7 @@
         <v>50</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G259" t="s">
         <v>1442</v>
@@ -15324,7 +15324,7 @@
         <v>34</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>1157</v>
@@ -15359,10 +15359,10 @@
         <v>50</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G261" s="2">
         <v>44262</v>
@@ -15397,7 +15397,7 @@
         <v>48</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G262" s="2">
         <v>43521</v>
@@ -15429,7 +15429,7 @@
         <v>36</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>970</v>
@@ -15464,10 +15464,10 @@
         <v>48</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G264" s="2">
         <v>44601</v>
@@ -15499,7 +15499,7 @@
         <v>160</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>962</v>
@@ -15537,7 +15537,7 @@
         <v>50</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G266" s="2">
         <v>44638</v>
@@ -15569,10 +15569,10 @@
         <v>45</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G267" s="2">
         <v>43857</v>
@@ -15604,10 +15604,10 @@
         <v>31</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G268" s="2">
         <v>45657</v>
@@ -15674,7 +15674,7 @@
         <v>50</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>1003</v>
@@ -15706,10 +15706,10 @@
         <v>39</v>
       </c>
       <c r="E271" s="5" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F271" s="5" t="s">
         <v>1935</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>1937</v>
       </c>
       <c r="G271" s="2">
         <v>43877</v>
@@ -15741,10 +15741,10 @@
         <v>48</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G272" s="2">
         <v>44169</v>
@@ -15808,10 +15808,10 @@
         <v>42</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G274" t="s">
         <v>1468</v>
@@ -15843,10 +15843,10 @@
         <v>28</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G275" s="2">
         <v>44661</v>
@@ -15878,10 +15878,10 @@
         <v>17</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G276" t="s">
         <v>1472</v>
@@ -15916,7 +15916,7 @@
         <v>48</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G277" s="2">
         <v>43818</v>
@@ -15948,10 +15948,10 @@
         <v>40</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G278" t="s">
         <v>48</v>
@@ -15983,10 +15983,10 @@
         <v>50</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G279" t="s">
         <v>1478</v>
@@ -16018,7 +16018,7 @@
         <v>26</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>48</v>
@@ -16056,7 +16056,7 @@
         <v>50</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G281" t="s">
         <v>1480</v>
@@ -16088,10 +16088,10 @@
         <v>44</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G282" s="2">
         <v>44907</v>
@@ -16126,7 +16126,7 @@
         <v>48</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G283" s="2">
         <v>44930</v>
@@ -16158,10 +16158,10 @@
         <v>30</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G284" t="s">
         <v>1486</v>
@@ -16193,10 +16193,10 @@
         <v>37</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G285" s="2">
         <v>45146</v>
@@ -16228,7 +16228,7 @@
         <v>23</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>970</v>
@@ -16263,10 +16263,10 @@
         <v>48</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G287" t="s">
         <v>1491</v>
@@ -16301,7 +16301,7 @@
         <v>50</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G288" s="2">
         <v>43500</v>
@@ -16330,7 +16330,7 @@
         <v>950</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F289" s="5">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>48</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G290" t="s">
         <v>1497</v>
@@ -16400,7 +16400,7 @@
         <v>31</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>1003</v>
@@ -16432,7 +16432,7 @@
         <v>41</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>48</v>
@@ -16464,10 +16464,10 @@
         <v>50</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G293" t="s">
         <v>1501</v>
@@ -16499,10 +16499,10 @@
         <v>20</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F294" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G294" s="2">
         <v>44249</v>
@@ -16537,7 +16537,7 @@
         <v>50</v>
       </c>
       <c r="F295" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G295" s="2">
         <v>44463</v>
@@ -16569,7 +16569,7 @@
         <v>43</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>962</v>
@@ -16604,7 +16604,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>958</v>
@@ -16674,7 +16674,7 @@
         <v>150</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>50</v>
@@ -16709,10 +16709,10 @@
         <v>32</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F300" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G300" t="s">
         <v>1515</v>
@@ -16744,7 +16744,7 @@
         <v>50</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F301" s="5">
         <v>0</v>
@@ -16779,7 +16779,7 @@
         <v>50</v>
       </c>
       <c r="F302" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G302" s="2">
         <v>44630</v>
@@ -16808,7 +16808,7 @@
         <v>48</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>970</v>
@@ -16843,10 +16843,10 @@
         <v>39</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G304" t="s">
         <v>1523</v>
@@ -16910,7 +16910,7 @@
         <v>29</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>1055</v>
@@ -16945,10 +16945,10 @@
         <v>-5</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G307" t="s">
         <v>1530</v>
@@ -16980,10 +16980,10 @@
         <v>35</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G308" t="s">
         <v>1533</v>
@@ -17018,7 +17018,7 @@
         <v>50</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G309" t="s">
         <v>1536</v>
@@ -17050,10 +17050,10 @@
         <v>40</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G310" t="s">
         <v>1539</v>
@@ -17085,10 +17085,10 @@
         <v>48</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G311" s="2">
         <v>45018</v>
@@ -17123,7 +17123,7 @@
         <v>48</v>
       </c>
       <c r="F312" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G312" s="2">
         <v>43600</v>
@@ -17155,7 +17155,7 @@
         <v>31</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>33</v>
@@ -17190,10 +17190,10 @@
         <v>50</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F314" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G314" t="s">
         <v>48</v>
@@ -17225,7 +17225,7 @@
         <v>24</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="F315" s="5" t="s">
         <v>962</v>
@@ -17260,7 +17260,7 @@
         <v>42</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F316" s="5" t="s">
         <v>48</v>
@@ -17298,7 +17298,7 @@
         <v>50</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G317" t="s">
         <v>1553</v>
@@ -17330,7 +17330,7 @@
         <v>48</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F318" s="5" t="s">
         <v>1003</v>
@@ -17365,10 +17365,10 @@
         <v>18</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G319" s="2">
         <v>43613</v>
@@ -17432,10 +17432,10 @@
         <v>45</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G321" s="2">
         <v>43984</v>
@@ -17464,7 +17464,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F322" s="5" t="s">
         <v>962</v>
@@ -17499,10 +17499,10 @@
         <v>50</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F323" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G323" t="s">
         <v>1565</v>
@@ -17569,10 +17569,10 @@
         <v>48</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F325" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G325" s="2">
         <v>44364</v>
@@ -17636,10 +17636,10 @@
         <v>26</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F327" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G327" s="2">
         <v>44502</v>
@@ -17671,7 +17671,7 @@
         <v>41</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F328" s="5" t="s">
         <v>48</v>
@@ -17706,7 +17706,7 @@
         <v>22</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F329" s="5" t="s">
         <v>33</v>
@@ -17738,10 +17738,10 @@
         <v>948</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="F330" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G330" s="2">
         <v>44318</v>
@@ -17773,7 +17773,7 @@
         <v>50</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G331" s="2">
         <v>44806</v>
@@ -17805,10 +17805,10 @@
         <v>48</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F332" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G332" t="s">
         <v>1581</v>
@@ -17840,10 +17840,10 @@
         <v>33</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G333" s="2">
         <v>43482</v>
@@ -17878,7 +17878,7 @@
         <v>48</v>
       </c>
       <c r="F334" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G334" t="s">
         <v>1584</v>
@@ -17910,7 +17910,7 @@
         <v>50</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="F335" s="5">
         <v>0</v>
@@ -17942,10 +17942,10 @@
         <v>44</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G336" t="s">
         <v>1589</v>
@@ -17977,10 +17977,10 @@
         <v>19</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F337" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G337" t="s">
         <v>1592</v>
@@ -18015,7 +18015,7 @@
         <v>50</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G338" t="s">
         <v>1595</v>
@@ -18044,10 +18044,10 @@
         <v>36</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G339" s="2">
         <v>44532</v>
@@ -18076,7 +18076,7 @@
         <v>31</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F340" s="5">
         <v>0</v>
@@ -18111,7 +18111,7 @@
         <v>48</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G341" t="s">
         <v>1601</v>
@@ -18143,7 +18143,7 @@
         <v>40</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F342" s="5">
         <v>0</v>
@@ -18178,10 +18178,10 @@
         <v>25</v>
       </c>
       <c r="E343" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F343" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G343" s="2">
         <v>44848</v>
@@ -18210,7 +18210,7 @@
         <v>50</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F344" s="5" t="s">
         <v>1157</v>
@@ -18248,7 +18248,7 @@
         <v>50</v>
       </c>
       <c r="F345" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G345" t="s">
         <v>1608</v>
@@ -18280,7 +18280,7 @@
         <v>43</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F346" s="5">
         <v>0</v>
@@ -18315,10 +18315,10 @@
         <v>28</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F347" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G347" s="2">
         <v>44192</v>
@@ -18350,10 +18350,10 @@
         <v>35</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="F348" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G348" s="2">
         <v>44323</v>
@@ -18388,7 +18388,7 @@
         <v>48</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G349" s="2">
         <v>45390</v>
@@ -18420,7 +18420,7 @@
         <v>24</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F350" s="5" t="s">
         <v>48</v>
@@ -18452,7 +18452,7 @@
         <v>42</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F351" s="5" t="s">
         <v>958</v>
@@ -18487,7 +18487,7 @@
         <v>50</v>
       </c>
       <c r="E352" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F352" s="5" t="s">
         <v>1157</v>
@@ -18525,7 +18525,7 @@
         <v>50</v>
       </c>
       <c r="F353" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G353" t="s">
         <v>51</v>
@@ -18554,10 +18554,10 @@
         <v>48</v>
       </c>
       <c r="E354" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F354" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G354" t="s">
         <v>1623</v>
@@ -18589,7 +18589,7 @@
         <v>956</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F355" s="5">
         <v>0</v>
@@ -18627,7 +18627,7 @@
         <v>48</v>
       </c>
       <c r="F356" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G356" s="2">
         <v>43862</v>
@@ -18659,7 +18659,7 @@
         <v>27</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F357" s="5" t="s">
         <v>48</v>
@@ -18694,7 +18694,7 @@
         <v>46</v>
       </c>
       <c r="E358" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F358" s="5" t="s">
         <v>33</v>
@@ -18726,7 +18726,7 @@
         <v>32</v>
       </c>
       <c r="E359" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F359" s="5" t="s">
         <v>958</v>
@@ -18790,7 +18790,7 @@
         <v>41</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F361" s="5">
         <v>0</v>
@@ -18828,7 +18828,7 @@
         <v>48</v>
       </c>
       <c r="F362" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G362" t="s">
         <v>1137</v>
@@ -18860,7 +18860,7 @@
         <v>50</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F363" s="5">
         <v>0</v>
@@ -18895,10 +18895,10 @@
         <v>36</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F364" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G364" t="s">
         <v>1641</v>
@@ -18930,7 +18930,7 @@
         <v>18</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="F365" s="5" t="s">
         <v>1157</v>
@@ -18968,7 +18968,7 @@
         <v>50</v>
       </c>
       <c r="F366" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G366" s="2">
         <v>44450</v>
@@ -19000,10 +19000,10 @@
         <v>34</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F367" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G367" t="s">
         <v>1646</v>
@@ -19035,10 +19035,10 @@
         <v>29</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F368" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G368" s="2">
         <v>43681</v>
@@ -19102,7 +19102,7 @@
         <v>47</v>
       </c>
       <c r="E370" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F370" s="5" t="s">
         <v>970</v>
@@ -19134,7 +19134,7 @@
         <v>25</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F371" s="5" t="s">
         <v>33</v>
@@ -19169,10 +19169,10 @@
         <v>40</v>
       </c>
       <c r="E372" s="5" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G372" s="2">
         <v>45339</v>
@@ -19207,7 +19207,7 @@
         <v>50</v>
       </c>
       <c r="F373" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G373" t="s">
         <v>1657</v>
@@ -19239,10 +19239,10 @@
         <v>33</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F374" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G374" t="s">
         <v>48</v>
@@ -19274,10 +19274,10 @@
         <v>48</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F375" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G375" t="s">
         <v>1661</v>
@@ -19312,7 +19312,7 @@
         <v>48</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G376" t="s">
         <v>1663</v>
@@ -19344,10 +19344,10 @@
         <v>21</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F377" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G377" t="s">
         <v>1665</v>
@@ -19379,7 +19379,7 @@
         <v>145</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F378" s="5" t="s">
         <v>48</v>
@@ -19411,10 +19411,10 @@
         <v>31</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G379" s="2">
         <v>45159</v>
@@ -19481,7 +19481,7 @@
         <v>44</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F381" s="5" t="s">
         <v>48</v>
@@ -19516,10 +19516,10 @@
         <v>48</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G382" t="s">
         <v>1049</v>
@@ -19554,7 +19554,7 @@
         <v>48</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G383" s="2">
         <v>44114</v>
@@ -19586,10 +19586,10 @@
         <v>26</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G384" s="2">
         <v>44904</v>
@@ -19621,10 +19621,10 @@
         <v>50</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F385" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G385" t="s">
         <v>1680</v>
@@ -19656,7 +19656,7 @@
         <v>37</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F386" s="5" t="s">
         <v>1010</v>
@@ -19726,7 +19726,7 @@
         <v>48</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F388" s="5" t="s">
         <v>962</v>
@@ -19761,10 +19761,10 @@
         <v>42</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G389" s="2">
         <v>44159</v>
@@ -19831,10 +19831,10 @@
         <v>28</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G391" s="2">
         <v>44810</v>
@@ -19866,10 +19866,10 @@
         <v>-4</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G392" t="s">
         <v>1696</v>
@@ -19901,7 +19901,7 @@
         <v>49</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="F393" s="5" t="s">
         <v>48</v>
@@ -19971,10 +19971,10 @@
         <v>48</v>
       </c>
       <c r="E395" s="5" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G395" s="2">
         <v>45601</v>
@@ -20006,10 +20006,10 @@
         <v>32</v>
       </c>
       <c r="E396" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G396" s="2">
         <v>45385</v>
@@ -20041,7 +20041,7 @@
         <v>48</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G397" t="s">
         <v>1706</v>
@@ -20073,7 +20073,7 @@
         <v>24</v>
       </c>
       <c r="E398" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F398" s="5" t="s">
         <v>48</v>
@@ -20108,10 +20108,10 @@
         <v>36</v>
       </c>
       <c r="E399" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F399" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G399" t="s">
         <v>1003</v>
@@ -20143,10 +20143,10 @@
         <v>48</v>
       </c>
       <c r="E400" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G400" s="2">
         <v>44660</v>
@@ -20213,10 +20213,10 @@
         <v>43</v>
       </c>
       <c r="E402" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G402" t="s">
         <v>51</v>
@@ -20248,7 +20248,7 @@
         <v>50</v>
       </c>
       <c r="E403" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F403" s="5" t="s">
         <v>33</v>
@@ -20286,7 +20286,7 @@
         <v>48</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G404" s="2">
         <v>45408</v>
@@ -20315,10 +20315,10 @@
         <v>160</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G405" t="s">
         <v>1719</v>
@@ -20350,10 +20350,10 @@
         <v>39</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G406" t="s">
         <v>1722</v>
@@ -20385,10 +20385,10 @@
         <v>22</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G407" t="s">
         <v>1724</v>
@@ -20455,10 +20455,10 @@
         <v>49</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G409" s="2">
         <v>43930</v>
@@ -20490,10 +20490,10 @@
         <v>34</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G410" t="s">
         <v>1730</v>
@@ -20528,7 +20528,7 @@
         <v>48</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G411" t="s">
         <v>1733</v>
@@ -20560,10 +20560,10 @@
         <v>29</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G412" s="2">
         <v>45574</v>
@@ -20595,10 +20595,10 @@
         <v>50</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G413" t="s">
         <v>51</v>
@@ -20630,7 +20630,7 @@
         <v>18</v>
       </c>
       <c r="E414" s="5" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="F414" s="5" t="s">
         <v>50</v>
@@ -20665,7 +20665,7 @@
         <v>50</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G415" s="2">
         <v>43792</v>
@@ -20697,10 +20697,10 @@
         <v>37</v>
       </c>
       <c r="E416" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G416" t="s">
         <v>1742</v>
@@ -20732,10 +20732,10 @@
         <v>25</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G417" s="2">
         <v>45383</v>
@@ -20770,7 +20770,7 @@
         <v>48</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G418" s="2">
         <v>44545</v>
@@ -20802,10 +20802,10 @@
         <v>-1</v>
       </c>
       <c r="E419" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G419" t="s">
         <v>1748</v>
@@ -20837,10 +20837,10 @@
         <v>31</v>
       </c>
       <c r="E420" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G420" t="s">
         <v>1751</v>
@@ -20872,7 +20872,7 @@
         <v>50</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F421" s="5" t="s">
         <v>48</v>
@@ -20910,7 +20910,7 @@
         <v>50</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G422" t="s">
         <v>1137</v>
@@ -20942,10 +20942,10 @@
         <v>44</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G423" t="s">
         <v>1757</v>
@@ -20977,10 +20977,10 @@
         <v>33</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G424" t="s">
         <v>1759</v>
@@ -21047,7 +21047,7 @@
         <v>38</v>
       </c>
       <c r="E426" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F426" s="5" t="s">
         <v>1014</v>
@@ -21082,10 +21082,10 @@
         <v>48</v>
       </c>
       <c r="E427" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G427" s="2">
         <v>44199</v>
@@ -21117,10 +21117,10 @@
         <v>26</v>
       </c>
       <c r="E428" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G428" t="s">
         <v>1766</v>
@@ -21155,7 +21155,7 @@
         <v>50</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G429" s="2">
         <v>43952</v>
@@ -21187,10 +21187,10 @@
         <v>50</v>
       </c>
       <c r="E430" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G430" t="s">
         <v>1137</v>
@@ -21222,7 +21222,7 @@
         <v>48</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G431" s="2">
         <v>45583</v>
@@ -21254,7 +21254,7 @@
         <v>150</v>
       </c>
       <c r="E432" s="5" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F432" s="5" t="s">
         <v>970</v>
@@ -21289,10 +21289,10 @@
         <v>30</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G433" t="s">
         <v>1003</v>
@@ -21324,10 +21324,10 @@
         <v>23</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G434" t="s">
         <v>1775</v>
@@ -21359,10 +21359,10 @@
         <v>48</v>
       </c>
       <c r="E435" s="5" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G435" s="2">
         <v>45264</v>
@@ -21426,7 +21426,7 @@
         <v>40</v>
       </c>
       <c r="E437" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F437" s="5" t="s">
         <v>1014</v>
@@ -21461,7 +21461,7 @@
         <v>32</v>
       </c>
       <c r="E438" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F438" s="5" t="s">
         <v>1014</v>
@@ -21499,7 +21499,7 @@
         <v>48</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="G439" s="2">
         <v>45551</v>
@@ -21531,10 +21531,10 @@
         <v>50</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G440" t="s">
         <v>1783</v>
@@ -21566,10 +21566,10 @@
         <v>19</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G441" s="2">
         <v>45650</v>
@@ -21598,7 +21598,7 @@
         <v>48</v>
       </c>
       <c r="E442" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F442" s="5" t="s">
         <v>958</v>
@@ -21668,10 +21668,10 @@
         <v>36</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G444" t="s">
         <v>1792</v>
@@ -21703,10 +21703,10 @@
         <v>25</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G445" s="2">
         <v>43533</v>
@@ -21773,7 +21773,7 @@
         <v>43</v>
       </c>
       <c r="E447" s="5" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F447" s="5" t="s">
         <v>50</v>
@@ -21808,7 +21808,7 @@
         <v>50</v>
       </c>
       <c r="E448" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F448" s="5">
         <v>0</v>
@@ -21840,10 +21840,10 @@
         <v>48</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G449" t="s">
         <v>1802</v>
@@ -21878,7 +21878,7 @@
         <v>50</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G450" s="2">
         <v>44471</v>
@@ -21907,7 +21907,7 @@
         <v>34</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F451" s="5" t="s">
         <v>1157</v>
@@ -21942,7 +21942,7 @@
         <v>21</v>
       </c>
       <c r="E452" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F452" s="5" t="s">
         <v>1157</v>
@@ -21980,7 +21980,7 @@
         <v>48</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G453" s="2">
         <v>44623</v>
@@ -22012,10 +22012,10 @@
         <v>48</v>
       </c>
       <c r="E454" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G454" t="s">
         <v>1808</v>
@@ -22047,7 +22047,7 @@
         <v>38</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F455" s="5" t="s">
         <v>1157</v>
@@ -22079,10 +22079,10 @@
         <v>27</v>
       </c>
       <c r="E456" s="5" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G456" s="2">
         <v>45482</v>
@@ -22117,7 +22117,7 @@
         <v>50</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G457" t="s">
         <v>1813</v>
@@ -22149,7 +22149,7 @@
         <v>31</v>
       </c>
       <c r="E458" s="5" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="F458" s="5" t="s">
         <v>50</v>
@@ -22184,10 +22184,10 @@
         <v>175</v>
       </c>
       <c r="E459" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F459" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G459" s="2">
         <v>44361</v>
@@ -22222,7 +22222,7 @@
         <v>48</v>
       </c>
       <c r="F460" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G460" t="s">
         <v>1820</v>
@@ -22254,7 +22254,7 @@
         <v>24</v>
       </c>
       <c r="E461" s="5" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="F461" s="5" t="s">
         <v>50</v>
@@ -22289,10 +22289,10 @@
         <v>48</v>
       </c>
       <c r="E462" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F462" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G462" t="s">
         <v>1825</v>
@@ -22324,10 +22324,10 @@
         <v>952</v>
       </c>
       <c r="E463" s="5" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G463" t="s">
         <v>1828</v>
@@ -22362,7 +22362,7 @@
         <v>50</v>
       </c>
       <c r="F464" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G464" s="2">
         <v>43931</v>
@@ -22394,10 +22394,10 @@
         <v>33</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G465" t="s">
         <v>1003</v>
@@ -22432,7 +22432,7 @@
         <v>48</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G466" s="2">
         <v>43471</v>
@@ -22464,10 +22464,10 @@
         <v>50</v>
       </c>
       <c r="E467" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G467" s="2">
         <v>45066</v>
@@ -22499,10 +22499,10 @@
         <v>22</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="G468" t="s">
         <v>1137</v>
@@ -22534,10 +22534,10 @@
         <v>48</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G469" s="2">
         <v>45472</v>
@@ -22572,7 +22572,7 @@
         <v>50</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G470" s="2">
         <v>45613</v>
@@ -22604,7 +22604,7 @@
         <v>35</v>
       </c>
       <c r="E471" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F471" s="5" t="s">
         <v>958</v>
@@ -22639,10 +22639,10 @@
         <v>28</v>
       </c>
       <c r="E472" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G472" s="2">
         <v>45607</v>
@@ -22677,7 +22677,7 @@
         <v>48</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="G473" t="s">
         <v>48</v>
@@ -22709,10 +22709,10 @@
         <v>41</v>
       </c>
       <c r="E474" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F474" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G474" s="2">
         <v>44677</v>
@@ -22744,10 +22744,10 @@
         <v>50</v>
       </c>
       <c r="E475" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G475" s="2">
         <v>44929</v>
@@ -22779,7 +22779,7 @@
         <v>48</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="F476" s="5" t="s">
         <v>1014</v>
@@ -22849,10 +22849,10 @@
         <v>37</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G478" s="2">
         <v>44970</v>
@@ -22884,10 +22884,10 @@
         <v>19</v>
       </c>
       <c r="E479" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G479" t="s">
         <v>1853</v>
@@ -22922,7 +22922,7 @@
         <v>48</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="G480" t="s">
         <v>1856</v>
@@ -22954,10 +22954,10 @@
         <v>48</v>
       </c>
       <c r="E481" s="5" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G481" t="s">
         <v>1858</v>
@@ -22989,7 +22989,7 @@
         <v>31</v>
       </c>
       <c r="E482" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F482" s="5" t="s">
         <v>48</v>
@@ -23024,10 +23024,10 @@
         <v>26</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G483" s="2">
         <v>44082</v>
@@ -23059,7 +23059,7 @@
         <v>50</v>
       </c>
       <c r="F484" s="5" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="G484" s="2">
         <v>44512</v>
@@ -23088,10 +23088,10 @@
         <v>40</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="G485" s="2">
         <v>44965</v>
@@ -23155,7 +23155,7 @@
         <v>34</v>
       </c>
       <c r="E487" s="5" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F487" s="5" t="s">
         <v>1003</v>
@@ -23190,10 +23190,10 @@
         <v>23</v>
       </c>
       <c r="E488" s="5" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="G488" t="s">
         <v>1871</v>
@@ -23225,10 +23225,10 @@
         <v>48</v>
       </c>
       <c r="E489" s="5" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G489" t="s">
         <v>1874</v>
@@ -23263,7 +23263,7 @@
         <v>50</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G490" t="s">
         <v>1876</v>
@@ -23295,10 +23295,10 @@
         <v>42</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="G491" s="2">
         <v>45010</v>
@@ -23330,10 +23330,10 @@
         <v>29</v>
       </c>
       <c r="E492" s="5" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G492" t="s">
         <v>1221</v>
@@ -23397,10 +23397,10 @@
         <v>50</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G494" s="2">
         <v>45294</v>
@@ -23432,7 +23432,7 @@
         <v>18</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F495" s="5" t="s">
         <v>33</v>
@@ -23464,10 +23464,10 @@
         <v>48</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="G496" t="s">
         <v>978</v>
@@ -23502,7 +23502,7 @@
         <v>50</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="G497" s="2">
         <v>43505</v>
@@ -23534,10 +23534,10 @@
         <v>32</v>
       </c>
       <c r="E498" s="5" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G498" t="s">
         <v>1885</v>
@@ -23572,7 +23572,7 @@
         <v>48</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="G499" s="2">
         <v>44180</v>
@@ -23604,7 +23604,7 @@
         <v>38</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F500" s="5">
         <v>0</v>
@@ -23639,7 +23639,7 @@
         <v>38</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="F501" s="5">
         <v>0</v>
